--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.3.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y465"/>
+  <dimension ref="A1:Y496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.3.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1,78 To Balance on hand from last year $ 48 14 cultivation. The lot extends to the Bay below â€”â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L14: symbol-only separator/garbage line :: 422.46</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -704,12 +708,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: to Ludger DEPAR â€¦</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+25B2 BLACK UP-POINTING TRIANGLE :: water) at the bre of ▲ L</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: |*% JOHN WHITEFORD, He â€”1-----------" â€”he â€” in will</t>
+          <t>L538: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 18. 2nd Ron Wolfstown 200 | who will be present in Montreal € n the occa-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -786,17 +790,17 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 1as (letter/digit mix) :: â€”1as will defy competition.</t>
+          <t>L63: suspicious token(s): 1as (letter/digit mix) :: —1as will defy competition.</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Antoine Vasseur stone.â€¦...</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 1as (letter/digit mix) :: â€”1as will defy competition.</t>
+          <t>L539: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: 19. •. ** 200 sion; and the opportunity thus afforded to</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -813,12 +817,12 @@
       </c>
       <c r="P4" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Antoine Vasseur stone.â€¦...</t>
+          <t>L84: punctuation artifact: repeated periods :: Antoine Vasseur stone.…...</t>
         </is>
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: |*% JOHN WHITEFORD, He â€”1-----------" â€”he â€” in will</t>
+          <t>L55: punctuation artifact: double/multiple hyphen :: |*% JOHN WHITEFORD, He —1-----------" —he — in will</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -850,12 +854,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>621</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>365</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -878,12 +882,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: æº�</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 2 toisestone.. - 12,00</t>
+          <t>L546: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: 98-• " 200 Establishments, will use every effort to make</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -905,7 +909,7 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 2 toisestone.. - 12,00</t>
+          <t>L71: punctuation artifact: repeated periods :: Antoine Délorier 2 toisestone.. - 12,00</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
@@ -965,12 +969,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ,â€”"Wholesale and Retail.</t>
+          <t>L553: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: ±7, " " 200 on or before the 15th day of July, and all such</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -1052,12 +1056,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Receipts from all sources ...â€¦ ...</t>
+          <t>L178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | symbol-only separator/garbage line :: 48€,00</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - â€” 1 sincere thanks to his friends and the</t>
+          <t>L554: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: • ----------------articles must be delivered at the Exhibition</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1139,19 +1143,19 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: 48â‚¬,00</t>
+          <t>L187: stray/suspicious non-ASCII glyph(s): U+25B2 BLACK UP-POINTING TRIANGLE :: ▲ Card to the Suffering.</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To Augustin Godin work â€”: 11,35</t>
+          <t>L640: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Apply •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1161,7 +1165,7 @@
       </c>
       <c r="P8" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Receipts from all sources ...â€¦ ...</t>
+          <t>L148: punctuation artifact: repeated periods :: Receipts from all sources ...… ...</t>
         </is>
       </c>
       <c r="Q8" s="1" t="inlineStr">
@@ -1226,12 +1230,12 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L223: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L220: stray/suspicious non-ASCII glyph(s): U+4E91 CJK UNIFIED IDEOGRAPH-4E91 | isolated marker/symbol line :: 云</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L172: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Salaries.........- â€” ......</t>
+          <t>L825: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1285,12 +1289,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1313,12 +1317,12 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L259: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L223: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rehantâ€™s Liquor Licence,.... 512,00</t>
+          <t>L872: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •• St. Stanislas and St. Tite,</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1373,7 +1377,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1396,12 +1400,12 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L272: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L259: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: dlarâ€™s Licence,..........13,00</t>
+          <t>L881: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Cash principle; and by this means will be•</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1451,12 +1455,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>495</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1479,12 +1483,12 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L273: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L323: stray/suspicious non-ASCII glyph(s): U+4E1C CJK UNIFIED IDEOGRAPH-4E1C | isolated marker/symbol line :: 东</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L237: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paid to AimÃ© Panneton, for a Poll in</t>
+          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1512,7 +1516,7 @@
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
+          <t>L872: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •• St. Stanislas and St. Tite,</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
@@ -1539,7 +1543,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1562,12 +1566,12 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L323: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸œ</t>
+          <t>L406: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: St. Philipâ€™s Ward, ......</t>
+          <t>L1134: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: ■ Olivier Pothier for the large</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
@@ -1595,7 +1599,7 @@
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr">
         <is>
-          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
+          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr"/>
@@ -1603,7 +1607,7 @@
       <c r="V13" s="1" t="inlineStr"/>
       <c r="W13" s="1" t="inlineStr">
         <is>
-          <t>L1351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Arriving in Montreal at â€” 6.30 P.M.</t>
+          <t>L1351: abbreviation/spacing may be garbled :: Arriving in Montreal at — 6.30 P.M.</t>
         </is>
       </c>
       <c r="X13" s="1" t="inlineStr"/>
@@ -1622,7 +1626,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1645,12 +1649,12 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L385: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Way Stations, at...â€¦.</t>
+          <t>L422: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L251: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Jesuitsâ€™ Estates &amp; Crown Domain Branch,</t>
+          <t>L1242: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • VIEWS ON THE</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
@@ -1667,7 +1671,7 @@
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>L385: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Way Stations, at...â€¦.</t>
+          <t>L385: punctuation artifact: repeated periods :: Way Stations, at...….</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
@@ -1678,7 +1682,7 @@
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="1" t="inlineStr">
         <is>
-          <t>L1017: line starts with punctuation glued to text :: ** St. Maurice, at St. Maurice</t>
+          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
         </is>
       </c>
       <c r="T14" s="1" t="inlineStr"/>
@@ -1728,12 +1732,12 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L398: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ã€Š</t>
+          <t>L429: stray/suspicious non-ASCII glyph(s): U+81EA CJK UNIFIED IDEOGRAPH-81EA, U+53F2 CJK UNIFIED IDEOGRAPH-53F2 :: 自 史</t>
         </is>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 200 â€”</t>
+          <t>L1509: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Maurice Sayer damage €</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
@@ -1761,7 +1765,7 @@
       <c r="R15" s="1" t="inlineStr"/>
       <c r="S15" s="1" t="inlineStr">
         <is>
-          <t>L1024: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | line starts with punctuation glued to text :: ** RiviÃ¨re du Loup, at</t>
+          <t>L1017: line starts with punctuation glued to text :: ** St. Maurice, at St. Maurice</t>
         </is>
       </c>
       <c r="T15" s="1" t="inlineStr"/>
@@ -1811,12 +1815,12 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L434: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: rue. Esquireâ€™s barn, .</t>
+          <t>L1594: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
@@ -1844,7 +1848,7 @@
       <c r="R16" s="1" t="inlineStr"/>
       <c r="S16" s="1" t="inlineStr">
         <is>
-          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
+          <t>L1024: line starts with punctuation glued to text :: ** Rivière du Loup, at</t>
         </is>
       </c>
       <c r="T16" s="1" t="inlineStr"/>
@@ -1894,14 +1898,10 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L429: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: è‡ª å�²</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: I Quarter,.;.â€”</t>
-        </is>
-      </c>
+          <t>L436: stray/suspicious non-ASCII glyph(s): U+81EA CJK UNIFIED IDEOGRAPH-81EA | isolated marker/symbol line :: 自</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: " Gentilly, at Gentilly...â€¦</t>
+          <t>L696: punctuation artifact: repeated periods :: " Gentilly, at Gentilly...…</t>
         </is>
       </c>
       <c r="Q17" s="1" t="inlineStr">
@@ -1927,7 +1927,7 @@
       <c r="R17" s="1" t="inlineStr"/>
       <c r="S17" s="1" t="inlineStr">
         <is>
-          <t>L1428: line starts with punctuation glued to text :: .secretary of the Municipality:</t>
+          <t>L1242: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • VIEWS ON THE</t>
         </is>
       </c>
       <c r="T17" s="1" t="inlineStr"/>
@@ -1961,14 +1961,10 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L438: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: from Montreal on articles for Exhibitionâ€”</t>
-        </is>
-      </c>
+          <t>L438: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1994,7 +1990,7 @@
       <c r="R18" s="1" t="inlineStr"/>
       <c r="S18" s="1" t="inlineStr">
         <is>
-          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
+          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
         </is>
       </c>
       <c r="T18" s="1" t="inlineStr"/>
@@ -2028,14 +2024,10 @@
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L447: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L416: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: approved by the Local Committeesâ€”will be</t>
-        </is>
-      </c>
+          <t>L503: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -2061,7 +2053,7 @@
       <c r="R19" s="1" t="inlineStr"/>
       <c r="S19" s="1" t="inlineStr">
         <is>
-          <t>L1586: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aFor (odd internal casing) :: aFor any further information, apply to</t>
+          <t>L1428: line starts with punctuation glued to text :: .secretary of the Municipality:</t>
         </is>
       </c>
       <c r="T19" s="1" t="inlineStr"/>
@@ -2091,14 +2083,10 @@
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�°</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L421: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To G. Lanigan, Esq., .â€” 84.30</t>
-        </is>
-      </c>
+          <t>L549: stray/suspicious non-ASCII glyph(s): U+7279 CJK UNIFIED IDEOGRAPH-7279 | isolated marker/symbol line :: 特</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -2124,7 +2112,7 @@
       <c r="R20" s="1" t="inlineStr"/>
       <c r="S20" s="1" t="inlineStr">
         <is>
-          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
+          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
         </is>
       </c>
       <c r="T20" s="1" t="inlineStr"/>
@@ -2154,14 +2142,10 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>L662: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: å…¬</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”|keeping, to examine, compare and stamp all</t>
-        </is>
-      </c>
+          <t>L554: stray/suspicious non-ASCII glyph(s): U+53F0 CJK UNIFIED IDEOGRAPH-53F0 | isolated marker/symbol line :: 台</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -2187,7 +2171,7 @@
       <c r="R21" s="1" t="inlineStr"/>
       <c r="S21" s="1" t="inlineStr">
         <is>
-          <t>L1657: line starts with punctuation glued to text | abbreviation/spacing may be garbled :: _____ Deputy C.C. C. Landrie, Charles</t>
+          <t>L1586: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aFor (odd internal casing) :: aFor any further information, apply to</t>
         </is>
       </c>
       <c r="T21" s="1" t="inlineStr"/>
@@ -2217,14 +2201,10 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: " Gentilly, at Gentilly...â€¦</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Becancour and Ste. Gertrude,</t>
-        </is>
-      </c>
+          <t>L568: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
@@ -2239,18 +2219,18 @@
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>L761: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: viere du Loup. . â€¦... 18th &amp; 19th "</t>
+          <t>L761: punctuation artifact: repeated periods :: viere du Loup. . …... 18th &amp; 19th "</t>
         </is>
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L172: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Salaries.........- â€” ......</t>
+          <t>L172: punctuation artifact: repeated periods :: Salaries.........- — ......</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
       <c r="S22" s="1" t="inlineStr">
         <is>
-          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
         </is>
       </c>
       <c r="T22" s="1" t="inlineStr"/>
@@ -2270,7 +2250,7 @@
       <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>L767: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): Yamachiche27th (letter/digit mix) :: â€œYamachiche, at Yamachiche27th &amp; 28thâ€œ</t>
+          <t>L767: suspicious token(s): Yamachiche27th (letter/digit mix) :: “Yamachiche, at Yamachiche27th &amp; 28th“</t>
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr">
@@ -2280,14 +2260,10 @@
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>L699: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L507: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Rivers Turf Club will be held at the Court.</t>
-        </is>
-      </c>
+          <t>L662: stray/suspicious non-ASCII glyph(s): U+516C CJK UNIFIED IDEOGRAPH-516C | isolated marker/symbol line :: 公</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
@@ -2302,7 +2278,7 @@
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>L765: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: at S. Barnab. ... 25th &amp; 26th â€œ</t>
+          <t>L765: punctuation artifact: repeated periods :: at S. Barnab. ... 25th &amp; 26th “</t>
         </is>
       </c>
       <c r="Q23" s="1" t="inlineStr">
@@ -2311,7 +2287,11 @@
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
+      <c r="S23" s="1" t="inlineStr">
+        <is>
+          <t>L1657: line starts with punctuation glued to text | abbreviation/spacing may be garbled :: _____ Deputy C.C. C. Landrie, Charles</t>
+        </is>
+      </c>
       <c r="T23" s="1" t="inlineStr"/>
       <c r="U23" s="1" t="inlineStr"/>
       <c r="V23" s="1" t="inlineStr"/>
@@ -2339,14 +2319,10 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�£</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L508: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: House on Monday next 9th inst, at 2 oâ€™clockI</t>
-        </is>
-      </c>
+          <t>L699: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -2370,7 +2346,11 @@
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
+      <c r="S24" s="1" t="inlineStr">
+        <is>
+          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+        </is>
+      </c>
       <c r="T24" s="1" t="inlineStr"/>
       <c r="U24" s="1" t="inlineStr"/>
       <c r="V24" s="1" t="inlineStr"/>
@@ -2398,14 +2378,10 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>L714: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 15th â€œ</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L538: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: 18. 2nd Ron Wolfstown 200 | who will be present in Montreal â‚¬ n the occa-</t>
-        </is>
-      </c>
+          <t>L703: stray/suspicious non-ASCII glyph(s): U+53E3 CJK UNIFIED IDEOGRAPH-53E3 | isolated marker/symbol line :: 口</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
@@ -2457,14 +2433,10 @@
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>L727: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 25th â€œ</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L539: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 19. â€¢. ** 200 sion; and the opportunity thus afforded to</t>
-        </is>
-      </c>
+          <t>L719: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
@@ -2511,19 +2483,15 @@
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>L1587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): AyImer (odd internal casing) :: the U. F. Coâ€™s: Office, AyImer, or on Board</t>
+          <t>L1587: suspicious token(s): AyImer (odd internal casing) :: the U. F. Co’s: Office, AyImer, or on Board</t>
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 30th â€œ</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L546: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 98-â€¢ " 200 Establishments, will use every effort to make</t>
-        </is>
-      </c>
+          <t>L742: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
@@ -2575,14 +2543,10 @@
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 5th â€œ</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L553: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: Â±7, " " 200 on or before the 15th day of July, and all such</t>
-        </is>
-      </c>
+          <t>L745: stray/suspicious non-ASCII glyph(s): U+5EFA CJK UNIFIED IDEOGRAPH-5EFA | isolated marker/symbol line :: 建</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
@@ -2630,14 +2594,10 @@
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>L747: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 7th â€œ</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: â€¢ ----------------articles must be delivered at the Exhibition</t>
-        </is>
-      </c>
+          <t>L749: stray/suspicious non-ASCII glyph(s): U+4E8B CJK UNIFIED IDEOGRAPH-4E8B | isolated marker/symbol line :: 事</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
@@ -2685,14 +2645,10 @@
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>L761: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: viere du Loup. . â€¦... 18th &amp; 19th "</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L560: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SENGERSâ€”</t>
-        </is>
-      </c>
+          <t>L775: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
@@ -2712,7 +2668,7 @@
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rehantâ€™s Liquor Licence,.... 512,00</t>
+          <t>L193: punctuation artifact: repeated periods :: rehant’s Liquor Licence,.... 512,00</t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2740,14 +2696,10 @@
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: at St. Leon.Â·Â·. 21st &amp; 22nd â€œ</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Arriving in Montreal,.........â€”7 A. M.</t>
-        </is>
-      </c>
+          <t>L831: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
@@ -2757,7 +2709,7 @@
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L304: symbol-only separator/garbage line :: 20"</t>
+          <t>L302: symbol-only separator/garbage line :: 200 —</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr">
@@ -2767,7 +2719,7 @@
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L194: punctuation artifact: repeated periods :: as Â« Rentes,.............58,66</t>
+          <t>L194: punctuation artifact: repeated periods :: as « Rentes,.............58,66</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2795,14 +2747,10 @@
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>L764: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: " St. Barnab Ã© &amp; sl. Paulin,</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L640: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Apply â€¢</t>
-        </is>
-      </c>
+          <t>L832: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
@@ -2812,7 +2760,7 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L316: symbol-only separator/garbage line :: 14.00</t>
+          <t>L304: symbol-only separator/garbage line :: 20"</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -2850,14 +2798,10 @@
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>L765: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: at S. Barnab. ... 25th &amp; 26th â€œ</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L646: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Montreal, 10 April. 1860 â€˜84</t>
-        </is>
-      </c>
+          <t>L833: stray/suspicious non-ASCII glyph(s): U+8B66 CJK UNIFIED IDEOGRAPH-8B66 | isolated marker/symbol line :: 警</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
@@ -2867,7 +2811,7 @@
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L318: symbol-only separator/garbage line :: 4-00</t>
+          <t>L316: symbol-only separator/garbage line :: 14.00</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -2877,7 +2821,7 @@
       </c>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>L196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: dlarâ€™s Licence,..........13,00</t>
+          <t>L196: punctuation artifact: repeated periods :: dlar’s Licence,..........13,00</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr"/>
@@ -2905,14 +2849,10 @@
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>L767: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): Yamachiche27th (letter/digit mix) :: â€œYamachiche, at Yamachiche27th &amp; 28thâ€œ</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: at station No. I, â€”..</t>
-        </is>
-      </c>
+          <t>L834: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
@@ -2922,7 +2862,7 @@
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L320: symbol-only separator/garbage line :: 4.00</t>
+          <t>L318: symbol-only separator/garbage line :: 4-00</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -2960,24 +2900,20 @@
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>L768: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L717: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 5â€™0</t>
-        </is>
-      </c>
+          <t>L868: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L106: symbol-only separator/garbage line :: $523, 451</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L322: symbol-only separator/garbage line :: 4.00</t>
+          <t>L320: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr">
@@ -3015,24 +2951,20 @@
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>L771: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L772: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 13th â€”</t>
-        </is>
-      </c>
+          <t>L889: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L106: symbol-only separator/garbage line :: $523, 451</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L324: symbol-only separator/garbage line :: 4.00</t>
+          <t>L322: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr">
@@ -3070,24 +3002,20 @@
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>L772: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 29th â€œ</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L778: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: 4 Grande RiviÃ¨re, at the Ferry</t>
-        </is>
-      </c>
+          <t>L919: stray/suspicious non-ASCII glyph(s): U+697C CJK UNIFIED IDEOGRAPH-697C | isolated marker/symbol line :: 楼</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L112: symbol-only separator/garbage line :: 1.00</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L326: symbol-only separator/garbage line :: $6375,09</t>
+          <t>L324: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -3125,24 +3053,20 @@
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>L775: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L825: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+          <t>L928: stray/suspicious non-ASCII glyph(s): U+6210 CJK UNIFIED IDEOGRAPH-6210 | isolated marker/symbol line :: 成</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: .</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L350: isolated marker/symbol line :: 30</t>
+          <t>L326: symbol-only separator/garbage line :: $6375,09</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr">
@@ -3180,24 +3104,20 @@
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>L777: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 4th â€œ</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢â€¢ St. Stanislas and St. Tite,</t>
-        </is>
-      </c>
+          <t>L1002: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L117: symbol-only separator/garbage line :: 4-00</t>
+          <t>L112: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L352: symbol-only separator/garbage line :: 31.00</t>
+          <t>L350: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr">
@@ -3235,24 +3155,20 @@
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr">
         <is>
-          <t>L831: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L873: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” at St. Stanislas.........28th &amp; 29th "</t>
-        </is>
-      </c>
+          <t>L1019: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L120: symbol-only separator/garbage line :: 4-00</t>
+          <t>L115: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L354: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 125,75</t>
+          <t>L352: symbol-only separator/garbage line :: 31.00</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr">
@@ -3290,24 +3206,20 @@
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr">
         <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+00A6 BROKEN BAR | isolated marker/symbol line :: è­¦</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Cash principle; and by this means will beâ€¢</t>
-        </is>
-      </c>
+          <t>L1058: stray/suspicious non-ASCII glyph(s): U+5730 CJK UNIFIED IDEOGRAPH-5730 | isolated marker/symbol line :: 地</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L122: symbol-only separator/garbage line :: 4.00</t>
+          <t>L117: symbol-only separator/garbage line :: 4-00</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L355: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...127.45</t>
+          <t>L354: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 125,75</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr">
@@ -3345,24 +3257,20 @@
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr">
         <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SENGERS â€”</t>
-        </is>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
+          <t>L1099: stray/suspicious non-ASCII glyph(s): U+5982 CJK UNIFIED IDEOGRAPH-5982 | isolated marker/symbol line :: 如</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L124: symbol-only separator/garbage line :: 4.00</t>
+          <t>L120: symbol-only separator/garbage line :: 4-00</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L357: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 113.27</t>
+          <t>L355: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...127.45</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr">
@@ -3400,24 +3308,20 @@
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr">
         <is>
-          <t>L919: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN :: æ¥¼</t>
-        </is>
-      </c>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L929: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 30th â€œ</t>
-        </is>
-      </c>
+          <t>L1121: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L126: symbol-only separator/garbage line :: 4.00</t>
+          <t>L122: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L359: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 125 15</t>
+          <t>L357: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 113.27</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr">
@@ -3455,24 +3359,20 @@
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>L928: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: æˆ�</t>
-        </is>
-      </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L931: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 4th â€œ</t>
-        </is>
-      </c>
+          <t>L1166: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。。</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L129: isolated marker/symbol line :: 1</t>
+          <t>L124: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L361: symbol-only separator/garbage line :: 491.62</t>
+          <t>L359: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 125 15</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr">
@@ -3510,24 +3410,20 @@
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr">
         <is>
-          <t>L955: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L947: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ing L E. Pacaudâ€™s insur</t>
-        </is>
-      </c>
+          <t>L1186: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: Mr. Alfred Beliale ， service</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: **</t>
+          <t>L126: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: 70</t>
+          <t>L361: symbol-only separator/garbage line :: 491.62</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr">
@@ -3565,24 +3461,20 @@
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>L956: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L965: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Expert Taxâ€™s occasion of</t>
-        </is>
-      </c>
+          <t>L1192: stray/suspicious non-ASCII glyph(s): U+8981 CJK UNIFIED IDEOGRAPH-8981 | isolated marker/symbol line :: 要</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L135: symbol-only separator/garbage line :: 84.30</t>
+          <t>L129: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L385: symbol-only separator/garbage line :: 75.00</t>
+          <t>L363: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr">
@@ -3620,24 +3512,20 @@
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr">
         <is>
-          <t>L973: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: corporation,â€¦.,-.</t>
-        </is>
-      </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: the Governorâ€™s visit,....</t>
-        </is>
-      </c>
+          <t>L1217: stray/suspicious non-ASCII glyph(s): U+96C5 CJK UNIFIED IDEOGRAPH-96C5 | isolated marker/symbol line :: 雅</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L137: symbol-only separator/garbage line :: 12.00</t>
+          <t>L131: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L387: symbol-only separator/garbage line :: 18.80</t>
+          <t>L385: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr">
@@ -3647,7 +3535,7 @@
       </c>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: St. Philipâ€™s Ward, ......</t>
+          <t>L238: punctuation artifact: repeated periods :: St. Philip’s Ward, ......</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3675,24 +3563,20 @@
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>L1002: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: â€˜or euregistration Doucetâ€™s</t>
-        </is>
-      </c>
+          <t>L1218: stray/suspicious non-ASCII glyph(s): U+6625 CJK UNIFIED IDEOGRAPH-6625 | isolated marker/symbol line :: 春</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L139: symbol-only separator/garbage line :: 5, 38</t>
+          <t>L135: symbol-only separator/garbage line :: 84.30</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: h</t>
+          <t>L387: symbol-only separator/garbage line :: 18.80</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr">
@@ -3730,24 +3614,20 @@
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr">
         <is>
-          <t>L1019: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L992: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Canada, to the Writ of Sumn</t>
-        </is>
-      </c>
+          <t>L1361: stray/suspicious non-ASCII glyph(s): U+5E7F CJK UNIFIED IDEOGRAPH-5E7F | isolated marker/symbol line :: 广</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L143: symbol-only separator/garbage line :: 491.62</t>
+          <t>L137: symbol-only separator/garbage line :: 12.00</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L510: symbol-only separator/garbage line :: 10.00</t>
+          <t>L397: isolated marker/symbol line :: h</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr">
@@ -3785,24 +3665,20 @@
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr">
         <is>
-          <t>L1099: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR | isolated marker/symbol line :: å¦‚</t>
-        </is>
-      </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1007: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: strongâ€™s fire, â€”........</t>
-        </is>
-      </c>
+          <t>L1433: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: follows: 一</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L146: symbol-only separator/garbage line :: 1, 78</t>
+          <t>L139: symbol-only separator/garbage line :: 5, 38</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L512: isolated marker/symbol line :: 800</t>
+          <t>L510: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr">
@@ -3836,24 +3712,20 @@
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr">
         <is>
-          <t>L1166: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ã€‚ã€‚</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1019: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: a MaskinongÃ©, at MaskinongÃ©11th &amp;</t>
-        </is>
-      </c>
+          <t>L1434: stray/suspicious non-ASCII glyph(s): U+5168 CJK UNIFIED IDEOGRAPH-5168 | isolated marker/symbol line :: 全</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L147: symbol-only separator/garbage line :: $48, 14</t>
+          <t>L143: symbol-only separator/garbage line :: 491.62</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L514: symbol-only separator/garbage line :: 4.00</t>
+          <t>L512: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -3883,24 +3755,20 @@
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr">
         <is>
-          <t>L1192: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: è¦�</t>
-        </is>
-      </c>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1024: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | line starts with punctuation glued to text :: ** RiviÃ¨re du Loup, at</t>
-        </is>
-      </c>
+          <t>L1475: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: P: Prescription ， with full directions Ufres</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L149: symbol-only separator/garbage line :: 6375.09</t>
+          <t>L146: symbol-only separator/garbage line :: 1, 78</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L516: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L514: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
@@ -3930,24 +3798,20 @@
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr">
         <is>
-          <t>L1218: stray/suspicious non-ASCII glyph(s): U+02DC SMALL TILDE, U+00A5 YEN SIGN | isolated marker/symbol line :: æ˜¥</t>
-        </is>
-      </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 44 St. LÃ©on, and Hunterstown,</t>
-        </is>
-      </c>
+          <t>L1489: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L151: symbol-only separator/garbage line :: 5.00</t>
+          <t>L147: symbol-only separator/garbage line :: $48, 14</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L518: symbol-only separator/garbage line :: 91.30</t>
+          <t>L516: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
@@ -3977,24 +3841,20 @@
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr">
         <is>
-          <t>L1226: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: i da Louis Godin.â€¦</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L1029: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. LÃ©on................ 21st &amp; 22nd "</t>
-        </is>
-      </c>
+          <t>L1494: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L153: symbol-only separator/garbage line :: 334.31</t>
+          <t>L149: symbol-only separator/garbage line :: 6375.09</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L528: symbol-only separator/garbage line :: 480.00</t>
+          <t>L518: symbol-only separator/garbage line :: 91.30</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
@@ -4024,24 +3884,20 @@
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr">
         <is>
-          <t>L1433: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: follows: ä¸€</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L1031: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: " St. BarnabÃ© &amp; St. Paulin,</t>
-        </is>
-      </c>
+          <t>L1513: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L154: isolated marker/symbol line :: 500</t>
+          <t>L151: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L580: symbol-only separator/garbage line :: 8.00</t>
+          <t>L528: symbol-only separator/garbage line :: 480.00</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
@@ -4071,24 +3927,20 @@
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr">
         <is>
-          <t>L1434: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | isolated marker/symbol line :: å…¨</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L1032: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. BarnabÃ©............25th &amp; 26th "</t>
-        </is>
-      </c>
+          <t>L1514: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: 2 ，</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L157: symbol-only separator/garbage line :: 116, 37</t>
+          <t>L153: symbol-only separator/garbage line :: 334.31</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L582: symbol-only separator/garbage line :: 5.00</t>
+          <t>L580: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
@@ -4118,24 +3970,20 @@
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr">
         <is>
-          <t>L1489: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L1046: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a St Etienne, at St Etienne 6th â€œ</t>
-        </is>
-      </c>
+          <t>L1536: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L158: symbol-only separator/garbage line :: 11.35</t>
+          <t>L154: isolated marker/symbol line :: 500</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L584: symbol-only separator/garbage line :: 8.00</t>
+          <t>L582: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
@@ -4163,26 +4011,18 @@
       <c r="G58" s="1" t="inlineStr"/>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>L1494: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L1113: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Kiernanâ€™s Commercial Buildings,</t>
-        </is>
-      </c>
+      <c r="J58" s="1" t="inlineStr"/>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L161: symbol-only separator/garbage line :: 523.45</t>
+          <t>L157: symbol-only separator/garbage line :: 116, 37</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L586: symbol-only separator/garbage line :: $3842.404</t>
+          <t>L584: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
@@ -4210,26 +4050,18 @@
       <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>L1513: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L1171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: follows:â€”</t>
-        </is>
-      </c>
+      <c r="J59" s="1" t="inlineStr"/>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L163: symbol-only separator/garbage line :: 86.30</t>
+          <t>L158: symbol-only separator/garbage line :: 11.35</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L611: isolated marker/symbol line :: 9</t>
+          <t>L586: symbol-only separator/garbage line :: $3842.404</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
@@ -4257,26 +4089,18 @@
       <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>L1516: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: To Mr. Rowan, old account.â€¦.</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L1228: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N. B.â€”Any person or persons who neglects</t>
-        </is>
-      </c>
+      <c r="J60" s="1" t="inlineStr"/>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L164: symbol-only separator/garbage line :: 1.50</t>
+          <t>L161: symbol-only separator/garbage line :: 523.45</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L613: symbol-only separator/garbage line :: 4 00</t>
+          <t>L611: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
@@ -4305,21 +4129,17 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1242: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ VIEWS ON THE</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L166: symbol-only separator/garbage line :: 127.331</t>
+          <t>L163: symbol-only separator/garbage line :: 86.30</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L614: isolated marker/symbol line :: 18</t>
+          <t>L613: symbol-only separator/garbage line :: 4 00</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
@@ -4348,21 +4168,17 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1282: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” CAPT. CUMING, 7 F MRS. FRANCIS PATTI BAINS, who</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L167: symbol-only separator/garbage line :: 46.00</t>
+          <t>L164: symbol-only separator/garbage line :: 1.50</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L616: symbol-only separator/garbage line :: 100.00</t>
+          <t>L614: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -4391,21 +4207,17 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1286: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: steamer OREGON at Chattsâ€™ Railroad, and tary to General Platt in 1813. , GRECO</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L169: symbol-only separator/garbage line :: 3.00</t>
+          <t>L166: symbol-only separator/garbage line :: 127.331</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L627: symbol-only separator/garbage line :: 6.90</t>
+          <t>L616: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -4434,21 +4246,17 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1290: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - â€” Brooklyn, Long Island, N. Y. who will be</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L170: isolated marker/symbol line :: 25</t>
+          <t>L167: symbol-only separator/garbage line :: 46.00</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L642: symbol-only separator/garbage line :: 24.00</t>
+          <t>L627: symbol-only separator/garbage line :: 6.90</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -4477,21 +4285,17 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: Arriving in Montreal at â€” 6.30 P.M.</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L171: isolated marker/symbol line :: 2</t>
+          <t>L169: symbol-only separator/garbage line :: 3.00</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L687: isolated marker/symbol line :: 50</t>
+          <t>L642: symbol-only separator/garbage line :: 24.00</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -4520,21 +4324,17 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1420: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: To Mr. Charles DugrÃ© ........</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L173: symbol-only separator/garbage line :: 491, 62</t>
+          <t>L170: isolated marker/symbol line :: 25</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L689: symbol-only separator/garbage line :: 4.05</t>
+          <t>L687: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -4563,21 +4363,17 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1430: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: I given to AimÃ© Panneton X ;</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L175: symbol-only separator/garbage line :: 91.00</t>
+          <t>L171: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L710: symbol-only separator/garbage line :: 62.00</t>
+          <t>L689: symbol-only separator/garbage line :: 4.05</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
@@ -4606,21 +4402,17 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L1436: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: ruing at 1 â€˜Clock [Sundays excepted,]</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L176: symbol-only separator/garbage line :: 86.30</t>
+          <t>L173: symbol-only separator/garbage line :: 491, 62</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L712: isolated marker/symbol line :: 15</t>
+          <t>L710: symbol-only separator/garbage line :: 62.00</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -4649,21 +4441,17 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L1466: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Chattâ€™s Railroad, and returning thence to</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L180: symbol-only separator/garbage line :: 2621, 15</t>
+          <t>L175: symbol-only separator/garbage line :: 91.00</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L714: symbol-only separator/garbage line :: 9.50</t>
+          <t>L712: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4692,21 +4480,17 @@
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L1478: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜HE SUBSCRIBER respectfully informs</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L182: symbol-only separator/garbage line :: 526, 41</t>
+          <t>L176: symbol-only separator/garbage line :: 86.30</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L716: isolated marker/symbol line :: n</t>
+          <t>L714: symbol-only separator/garbage line :: 9.50</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
@@ -4735,21 +4519,17 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L1509: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: Maurice Sayer damage â‚¬</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L184: symbol-only separator/garbage line :: 427271</t>
+          <t>L178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | symbol-only separator/garbage line :: 48€,00</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L728: symbol-only separator/garbage line :: 4 50</t>
+          <t>L716: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4778,21 +4558,17 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L1561: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: HE Subscriber, for several years a restâ€”</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L185: symbol-only separator/garbage line :: $6856, 23</t>
+          <t>L180: symbol-only separator/garbage line :: 2621, 15</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L730: isolated marker/symbol line :: 37</t>
+          <t>L717: symbol-only separator/garbage line :: 5’0</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4821,21 +4597,17 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L1563: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: simple vegetable remedyâ€”a sure Cure for</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L188: isolated marker/symbol line :: 7</t>
+          <t>L182: symbol-only separator/garbage line :: 526, 41</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L732: isolated marker/symbol line :: 90</t>
+          <t>L728: symbol-only separator/garbage line :: 4 50</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4864,21 +4636,17 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L1569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜othose who desire it, he will send the</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L209: isolated marker/symbol line :: 0</t>
+          <t>L184: symbol-only separator/garbage line :: 427271</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L749: isolated marker/symbol line :: A</t>
+          <t>L730: isolated marker/symbol line :: 37</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4907,21 +4675,17 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L1581: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | punctuation artifact: double/multiple hyphen :: tiae " -- Oregon,â€� 4- Snow Bird,â€� â€œ- Emerald,"</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L219: isolated marker/symbol line :: *</t>
+          <t>L185: symbol-only separator/garbage line :: $6856, 23</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L751: symbol-only separator/garbage line :: 40.00</t>
+          <t>L732: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -4950,21 +4714,17 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L1582: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: and ** Anne Sisson,â€� either by the Hour, by</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L221: isolated marker/symbol line :: e</t>
+          <t>L188: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L760: symbol-only separator/garbage line :: 1.00</t>
+          <t>L749: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -4993,21 +4753,17 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L1587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): AyImer (odd internal casing) :: the U. F. Coâ€™s: Office, AyImer, or on Board</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L223: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L209: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L762: isolated marker/symbol line :: 70</t>
+          <t>L751: symbol-only separator/garbage line :: 40.00</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -5036,27 +4792,23 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L1594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L225: isolated marker/symbol line :: 0</t>
+          <t>L219: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L764: symbol-only separator/garbage line :: 16 00</t>
+          <t>L760: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
       <c r="Q78" s="1" t="inlineStr">
         <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: â€¢ ----------------articles must be delivered at the Exhibition</t>
+          <t>L546: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: 98-• " 200 Establishments, will use every effort to make</t>
         </is>
       </c>
       <c r="R78" s="1" t="inlineStr"/>
@@ -5079,27 +4831,23 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L1612: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: For M. Aaron Hart (RiviÃ¨re du</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L233: isolated marker/symbol line :: N</t>
+          <t>L220: stray/suspicious non-ASCII glyph(s): U+4E91 CJK UNIFIED IDEOGRAPH-4E91 | isolated marker/symbol line :: 云</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L766: symbol-only separator/garbage line :: 32.00</t>
+          <t>L762: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
       <c r="Q79" s="1" t="inlineStr">
         <is>
-          <t>L562: punctuation artifact: repeated periods :: Will leave POINT LEVI at..........6 P. M.</t>
+          <t>L554: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: • ----------------articles must be delivered at the Exhibition</t>
         </is>
       </c>
       <c r="R79" s="1" t="inlineStr"/>
@@ -5122,27 +4870,23 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
       <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L1621: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 4 do.. ....</t>
-        </is>
-      </c>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L259: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L221: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L787: isolated marker/symbol line :: n</t>
+          <t>L764: symbol-only separator/garbage line :: 16 00</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
       <c r="Q80" s="1" t="inlineStr">
         <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Arriving in Montreal,.........â€”7 A. M.</t>
+          <t>L562: punctuation artifact: repeated periods :: Will leave POINT LEVI at..........6 P. M.</t>
         </is>
       </c>
       <c r="R80" s="1" t="inlineStr"/>
@@ -5165,27 +4909,23 @@
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
       <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L1681: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of Natureâ€™s simple herbs. Those desiring the</t>
-        </is>
-      </c>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L262: isolated marker/symbol line :: 93</t>
+          <t>L223: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L798: symbol-only separator/garbage line :: 50.00</t>
+          <t>L766: symbol-only separator/garbage line :: 32.00</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
       <c r="Q81" s="1" t="inlineStr">
         <is>
-          <t>L567: punctuation artifact: repeated periods :: TREAL...................-......5 P. M.</t>
+          <t>L564: punctuation artifact: repeated periods :: Arriving in Montreal,.........—7 A. M.</t>
         </is>
       </c>
       <c r="R81" s="1" t="inlineStr"/>
@@ -5213,18 +4953,18 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L267: isolated marker/symbol line :: 2</t>
+          <t>L225: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr">
         <is>
-          <t>L800: symbol-only separator/garbage line :: 3 37</t>
+          <t>L787: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P82" s="1" t="inlineStr"/>
       <c r="Q82" s="1" t="inlineStr">
         <is>
-          <t>L569: punctuation artifact: double/multiple hyphen | abbreviation/spacing may be garbled :: Arriving at Point Levi, -------5:30 A.M.</t>
+          <t>L567: punctuation artifact: repeated periods :: TREAL...................-......5 P. M.</t>
         </is>
       </c>
       <c r="R82" s="1" t="inlineStr"/>
@@ -5252,18 +4992,18 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L269: isolated marker/symbol line :: 39</t>
+          <t>L233: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr">
         <is>
-          <t>L802: isolated marker/symbol line :: 36</t>
+          <t>L798: symbol-only separator/garbage line :: 50.00</t>
         </is>
       </c>
       <c r="P83" s="1" t="inlineStr"/>
       <c r="Q83" s="1" t="inlineStr">
         <is>
-          <t>L598: punctuation artifact: repeated periods :: Interest,..............</t>
+          <t>L569: punctuation artifact: double/multiple hyphen | abbreviation/spacing may be garbled :: Arriving at Point Levi, -------5:30 A.M.</t>
         </is>
       </c>
       <c r="R83" s="1" t="inlineStr"/>
@@ -5291,18 +5031,18 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L270: symbol-only separator/garbage line :: 24.</t>
+          <t>L259: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr">
         <is>
-          <t>L825: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L800: symbol-only separator/garbage line :: 3 37</t>
         </is>
       </c>
       <c r="P84" s="1" t="inlineStr"/>
       <c r="Q84" s="1" t="inlineStr">
         <is>
-          <t>L606: punctuation artifact: repeated periods :: Costs. ............</t>
+          <t>L598: punctuation artifact: repeated periods :: Interest,..............</t>
         </is>
       </c>
       <c r="R84" s="1" t="inlineStr"/>
@@ -5330,18 +5070,18 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L271: isolated marker/symbol line :: 6</t>
+          <t>L262: isolated marker/symbol line :: 93</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr">
         <is>
-          <t>L827: symbol-only separator/garbage line :: 1.25</t>
+          <t>L802: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="P85" s="1" t="inlineStr"/>
       <c r="Q85" s="1" t="inlineStr">
         <is>
-          <t>L622: punctuation artifact: repeated periods :: the convenience of the purchasers..</t>
+          <t>L606: punctuation artifact: repeated periods :: Costs. ............</t>
         </is>
       </c>
       <c r="R85" s="1" t="inlineStr"/>
@@ -5369,18 +5109,18 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L275: isolated marker/symbol line :: 48</t>
+          <t>L267: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
-          <t>L829: symbol-only separator/garbage line :: 7.25</t>
+          <t>L825: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P86" s="1" t="inlineStr"/>
       <c r="Q86" s="1" t="inlineStr">
         <is>
-          <t>L649: punctuation artifact: repeated periods :: der, :........</t>
+          <t>L622: punctuation artifact: repeated periods :: the convenience of the purchasers..</t>
         </is>
       </c>
       <c r="R86" s="1" t="inlineStr"/>
@@ -5408,18 +5148,18 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L276: isolated marker/symbol line :: 200</t>
+          <t>L269: isolated marker/symbol line :: 39</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr">
         <is>
-          <t>L832: symbol-only separator/garbage line :: 2.00</t>
+          <t>L827: symbol-only separator/garbage line :: 1.25</t>
         </is>
       </c>
       <c r="P87" s="1" t="inlineStr"/>
       <c r="Q87" s="1" t="inlineStr">
         <is>
-          <t>L653: punctuation artifact: repeated periods; double/multiple hyphen :: Do. Do ..........-- .....</t>
+          <t>L649: punctuation artifact: repeated periods :: der, :........</t>
         </is>
       </c>
       <c r="R87" s="1" t="inlineStr"/>
@@ -5447,18 +5187,18 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L278: isolated marker/symbol line :: "</t>
+          <t>L270: symbol-only separator/garbage line :: 24.</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr">
         <is>
-          <t>L854: symbol-only separator/garbage line :: 5,21</t>
+          <t>L829: symbol-only separator/garbage line :: 7.25</t>
         </is>
       </c>
       <c r="P88" s="1" t="inlineStr"/>
       <c r="Q88" s="1" t="inlineStr">
         <is>
-          <t>L657: punctuation artifact: repeated periods :: No. 1 and No. 3, .......</t>
+          <t>L653: punctuation artifact: repeated periods; double/multiple hyphen :: Do. Do ..........-- .....</t>
         </is>
       </c>
       <c r="R88" s="1" t="inlineStr"/>
@@ -5486,18 +5226,18 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L279: isolated marker/symbol line :: " 6</t>
+          <t>L271: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr">
         <is>
-          <t>L856: symbol-only separator/garbage line :: 1.30</t>
+          <t>L832: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P89" s="1" t="inlineStr"/>
       <c r="Q89" s="1" t="inlineStr">
         <is>
-          <t>L659: punctuation artifact: double/multiple hyphen :: For wood sawing, --------</t>
+          <t>L657: punctuation artifact: repeated periods :: No. 1 and No. 3, .......</t>
         </is>
       </c>
       <c r="R89" s="1" t="inlineStr"/>
@@ -5525,18 +5265,18 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L280: isolated marker/symbol line :: 200</t>
+          <t>L272: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr">
         <is>
-          <t>L858: symbol-only separator/garbage line :: 21 00</t>
+          <t>L854: symbol-only separator/garbage line :: 5,21</t>
         </is>
       </c>
       <c r="P90" s="1" t="inlineStr"/>
       <c r="Q90" s="1" t="inlineStr">
         <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: at station No. I, â€”..</t>
+          <t>L659: punctuation artifact: double/multiple hyphen :: For wood sawing, --------</t>
         </is>
       </c>
       <c r="R90" s="1" t="inlineStr"/>
@@ -5564,18 +5304,18 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L281: symbol-only separator/garbage line :: 26,</t>
+          <t>L273: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr">
         <is>
-          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
+          <t>L856: symbol-only separator/garbage line :: 1.30</t>
         </is>
       </c>
       <c r="P91" s="1" t="inlineStr"/>
       <c r="Q91" s="1" t="inlineStr">
         <is>
-          <t>L755: punctuation artifact: repeated periods :: DSIN................Do</t>
+          <t>L673: punctuation artifact: repeated periods :: at station No. I, —..</t>
         </is>
       </c>
       <c r="R91" s="1" t="inlineStr"/>
@@ -5603,18 +5343,18 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L282: isolated marker/symbol line :: 66</t>
+          <t>L275: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr">
         <is>
-          <t>L913: isolated marker/symbol line :: C</t>
+          <t>L858: symbol-only separator/garbage line :: 21 00</t>
         </is>
       </c>
       <c r="P92" s="1" t="inlineStr"/>
       <c r="Q92" s="1" t="inlineStr">
         <is>
-          <t>L781: punctuation artifact: repeated periods :: Celestin ...................</t>
+          <t>L755: punctuation artifact: repeated periods :: DSIN................Do</t>
         </is>
       </c>
       <c r="R92" s="1" t="inlineStr"/>
@@ -5642,18 +5382,18 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L283: isolated marker/symbol line :: 68</t>
+          <t>L276: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr">
         <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
         </is>
       </c>
       <c r="P93" s="1" t="inlineStr"/>
       <c r="Q93" s="1" t="inlineStr">
         <is>
-          <t>L804: punctuation artifact: double/multiple hyphen :: ed, --------------------</t>
+          <t>L781: punctuation artifact: repeated periods :: Celestin ...................</t>
         </is>
       </c>
       <c r="R93" s="1" t="inlineStr"/>
@@ -5681,18 +5421,18 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L284: isolated marker/symbol line :: 210</t>
+          <t>L278: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr">
         <is>
-          <t>L916: symbol-only separator/garbage line :: 16 00</t>
+          <t>L913: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P94" s="1" t="inlineStr"/>
       <c r="Q94" s="1" t="inlineStr">
         <is>
-          <t>L806: punctuation artifact: repeated periods :: Poli-hing of the stove......</t>
+          <t>L804: punctuation artifact: double/multiple hyphen :: ed, --------------------</t>
         </is>
       </c>
       <c r="R94" s="1" t="inlineStr"/>
@@ -5720,18 +5460,18 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L286: isolated marker/symbol line :: 66</t>
+          <t>L279: isolated marker/symbol line :: " 6</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr">
         <is>
-          <t>L918: symbol-only separator/garbage line :: 1.35</t>
+          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="P95" s="1" t="inlineStr"/>
       <c r="Q95" s="1" t="inlineStr">
         <is>
-          <t>L809: punctuation artifact: double/multiple hyphen :: whole year, ------------</t>
+          <t>L806: punctuation artifact: repeated periods :: Poli-hing of the stove......</t>
         </is>
       </c>
       <c r="R95" s="1" t="inlineStr"/>
@@ -5759,18 +5499,18 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L287: isolated marker/symbol line :: " 4</t>
+          <t>L280: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr">
         <is>
-          <t>L920: isolated marker/symbol line :: 00</t>
+          <t>L916: symbol-only separator/garbage line :: 16 00</t>
         </is>
       </c>
       <c r="P96" s="1" t="inlineStr"/>
       <c r="Q96" s="1" t="inlineStr">
         <is>
-          <t>L810: punctuation artifact: repeated periods :: Postage...................- -</t>
+          <t>L809: punctuation artifact: double/multiple hyphen :: whole year, ------------</t>
         </is>
       </c>
       <c r="R96" s="1" t="inlineStr"/>
@@ -5798,18 +5538,18 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L288: isolated marker/symbol line :: 200</t>
+          <t>L281: symbol-only separator/garbage line :: 26,</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr">
         <is>
-          <t>L921: isolated marker/symbol line :: C.</t>
+          <t>L918: symbol-only separator/garbage line :: 1.35</t>
         </is>
       </c>
       <c r="P97" s="1" t="inlineStr"/>
       <c r="Q97" s="1" t="inlineStr">
         <is>
-          <t>L819: punctuation artifact: repeated periods :: eil, ..................</t>
+          <t>L810: punctuation artifact: repeated periods :: Postage...................- -</t>
         </is>
       </c>
       <c r="R97" s="1" t="inlineStr"/>
@@ -5837,18 +5577,18 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L289: symbol-only separator/garbage line :: 24,</t>
+          <t>L282: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr">
         <is>
-          <t>L998: isolated marker/symbol line :: C</t>
+          <t>L920: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P98" s="1" t="inlineStr"/>
       <c r="Q98" s="1" t="inlineStr">
         <is>
-          <t>L866: punctuation artifact: repeated periods :: Anne ..................... 21st &amp; 22nd "</t>
+          <t>L819: punctuation artifact: repeated periods :: eil, ..................</t>
         </is>
       </c>
       <c r="R98" s="1" t="inlineStr"/>
@@ -5876,18 +5616,18 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L290: isolated marker/symbol line :: 4</t>
+          <t>L283: isolated marker/symbol line :: 68</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr">
         <is>
-          <t>L1005: symbol-only separator/garbage line :: 1.00</t>
+          <t>L921: isolated marker/symbol line :: C.</t>
         </is>
       </c>
       <c r="P99" s="1" t="inlineStr"/>
       <c r="Q99" s="1" t="inlineStr">
         <is>
-          <t>L870: punctuation artifact: double/multiple hyphen :: " Batiscan, at Batiscan --25th "</t>
+          <t>L866: punctuation artifact: repeated periods :: Anne ..................... 21st &amp; 22nd "</t>
         </is>
       </c>
       <c r="R99" s="1" t="inlineStr"/>
@@ -5915,18 +5655,18 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L291: isolated marker/symbol line :: 6</t>
+          <t>L284: isolated marker/symbol line :: 210</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr">
         <is>
-          <t>L1052: isolated marker/symbol line :: 66</t>
+          <t>L998: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P100" s="1" t="inlineStr"/>
       <c r="Q100" s="1" t="inlineStr">
         <is>
-          <t>L873: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” at St. Stanislas.........28th &amp; 29th "</t>
+          <t>L870: punctuation artifact: double/multiple hyphen :: " Batiscan, at Batiscan --25th "</t>
         </is>
       </c>
       <c r="R100" s="1" t="inlineStr"/>
@@ -5954,18 +5694,18 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L292: isolated marker/symbol line :: 260</t>
+          <t>L286: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr">
         <is>
-          <t>L1054: isolated marker/symbol line :: 1"</t>
+          <t>L1005: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P101" s="1" t="inlineStr"/>
       <c r="Q101" s="1" t="inlineStr">
         <is>
-          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
+          <t>L873: punctuation artifact: repeated periods :: — at St. Stanislas.........28th &amp; 29th "</t>
         </is>
       </c>
       <c r="R101" s="1" t="inlineStr"/>
@@ -5993,18 +5733,18 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L293: isolated marker/symbol line :: .</t>
+          <t>L287: isolated marker/symbol line :: " 4</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr">
         <is>
-          <t>L1056: symbol-only separator/garbage line :: 2,00</t>
+          <t>L1052: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="P102" s="1" t="inlineStr"/>
       <c r="Q102" s="1" t="inlineStr">
         <is>
-          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
+          <t>L876: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------------------000 ----</t>
         </is>
       </c>
       <c r="R102" s="1" t="inlineStr"/>
@@ -6032,18 +5772,18 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L294: isolated marker/symbol line :: 1</t>
+          <t>L288: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr">
         <is>
-          <t>L1058: symbol-only separator/garbage line :: 5.00</t>
+          <t>L1054: isolated marker/symbol line :: 1"</t>
         </is>
       </c>
       <c r="P103" s="1" t="inlineStr"/>
       <c r="Q103" s="1" t="inlineStr">
         <is>
-          <t>L935: punctuation artifact: double/multiple hyphen :: -- Champlain, at Champlain</t>
+          <t>L934: punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: -* St. Narcisse, at St. Narcisse</t>
         </is>
       </c>
       <c r="R103" s="1" t="inlineStr"/>
@@ -6071,18 +5811,18 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L297: isolated marker/symbol line :: "</t>
+          <t>L289: symbol-only separator/garbage line :: 24,</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr">
         <is>
-          <t>L1092: symbol-only separator/garbage line :: 9.00</t>
+          <t>L1056: symbol-only separator/garbage line :: 2,00</t>
         </is>
       </c>
       <c r="P104" s="1" t="inlineStr"/>
       <c r="Q104" s="1" t="inlineStr">
         <is>
-          <t>L938: punctuation artifact: repeated periods :: Cap de la Magdelaine..</t>
+          <t>L935: punctuation artifact: double/multiple hyphen :: -- Champlain, at Champlain</t>
         </is>
       </c>
       <c r="R104" s="1" t="inlineStr"/>
@@ -6110,18 +5850,18 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L298: isolated marker/symbol line :: 66</t>
+          <t>L290: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr">
         <is>
-          <t>L1094: isolated marker/symbol line :: 39</t>
+          <t>L1058: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P105" s="1" t="inlineStr"/>
       <c r="Q105" s="1" t="inlineStr">
         <is>
-          <t>L950: punctuation artifact: repeated periods :: Auditor for two years, ..</t>
+          <t>L938: punctuation artifact: repeated periods :: Cap de la Magdelaine..</t>
         </is>
       </c>
       <c r="R105" s="1" t="inlineStr"/>
@@ -6149,18 +5889,18 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L299: isolated marker/symbol line :: 200</t>
+          <t>L291: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr">
         <is>
-          <t>L1095: symbol-only separator/garbage line :: 1.60</t>
+          <t>L1092: symbol-only separator/garbage line :: 9.00</t>
         </is>
       </c>
       <c r="P106" s="1" t="inlineStr"/>
       <c r="Q106" s="1" t="inlineStr">
         <is>
-          <t>L953: punctuation artifact: repeated periods :: ditor for two years,.....</t>
+          <t>L950: punctuation artifact: repeated periods :: Auditor for two years, ..</t>
         </is>
       </c>
       <c r="R106" s="1" t="inlineStr"/>
@@ -6188,18 +5928,18 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L301: isolated marker/symbol line :: 256</t>
+          <t>L292: isolated marker/symbol line :: 260</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr">
         <is>
-          <t>L1097: symbol-only separator/garbage line :: 7.87</t>
+          <t>L1094: isolated marker/symbol line :: 39</t>
         </is>
       </c>
       <c r="P107" s="1" t="inlineStr"/>
       <c r="Q107" s="1" t="inlineStr">
         <is>
-          <t>L958: punctuation artifact: repeated periods :: Hard ware, .............</t>
+          <t>L953: punctuation artifact: repeated periods :: ditor for two years,.....</t>
         </is>
       </c>
       <c r="R107" s="1" t="inlineStr"/>
@@ -6227,18 +5967,18 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L302: isolated marker/symbol line :: 00</t>
+          <t>L293: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr">
         <is>
-          <t>L1099: symbol-only separator/garbage line :: 4.80</t>
+          <t>L1095: symbol-only separator/garbage line :: 1.60</t>
         </is>
       </c>
       <c r="P108" s="1" t="inlineStr"/>
       <c r="Q108" s="1" t="inlineStr">
         <is>
-          <t>L960: punctuation artifact: repeated periods :: The Register office, ......</t>
+          <t>L958: punctuation artifact: repeated periods :: Hard ware, .............</t>
         </is>
       </c>
       <c r="R108" s="1" t="inlineStr"/>
@@ -6266,18 +6006,18 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L303: isolated marker/symbol line :: 64</t>
+          <t>L294: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr">
         <is>
-          <t>L1111: symbol-only separator/garbage line :: 334.31</t>
+          <t>L1097: symbol-only separator/garbage line :: 7.87</t>
         </is>
       </c>
       <c r="P109" s="1" t="inlineStr"/>
       <c r="Q109" s="1" t="inlineStr">
         <is>
-          <t>L962: punctuation artifact: repeated periods :: stall outside the hall.......</t>
+          <t>L960: punctuation artifact: repeated periods :: The Register office, ......</t>
         </is>
       </c>
       <c r="R109" s="1" t="inlineStr"/>
@@ -6305,18 +6045,18 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L304: isolated marker/symbol line :: 200</t>
+          <t>L297: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr">
         <is>
-          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
+          <t>L1099: symbol-only separator/garbage line :: 4.80</t>
         </is>
       </c>
       <c r="P110" s="1" t="inlineStr"/>
       <c r="Q110" s="1" t="inlineStr">
         <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: the Governorâ€™s visit,....</t>
+          <t>L962: punctuation artifact: repeated periods :: stall outside the hall.......</t>
         </is>
       </c>
       <c r="R110" s="1" t="inlineStr"/>
@@ -6344,18 +6084,18 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L307: isolated marker/symbol line :: .</t>
+          <t>L298: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr">
         <is>
-          <t>L1136: isolated marker/symbol line :: a-</t>
+          <t>L1111: symbol-only separator/garbage line :: 334.31</t>
         </is>
       </c>
       <c r="P111" s="1" t="inlineStr"/>
       <c r="Q111" s="1" t="inlineStr">
         <is>
-          <t>L972: punctuation artifact: repeated periods :: rendered, .............</t>
+          <t>L966: punctuation artifact: repeated periods :: the Governor’s visit,....</t>
         </is>
       </c>
       <c r="R111" s="1" t="inlineStr"/>
@@ -6383,18 +6123,18 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L308: isolated marker/symbol line :: 1</t>
+          <t>L299: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr">
         <is>
-          <t>L1138: isolated marker/symbol line :: 77</t>
+          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
         </is>
       </c>
       <c r="P112" s="1" t="inlineStr"/>
       <c r="Q112" s="1" t="inlineStr">
         <is>
-          <t>L976: punctuation artifact: repeated periods :: obligation, - ...........</t>
+          <t>L972: punctuation artifact: repeated periods :: rendered, .............</t>
         </is>
       </c>
       <c r="R112" s="1" t="inlineStr"/>
@@ -6422,18 +6162,18 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L309: isolated marker/symbol line :: 100</t>
+          <t>L301: isolated marker/symbol line :: 256</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr">
         <is>
-          <t>L1140: symbol-only separator/garbage line :: 002 1/2</t>
+          <t>L1136: isolated marker/symbol line :: a-</t>
         </is>
       </c>
       <c r="P113" s="1" t="inlineStr"/>
       <c r="Q113" s="1" t="inlineStr">
         <is>
-          <t>L1007: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: strongâ€™s fire, â€”........</t>
+          <t>L976: punctuation artifact: repeated periods :: obligation, - ...........</t>
         </is>
       </c>
       <c r="R113" s="1" t="inlineStr"/>
@@ -6461,18 +6201,18 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L310: isolated marker/symbol line :: 26</t>
+          <t>L302: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr">
         <is>
-          <t>L1142: symbol-only separator/garbage line :: 7,05</t>
+          <t>L1138: isolated marker/symbol line :: 77</t>
         </is>
       </c>
       <c r="P114" s="1" t="inlineStr"/>
       <c r="Q114" s="1" t="inlineStr">
         <is>
-          <t>L1020: punctuation artifact: repeated periods :: as St. Justin, at St. Justin..</t>
+          <t>L1007: punctuation artifact: repeated periods :: strong’s fire, —........</t>
         </is>
       </c>
       <c r="R114" s="1" t="inlineStr"/>
@@ -6500,18 +6240,18 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L311: isolated marker/symbol line :: 66</t>
+          <t>L303: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr">
         <is>
-          <t>L1144: symbol-only separator/garbage line :: 0,25</t>
+          <t>L1140: symbol-only separator/garbage line :: 002 1/2</t>
         </is>
       </c>
       <c r="P115" s="1" t="inlineStr"/>
       <c r="Q115" s="1" t="inlineStr">
         <is>
-          <t>L1026: punctuation artifact: repeated periods :: viere du Loop..........</t>
+          <t>L1020: punctuation artifact: repeated periods :: as St. Justin, at St. Justin..</t>
         </is>
       </c>
       <c r="R115" s="1" t="inlineStr"/>
@@ -6539,18 +6279,18 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L312: isolated marker/symbol line :: 4</t>
+          <t>L304: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr">
         <is>
-          <t>L1158: symbol-only separator/garbage line :: - 1.00</t>
+          <t>L1142: symbol-only separator/garbage line :: 7,05</t>
         </is>
       </c>
       <c r="P116" s="1" t="inlineStr"/>
       <c r="Q116" s="1" t="inlineStr">
         <is>
-          <t>L1029: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. LÃ©on................ 21st &amp; 22nd "</t>
+          <t>L1026: punctuation artifact: repeated periods :: viere du Loop..........</t>
         </is>
       </c>
       <c r="R116" s="1" t="inlineStr"/>
@@ -6578,18 +6318,18 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L313: isolated marker/symbol line :: 64</t>
+          <t>L307: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr">
         <is>
-          <t>L1190: isolated marker/symbol line :: -</t>
+          <t>L1144: symbol-only separator/garbage line :: 0,25</t>
         </is>
       </c>
       <c r="P117" s="1" t="inlineStr"/>
       <c r="Q117" s="1" t="inlineStr">
         <is>
-          <t>L1032: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: at St. BarnabÃ©............25th &amp; 26th "</t>
+          <t>L1029: punctuation artifact: repeated periods :: at St. Léon................ 21st &amp; 22nd "</t>
         </is>
       </c>
       <c r="R117" s="1" t="inlineStr"/>
@@ -6617,18 +6357,18 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L314: isolated marker/symbol line :: 100</t>
+          <t>L308: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr">
         <is>
-          <t>L1192: symbol-only separator/garbage line :: 618.60</t>
+          <t>L1158: symbol-only separator/garbage line :: - 1.00</t>
         </is>
       </c>
       <c r="P118" s="1" t="inlineStr"/>
       <c r="Q118" s="1" t="inlineStr">
         <is>
-          <t>L1036: punctuation artifact: double/multiple hyphen :: -- Pointe du Lac, at Pointe du</t>
+          <t>L1032: punctuation artifact: repeated periods :: at St. Barnabé............25th &amp; 26th "</t>
         </is>
       </c>
       <c r="R118" s="1" t="inlineStr"/>
@@ -6656,18 +6396,18 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L316: isolated marker/symbol line :: 200</t>
+          <t>L309: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr">
         <is>
-          <t>L1196: symbol-only separator/garbage line :: 5,38</t>
+          <t>L1190: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P119" s="1" t="inlineStr"/>
       <c r="Q119" s="1" t="inlineStr">
         <is>
-          <t>L1038: punctuation artifact: repeated periods :: Lac ...... 29th "</t>
+          <t>L1036: punctuation artifact: double/multiple hyphen :: -- Pointe du Lac, at Pointe du</t>
         </is>
       </c>
       <c r="R119" s="1" t="inlineStr"/>
@@ -6695,18 +6435,18 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L319: isolated marker/symbol line :: .</t>
+          <t>L310: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr">
         <is>
-          <t>L1197: isolated marker/symbol line :: 5</t>
+          <t>L1192: symbol-only separator/garbage line :: 618.60</t>
         </is>
       </c>
       <c r="P120" s="1" t="inlineStr"/>
       <c r="Q120" s="1" t="inlineStr">
         <is>
-          <t>L1042: punctuation artifact: repeated periods :: 46 Ste. Flore, at Ste. Flore.. 4th "</t>
+          <t>L1038: punctuation artifact: repeated periods :: Lac ...... 29th "</t>
         </is>
       </c>
       <c r="R120" s="1" t="inlineStr"/>
@@ -6734,18 +6474,18 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L320: isolated marker/symbol line :: .</t>
+          <t>L311: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr">
         <is>
-          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
+          <t>L1196: symbol-only separator/garbage line :: 5,38</t>
         </is>
       </c>
       <c r="P121" s="1" t="inlineStr"/>
       <c r="Q121" s="1" t="inlineStr">
         <is>
-          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
+          <t>L1042: punctuation artifact: repeated periods :: 46 Ste. Flore, at Ste. Flore.. 4th "</t>
         </is>
       </c>
       <c r="R121" s="1" t="inlineStr"/>
@@ -6773,18 +6513,18 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L321: isolated marker/symbol line :: 100</t>
+          <t>L312: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr">
         <is>
-          <t>L1218: symbol-only separator/garbage line :: 114.00</t>
+          <t>L1197: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="P122" s="1" t="inlineStr"/>
       <c r="Q122" s="1" t="inlineStr">
         <is>
-          <t>L1174: punctuation artifact: repeated periods | abbreviation/spacing may be garbled :: treal at ...............- - 10.30 A.M.</t>
+          <t>L1135: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: ------</t>
         </is>
       </c>
       <c r="R122" s="1" t="inlineStr"/>
@@ -6812,18 +6552,18 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L324: isolated marker/symbol line :: 9.</t>
+          <t>L313: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr">
         <is>
-          <t>L1220: symbol-only separator/garbage line :: 54.00</t>
+          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
         </is>
       </c>
       <c r="P123" s="1" t="inlineStr"/>
       <c r="Q123" s="1" t="inlineStr">
         <is>
-          <t>L1180: punctuation artifact: repeated periods :: mond) will leave Montreal at .. 5.00 P M.</t>
+          <t>L1174: punctuation artifact: repeated periods | abbreviation/spacing may be garbled :: treal at ...............- - 10.30 A.M.</t>
         </is>
       </c>
       <c r="R123" s="1" t="inlineStr"/>
@@ -6851,18 +6591,18 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L325: isolated marker/symbol line :: 46</t>
+          <t>L314: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr">
         <is>
-          <t>L1222: symbol-only separator/garbage line :: 1.39</t>
+          <t>L1218: symbol-only separator/garbage line :: 114.00</t>
         </is>
       </c>
       <c r="P124" s="1" t="inlineStr"/>
       <c r="Q124" s="1" t="inlineStr">
         <is>
-          <t>L1188: punctuation artifact: repeated periods :: Levi at.............-.,.-. 10.45 A M.</t>
+          <t>L1180: punctuation artifact: repeated periods :: mond) will leave Montreal at .. 5.00 P M.</t>
         </is>
       </c>
       <c r="R124" s="1" t="inlineStr"/>
@@ -6890,18 +6630,18 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L326: isolated marker/symbol line :: 48</t>
+          <t>L316: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr">
         <is>
-          <t>L1224: isolated marker/symbol line :: 240</t>
+          <t>L1220: symbol-only separator/garbage line :: 54.00</t>
         </is>
       </c>
       <c r="P125" s="1" t="inlineStr"/>
       <c r="Q125" s="1" t="inlineStr">
         <is>
-          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
+          <t>L1188: punctuation artifact: repeated periods :: Levi at.............-.,.-. 10.45 A M.</t>
         </is>
       </c>
       <c r="R125" s="1" t="inlineStr"/>
@@ -6929,18 +6669,18 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L328: isolated marker/symbol line :: 10</t>
+          <t>L319: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr">
         <is>
-          <t>L1257: symbol-only separator/garbage line :: 5,00</t>
+          <t>L1222: symbol-only separator/garbage line :: 1.39</t>
         </is>
       </c>
       <c r="P126" s="1" t="inlineStr"/>
       <c r="Q126" s="1" t="inlineStr">
         <is>
-          <t>L1201: punctuation artifact: repeated periods :: Market................</t>
+          <t>L1198: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 10,80</t>
         </is>
       </c>
       <c r="R126" s="1" t="inlineStr"/>
@@ -6968,18 +6708,18 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L333: isolated marker/symbol line :: .</t>
+          <t>L320: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr">
         <is>
-          <t>L1259: symbol-only separator/garbage line :: 7.50</t>
+          <t>L1224: isolated marker/symbol line :: 240</t>
         </is>
       </c>
       <c r="P127" s="1" t="inlineStr"/>
       <c r="Q127" s="1" t="inlineStr">
         <is>
-          <t>L1247: punctuation artifact: repeated periods :: for stalls ...........</t>
+          <t>L1201: punctuation artifact: repeated periods :: Market................</t>
         </is>
       </c>
       <c r="R127" s="1" t="inlineStr"/>
@@ -7007,18 +6747,18 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L334: isolated marker/symbol line :: 7</t>
+          <t>L321: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr">
         <is>
-          <t>L1260: symbol-only separator/garbage line :: 20,00</t>
+          <t>L1257: symbol-only separator/garbage line :: 5,00</t>
         </is>
       </c>
       <c r="P128" s="1" t="inlineStr"/>
       <c r="Q128" s="1" t="inlineStr">
         <is>
-          <t>L1249: punctuation artifact: repeated periods :: the large hall....</t>
+          <t>L1247: punctuation artifact: repeated periods :: for stalls ...........</t>
         </is>
       </c>
       <c r="R128" s="1" t="inlineStr"/>
@@ -7046,18 +6786,18 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L351: isolated marker/symbol line :: A</t>
+          <t>L323: stray/suspicious non-ASCII glyph(s): U+4E1C CJK UNIFIED IDEOGRAPH-4E1C | isolated marker/symbol line :: 东</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr">
         <is>
-          <t>L1262: symbol-only separator/garbage line :: 5,60</t>
+          <t>L1259: symbol-only separator/garbage line :: 7.50</t>
         </is>
       </c>
       <c r="P129" s="1" t="inlineStr"/>
       <c r="Q129" s="1" t="inlineStr">
         <is>
-          <t>L1298: punctuation artifact: repeated periods :: hall..</t>
+          <t>L1249: punctuation artifact: repeated periods :: the large hall....</t>
         </is>
       </c>
       <c r="R129" s="1" t="inlineStr"/>
@@ -7085,18 +6825,18 @@
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: $O</t>
+          <t>L324: isolated marker/symbol line :: 9.</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr">
         <is>
-          <t>L1264: symbol-only separator/garbage line :: 2,50</t>
+          <t>L1260: symbol-only separator/garbage line :: 20,00</t>
         </is>
       </c>
       <c r="P130" s="1" t="inlineStr"/>
       <c r="Q130" s="1" t="inlineStr">
         <is>
-          <t>L1304: punctuation artifact: repeated periods :: Louis Sarazin for iron work...</t>
+          <t>L1298: punctuation artifact: repeated periods :: hall..</t>
         </is>
       </c>
       <c r="R130" s="1" t="inlineStr"/>
@@ -7124,18 +6864,18 @@
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L364: isolated marker/symbol line :: 0</t>
+          <t>L325: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr">
         <is>
-          <t>L1266: symbol-only separator/garbage line :: 2,00</t>
+          <t>L1262: symbol-only separator/garbage line :: 5,60</t>
         </is>
       </c>
       <c r="P131" s="1" t="inlineStr"/>
       <c r="Q131" s="1" t="inlineStr">
         <is>
-          <t>L1306: punctuation artifact: repeated periods :: An accouunt for the little hall..</t>
+          <t>L1304: punctuation artifact: repeated periods :: Louis Sarazin for iron work...</t>
         </is>
       </c>
       <c r="R131" s="1" t="inlineStr"/>
@@ -7163,18 +6903,18 @@
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L366: isolated marker/symbol line :: D</t>
+          <t>L326: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr">
         <is>
-          <t>L1268: symbol-only separator/garbage line :: 1,12]</t>
+          <t>L1264: symbol-only separator/garbage line :: 2,50</t>
         </is>
       </c>
       <c r="P132" s="1" t="inlineStr"/>
       <c r="Q132" s="1" t="inlineStr">
         <is>
-          <t>L1308: punctuation artifact: repeated periods :: Mr. I ouis Lampron ........</t>
+          <t>L1306: punctuation artifact: repeated periods :: An accouunt for the little hall..</t>
         </is>
       </c>
       <c r="R132" s="1" t="inlineStr"/>
@@ -7202,18 +6942,18 @@
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L388: symbol-only separator/garbage line :: 1.4</t>
+          <t>L328: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr">
         <is>
-          <t>L1270: symbol-only separator/garbage line :: 11.25</t>
+          <t>L1266: symbol-only separator/garbage line :: 2,00</t>
         </is>
       </c>
       <c r="P133" s="1" t="inlineStr"/>
       <c r="Q133" s="1" t="inlineStr">
         <is>
-          <t>L1340: punctuation artifact: repeated periods :: Louis Sarazin work.......</t>
+          <t>L1308: punctuation artifact: repeated periods :: Mr. I ouis Lampron ........</t>
         </is>
       </c>
       <c r="R133" s="1" t="inlineStr"/>
@@ -7241,18 +6981,18 @@
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L390: isolated marker/symbol line :: W</t>
+          <t>L333: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr">
         <is>
-          <t>L1272: symbol-only separator/garbage line :: 4,511</t>
+          <t>L1268: symbol-only separator/garbage line :: 1,12]</t>
         </is>
       </c>
       <c r="P134" s="1" t="inlineStr"/>
       <c r="Q134" s="1" t="inlineStr">
         <is>
-          <t>L1371: punctuation artifact: repeated periods | suspicious token(s): 00A (letter/digit mix) :: Arriving at Montreal at..7 00A.M.</t>
+          <t>L1340: punctuation artifact: repeated periods :: Louis Sarazin work.......</t>
         </is>
       </c>
       <c r="R134" s="1" t="inlineStr"/>
@@ -7280,18 +7020,18 @@
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: %</t>
+          <t>L334: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr">
         <is>
-          <t>L1274: symbol-only separator/garbage line :: 12]</t>
+          <t>L1270: symbol-only separator/garbage line :: 11.25</t>
         </is>
       </c>
       <c r="P135" s="1" t="inlineStr"/>
       <c r="Q135" s="1" t="inlineStr">
         <is>
-          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
+          <t>L1371: punctuation artifact: repeated periods | suspicious token(s): 00A (letter/digit mix) :: Arriving at Montreal at..7 00A.M.</t>
         </is>
       </c>
       <c r="R135" s="1" t="inlineStr"/>
@@ -7319,18 +7059,18 @@
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L351: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr">
         <is>
-          <t>L1276: symbol-only separator/garbage line :: 7,10</t>
+          <t>L1272: symbol-only separator/garbage line :: 4,511</t>
         </is>
       </c>
       <c r="P136" s="1" t="inlineStr"/>
       <c r="Q136" s="1" t="inlineStr">
         <is>
-          <t>L1407: punctuation artifact: repeated periods :: Pompier............... .... 167,65</t>
+          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
         </is>
       </c>
       <c r="R136" s="1" t="inlineStr"/>
@@ -7358,18 +7098,18 @@
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L407: isolated marker/symbol line :: '</t>
+          <t>L363: isolated marker/symbol line :: $O</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr">
         <is>
-          <t>L1300: symbol-only separator/garbage line :: $1526.41</t>
+          <t>L1274: symbol-only separator/garbage line :: 12]</t>
         </is>
       </c>
       <c r="P137" s="1" t="inlineStr"/>
       <c r="Q137" s="1" t="inlineStr">
         <is>
-          <t>L1411: punctuation artifact: repeated periods :: To Mr. Louis Lampron .........</t>
+          <t>L1407: punctuation artifact: repeated periods :: Pompier............... .... 167,65</t>
         </is>
       </c>
       <c r="R137" s="1" t="inlineStr"/>
@@ -7397,18 +7137,18 @@
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L408: symbol-only separator/garbage line :: 30, 00</t>
+          <t>L364: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr">
         <is>
-          <t>L1307: isolated marker/symbol line :: .</t>
+          <t>L1276: symbol-only separator/garbage line :: 7,10</t>
         </is>
       </c>
       <c r="P138" s="1" t="inlineStr"/>
       <c r="Q138" s="1" t="inlineStr">
         <is>
-          <t>L1413: punctuation artifact: repeated periods :: To William McDougall Esq......</t>
+          <t>L1411: punctuation artifact: repeated periods :: To Mr. Louis Lampron .........</t>
         </is>
       </c>
       <c r="R138" s="1" t="inlineStr"/>
@@ -7436,18 +7176,18 @@
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L409: isolated marker/symbol line :: 1</t>
+          <t>L366: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr">
         <is>
-          <t>L1349: isolated marker/symbol line :: :s</t>
+          <t>L1300: symbol-only separator/garbage line :: $1526.41</t>
         </is>
       </c>
       <c r="P139" s="1" t="inlineStr"/>
       <c r="Q139" s="1" t="inlineStr">
         <is>
-          <t>L1416: punctuation artifact: repeated periods :: tracts).......................</t>
+          <t>L1413: punctuation artifact: repeated periods :: To William McDougall Esq......</t>
         </is>
       </c>
       <c r="R139" s="1" t="inlineStr"/>
@@ -7475,18 +7215,18 @@
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L410: symbol-only separator/garbage line :: 5, 00</t>
+          <t>L388: symbol-only separator/garbage line :: 1.4</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr">
         <is>
-          <t>L1359: symbol-only separator/garbage line :: $116,374</t>
+          <t>L1307: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="P140" s="1" t="inlineStr"/>
       <c r="Q140" s="1" t="inlineStr">
         <is>
-          <t>L1420: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: To Mr. Charles DugrÃ© ........</t>
+          <t>L1416: punctuation artifact: repeated periods :: tracts).......................</t>
         </is>
       </c>
       <c r="R140" s="1" t="inlineStr"/>
@@ -7514,18 +7254,18 @@
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L411: isolated marker/symbol line :: 75</t>
+          <t>L390: isolated marker/symbol line :: W</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr">
         <is>
-          <t>L1363: isolated marker/symbol line :: 0</t>
+          <t>L1349: isolated marker/symbol line :: :s</t>
         </is>
       </c>
       <c r="P141" s="1" t="inlineStr"/>
       <c r="Q141" s="1" t="inlineStr">
         <is>
-          <t>L1422: punctuation artifact: repeated periods :: To Mr. Jos. Dufresne ........</t>
+          <t>L1420: punctuation artifact: repeated periods :: To Mr. Charles Dugré ........</t>
         </is>
       </c>
       <c r="R141" s="1" t="inlineStr"/>
@@ -7553,18 +7293,18 @@
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L412: symbol-only separator/garbage line :: 36, 60</t>
+          <t>L397: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr">
         <is>
-          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
+          <t>L1359: symbol-only separator/garbage line :: $116,374</t>
         </is>
       </c>
       <c r="P142" s="1" t="inlineStr"/>
       <c r="Q142" s="1" t="inlineStr">
         <is>
-          <t>L1424: punctuation artifact: repeated periods :: To Mr. Rowan, old account ....</t>
+          <t>L1422: punctuation artifact: repeated periods :: To Mr. Jos. Dufresne ........</t>
         </is>
       </c>
       <c r="R142" s="1" t="inlineStr"/>
@@ -7592,18 +7332,18 @@
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L413: isolated marker/symbol line :: 6</t>
+          <t>L398: isolated marker/symbol line :: 《</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr">
         <is>
-          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
+          <t>L1363: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P143" s="1" t="inlineStr"/>
       <c r="Q143" s="1" t="inlineStr">
         <is>
-          <t>L1432: punctuation artifact: repeated periods :: I do. Louis Godin ........</t>
+          <t>L1424: punctuation artifact: repeated periods :: To Mr. Rowan, old account ....</t>
         </is>
       </c>
       <c r="R143" s="1" t="inlineStr"/>
@@ -7631,18 +7371,18 @@
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L414: symbol-only separator/garbage line :: 26.70</t>
+          <t>L406: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr">
         <is>
-          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
+          <t>L1398: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 523,75</t>
         </is>
       </c>
       <c r="P144" s="1" t="inlineStr"/>
       <c r="Q144" s="1" t="inlineStr">
         <is>
-          <t>L1434: punctuation artifact: repeated periods | suspicious token(s): ZephirinDuval (odd internal casing) :: I to ZephirinDuval.........</t>
+          <t>L1432: punctuation artifact: repeated periods :: I do. Louis Godin ........</t>
         </is>
       </c>
       <c r="R144" s="1" t="inlineStr"/>
@@ -7670,18 +7410,18 @@
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L415: symbol-only separator/garbage line :: 2.32</t>
+          <t>L407: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr">
         <is>
-          <t>L1490: isolated marker/symbol line :: 18</t>
+          <t>L1400: symbol-only separator/garbage line | line starts with punctuation glued to text :: ____1016,00</t>
         </is>
       </c>
       <c r="P145" s="1" t="inlineStr"/>
       <c r="Q145" s="1" t="inlineStr">
         <is>
-          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
+          <t>L1434: punctuation artifact: repeated periods | suspicious token(s): ZephirinDuval (odd internal casing) :: I to ZephirinDuval.........</t>
         </is>
       </c>
       <c r="R145" s="1" t="inlineStr"/>
@@ -7709,18 +7449,18 @@
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L417: isolated marker/symbol line :: 4</t>
+          <t>L408: symbol-only separator/garbage line :: 30, 00</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr">
         <is>
-          <t>L1492: symbol-only separator/garbage line :: 5,30</t>
+          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
         </is>
       </c>
       <c r="P146" s="1" t="inlineStr"/>
       <c r="Q146" s="1" t="inlineStr">
         <is>
-          <t>L1456: punctuation artifact: repeated periods :: winter roads ......</t>
+          <t>L1439: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -----1 ?</t>
         </is>
       </c>
       <c r="R146" s="1" t="inlineStr"/>
@@ -7748,18 +7488,18 @@
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
         <is>
-          <t>L418: symbol-only separator/garbage line :: 17.20</t>
+          <t>L409: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O147" s="1" t="inlineStr">
         <is>
-          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
+          <t>L1490: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P147" s="1" t="inlineStr"/>
       <c r="Q147" s="1" t="inlineStr">
         <is>
-          <t>L1458: punctuation artifact: repeated periods :: Louis Dargis .......</t>
+          <t>L1456: punctuation artifact: repeated periods :: winter roads ......</t>
         </is>
       </c>
       <c r="R147" s="1" t="inlineStr"/>
@@ -7787,18 +7527,18 @@
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
         <is>
-          <t>L419: isolated marker/symbol line :: Î”</t>
+          <t>L410: symbol-only separator/garbage line :: 5, 00</t>
         </is>
       </c>
       <c r="O148" s="1" t="inlineStr">
         <is>
-          <t>L1514: isolated marker/symbol line :: - 4</t>
+          <t>L1492: symbol-only separator/garbage line :: 5,30</t>
         </is>
       </c>
       <c r="P148" s="1" t="inlineStr"/>
       <c r="Q148" s="1" t="inlineStr">
         <is>
-          <t>L1503: punctuation artifact: repeated periods :: rent lot......</t>
+          <t>L1458: punctuation artifact: repeated periods :: Louis Dargis .......</t>
         </is>
       </c>
       <c r="R148" s="1" t="inlineStr"/>
@@ -7826,18 +7566,18 @@
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>L423: isolated marker/symbol line :: F</t>
+          <t>L411: isolated marker/symbol line :: 75</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr">
         <is>
-          <t>L1516: symbol-only separator/garbage line :: 11,37</t>
+          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
         </is>
       </c>
       <c r="P149" s="1" t="inlineStr"/>
       <c r="Q149" s="1" t="inlineStr">
         <is>
-          <t>L1507: punctuation artifact: repeated periods :: sioner Street. .......</t>
+          <t>L1503: punctuation artifact: repeated periods :: rent lot......</t>
         </is>
       </c>
       <c r="R149" s="1" t="inlineStr"/>
@@ -7865,18 +7605,18 @@
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
         <is>
-          <t>L424: isolated marker/symbol line :: 8</t>
+          <t>L412: symbol-only separator/garbage line :: 36, 60</t>
         </is>
       </c>
       <c r="O150" s="1" t="inlineStr">
         <is>
-          <t>L1518: symbol-only separator/garbage line :: 7,72</t>
+          <t>L1514: isolated marker/symbol line :: - 4</t>
         </is>
       </c>
       <c r="P150" s="1" t="inlineStr"/>
       <c r="Q150" s="1" t="inlineStr">
         <is>
-          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
+          <t>L1507: punctuation artifact: repeated periods :: sioner Street. .......</t>
         </is>
       </c>
       <c r="R150" s="1" t="inlineStr"/>
@@ -7904,18 +7644,18 @@
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
         <is>
-          <t>L425: isolated marker/symbol line :: 2</t>
+          <t>L413: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O151" s="1" t="inlineStr">
         <is>
-          <t>L1520: symbol-only separator/garbage line :: 140,00</t>
+          <t>L1516: symbol-only separator/garbage line :: 11,37</t>
         </is>
       </c>
       <c r="P151" s="1" t="inlineStr"/>
       <c r="Q151" s="1" t="inlineStr">
         <is>
-          <t>L1557: punctuation artifact: repeated periods :: &amp;c., &amp;c., &amp;c..</t>
+          <t>L1513: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 20,00</t>
         </is>
       </c>
       <c r="R151" s="1" t="inlineStr"/>
@@ -7943,18 +7683,18 @@
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
         <is>
-          <t>L427: symbol-only separator/garbage line :: 197.331</t>
+          <t>L414: symbol-only separator/garbage line :: 26.70</t>
         </is>
       </c>
       <c r="O152" s="1" t="inlineStr">
         <is>
-          <t>L1522: symbol-only separator/garbage line :: 4,20</t>
+          <t>L1518: symbol-only separator/garbage line :: 7,72</t>
         </is>
       </c>
       <c r="P152" s="1" t="inlineStr"/>
       <c r="Q152" s="1" t="inlineStr">
         <is>
-          <t>L1581: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | punctuation artifact: double/multiple hyphen :: tiae " -- Oregon,â€� 4- Snow Bird,â€� â€œ- Emerald,"</t>
+          <t>L1557: punctuation artifact: repeated periods :: &amp;c., &amp;c., &amp;c..</t>
         </is>
       </c>
       <c r="R152" s="1" t="inlineStr"/>
@@ -7982,18 +7722,18 @@
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
         <is>
-          <t>L428: symbol-only separator/garbage line :: $6856, 13</t>
+          <t>L415: symbol-only separator/garbage line :: 2.32</t>
         </is>
       </c>
       <c r="O153" s="1" t="inlineStr">
         <is>
-          <t>L1524: isolated marker/symbol line :: I</t>
+          <t>L1520: symbol-only separator/garbage line :: 140,00</t>
         </is>
       </c>
       <c r="P153" s="1" t="inlineStr"/>
       <c r="Q153" s="1" t="inlineStr">
         <is>
-          <t>L1601: punctuation artifact: repeated periods :: Coteau..............****......</t>
+          <t>L1581: punctuation artifact: double/multiple hyphen :: tiae " -- Oregon,” 4- Snow Bird,” “- Emerald,"</t>
         </is>
       </c>
       <c r="R153" s="1" t="inlineStr"/>
@@ -8021,18 +7761,18 @@
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
         <is>
-          <t>L431: symbol-only separator/garbage line :: 1906.30</t>
+          <t>L417: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O154" s="1" t="inlineStr">
         <is>
-          <t>L1590: isolated marker/symbol line :: :</t>
+          <t>L1522: symbol-only separator/garbage line :: 4,20</t>
         </is>
       </c>
       <c r="P154" s="1" t="inlineStr"/>
       <c r="Q154" s="1" t="inlineStr">
         <is>
-          <t>L1607: punctuation artifact: repeated periods :: The Inspector .................</t>
+          <t>L1601: punctuation artifact: repeated periods :: Coteau..............****......</t>
         </is>
       </c>
       <c r="R154" s="1" t="inlineStr"/>
@@ -8060,18 +7800,18 @@
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
         <is>
-          <t>L432: isolated marker/symbol line :: '</t>
+          <t>L418: symbol-only separator/garbage line :: 17.20</t>
         </is>
       </c>
       <c r="O155" s="1" t="inlineStr">
         <is>
-          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
+          <t>L1524: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P155" s="1" t="inlineStr"/>
       <c r="Q155" s="1" t="inlineStr">
         <is>
-          <t>L1609: punctuation artifact: repeated periods :: . Joseph Panneton winter roads..</t>
+          <t>L1607: punctuation artifact: repeated periods :: The Inspector .................</t>
         </is>
       </c>
       <c r="R155" s="1" t="inlineStr"/>
@@ -8099,18 +7839,18 @@
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>L434: isolated marker/symbol line :: â†’</t>
+          <t>L419: isolated marker/symbol line :: Δ</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr">
         <is>
-          <t>L1593: isolated marker/symbol line :: *</t>
+          <t>L1590: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P156" s="1" t="inlineStr"/>
       <c r="Q156" s="1" t="inlineStr">
         <is>
-          <t>L1610: punctuation artifact: repeated periods :: Mchel Boulard...............</t>
+          <t>L1609: punctuation artifact: repeated periods :: . Joseph Panneton winter roads..</t>
         </is>
       </c>
       <c r="R156" s="1" t="inlineStr"/>
@@ -8138,18 +7878,18 @@
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
         <is>
-          <t>L435: isolated marker/symbol line :: S</t>
+          <t>L422: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O157" s="1" t="inlineStr">
         <is>
-          <t>L1594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1591: symbol-only separator/garbage line | line starts with punctuation glued to text :: *38</t>
         </is>
       </c>
       <c r="P157" s="1" t="inlineStr"/>
       <c r="Q157" s="1" t="inlineStr">
         <is>
-          <t>L1613: punctuation artifact: repeated periods :: Leap) J......................</t>
+          <t>L1610: punctuation artifact: repeated periods :: Mchel Boulard...............</t>
         </is>
       </c>
       <c r="R157" s="1" t="inlineStr"/>
@@ -8177,18 +7917,18 @@
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>L437: symbol-only separator/garbage line :: 31.00</t>
+          <t>L423: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr">
         <is>
-          <t>L1596: symbol-only separator/garbage line :: 24,00</t>
+          <t>L1593: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P158" s="1" t="inlineStr"/>
       <c r="Q158" s="1" t="inlineStr">
         <is>
-          <t>L1615: punctuation artifact: repeated periods :: Joseph Giroux ...............</t>
+          <t>L1613: punctuation artifact: repeated periods :: Leap) J......................</t>
         </is>
       </c>
       <c r="R158" s="1" t="inlineStr"/>
@@ -8216,18 +7956,18 @@
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
         <is>
-          <t>L438: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L424: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O159" s="1" t="inlineStr">
         <is>
-          <t>L1597: isolated marker/symbol line :: 1</t>
+          <t>L1594: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P159" s="1" t="inlineStr"/>
       <c r="Q159" s="1" t="inlineStr">
         <is>
-          <t>L1616: punctuation artifact: repeated periods | suspicious token(s): LaBarre (odd internal casing) :: Deals to D, G. LaBarre Esq.,..</t>
+          <t>L1615: punctuation artifact: repeated periods :: Joseph Giroux ...............</t>
         </is>
       </c>
       <c r="R159" s="1" t="inlineStr"/>
@@ -8255,18 +7995,18 @@
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
         <is>
-          <t>L440: symbol-only separator/garbage line :: 125.75</t>
+          <t>L425: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O160" s="1" t="inlineStr">
         <is>
-          <t>L1635: isolated marker/symbol line :: n</t>
+          <t>L1596: symbol-only separator/garbage line :: 24,00</t>
         </is>
       </c>
       <c r="P160" s="1" t="inlineStr"/>
       <c r="Q160" s="1" t="inlineStr">
         <is>
-          <t>L1619: punctuation artifact: repeated periods :: toise of stone .............</t>
+          <t>L1616: punctuation artifact: repeated periods | suspicious token(s): LaBarre (odd internal casing) :: Deals to D, G. LaBarre Esq.,..</t>
         </is>
       </c>
       <c r="R160" s="1" t="inlineStr"/>
@@ -8294,18 +8034,18 @@
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>L441: symbol-only separator/garbage line :: 127.45</t>
+          <t>L427: symbol-only separator/garbage line :: 197.331</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr">
         <is>
-          <t>L1677: isolated marker/symbol line :: a.</t>
+          <t>L1597: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P161" s="1" t="inlineStr"/>
       <c r="Q161" s="1" t="inlineStr">
         <is>
-          <t>L1621: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoine DÃ©lorier 4 do.. ....</t>
+          <t>L1619: punctuation artifact: repeated periods :: toise of stone .............</t>
         </is>
       </c>
       <c r="R161" s="1" t="inlineStr"/>
@@ -8333,18 +8073,18 @@
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
         <is>
-          <t>L442: isolated marker/symbol line :: 92</t>
+          <t>L428: symbol-only separator/garbage line :: $6856, 13</t>
         </is>
       </c>
       <c r="O162" s="1" t="inlineStr">
         <is>
-          <t>L1679: symbol-only separator/garbage line :: 61,67</t>
+          <t>L1635: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P162" s="1" t="inlineStr"/>
       <c r="Q162" s="1" t="inlineStr">
         <is>
-          <t>L1623: punctuation artifact: repeated periods :: Moise Matton wood ......</t>
+          <t>L1621: punctuation artifact: repeated periods :: Antoine Délorier 4 do.. ....</t>
         </is>
       </c>
       <c r="R162" s="1" t="inlineStr"/>
@@ -8372,18 +8112,18 @@
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
         <is>
-          <t>L443: symbol-only separator/garbage line :: 113.97</t>
+          <t>L431: symbol-only separator/garbage line :: 1906.30</t>
         </is>
       </c>
       <c r="O163" s="1" t="inlineStr">
         <is>
-          <t>L1702: isolated marker/symbol line :: t</t>
+          <t>L1677: isolated marker/symbol line :: a.</t>
         </is>
       </c>
       <c r="P163" s="1" t="inlineStr"/>
       <c r="Q163" s="1" t="inlineStr">
         <is>
-          <t>L1634: punctuation artifact: repeated periods :: To Mr. Andrew Craik... 53,80</t>
+          <t>L1623: punctuation artifact: repeated periods :: Moise Matton wood ......</t>
         </is>
       </c>
       <c r="R163" s="1" t="inlineStr"/>
@@ -8411,16 +8151,20 @@
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
         <is>
-          <t>L444: symbol-only separator/garbage line :: 125 16</t>
+          <t>L432: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O164" s="1" t="inlineStr">
         <is>
-          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+          <t>L1679: symbol-only separator/garbage line :: 61,67</t>
         </is>
       </c>
       <c r="P164" s="1" t="inlineStr"/>
-      <c r="Q164" s="1" t="inlineStr"/>
+      <c r="Q164" s="1" t="inlineStr">
+        <is>
+          <t>L1634: punctuation artifact: repeated periods :: To Mr. Andrew Craik... 53,80</t>
+        </is>
+      </c>
       <c r="R164" s="1" t="inlineStr"/>
       <c r="S164" s="1" t="inlineStr"/>
       <c r="T164" s="1" t="inlineStr"/>
@@ -8446,12 +8190,12 @@
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr">
         <is>
-          <t>L445: isolated marker/symbol line :: 3</t>
+          <t>L434: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="O165" s="1" t="inlineStr">
         <is>
-          <t>L1706: isolated marker/symbol line :: -</t>
+          <t>L1694: isolated marker/symbol line :: 9°</t>
         </is>
       </c>
       <c r="P165" s="1" t="inlineStr"/>
@@ -8481,10 +8225,14 @@
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr">
         <is>
-          <t>L446: symbol-only separator/garbage line :: 10,</t>
-        </is>
-      </c>
-      <c r="O166" s="1" t="inlineStr"/>
+          <t>L435: isolated marker/symbol line :: S</t>
+        </is>
+      </c>
+      <c r="O166" s="1" t="inlineStr">
+        <is>
+          <t>L1702: isolated marker/symbol line :: t</t>
+        </is>
+      </c>
       <c r="P166" s="1" t="inlineStr"/>
       <c r="Q166" s="1" t="inlineStr"/>
       <c r="R166" s="1" t="inlineStr"/>
@@ -8512,10 +8260,14 @@
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr">
         <is>
-          <t>L448: isolated marker/symbol line :: " 6</t>
-        </is>
-      </c>
-      <c r="O167" s="1" t="inlineStr"/>
+          <t>L436: stray/suspicious non-ASCII glyph(s): U+81EA CJK UNIFIED IDEOGRAPH-81EA | isolated marker/symbol line :: 自</t>
+        </is>
+      </c>
+      <c r="O167" s="1" t="inlineStr">
+        <is>
+          <t>L1704: isolated marker/symbol line | line starts with punctuation glued to text :: .J</t>
+        </is>
+      </c>
       <c r="P167" s="1" t="inlineStr"/>
       <c r="Q167" s="1" t="inlineStr"/>
       <c r="R167" s="1" t="inlineStr"/>
@@ -8543,10 +8295,14 @@
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr">
         <is>
-          <t>L449: isolated marker/symbol line :: 20</t>
-        </is>
-      </c>
-      <c r="O168" s="1" t="inlineStr"/>
+          <t>L437: symbol-only separator/garbage line :: 31.00</t>
+        </is>
+      </c>
+      <c r="O168" s="1" t="inlineStr">
+        <is>
+          <t>L1706: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P168" s="1" t="inlineStr"/>
       <c r="Q168" s="1" t="inlineStr"/>
       <c r="R168" s="1" t="inlineStr"/>
@@ -8574,7 +8330,7 @@
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr">
         <is>
-          <t>L450: symbol-only separator/garbage line :: 15,</t>
+          <t>L438: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O169" s="1" t="inlineStr"/>
@@ -8605,7 +8361,7 @@
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr">
         <is>
-          <t>L451: isolated marker/symbol line :: 6</t>
+          <t>L440: symbol-only separator/garbage line :: 125.75</t>
         </is>
       </c>
       <c r="O170" s="1" t="inlineStr"/>
@@ -8636,7 +8392,7 @@
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr">
         <is>
-          <t>L452: symbol-only separator/garbage line :: 2.1</t>
+          <t>L441: symbol-only separator/garbage line :: 127.45</t>
         </is>
       </c>
       <c r="O171" s="1" t="inlineStr"/>
@@ -8667,7 +8423,7 @@
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr">
         <is>
-          <t>L454: isolated marker/symbol line :: 200</t>
+          <t>L442: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="O172" s="1" t="inlineStr"/>
@@ -8698,7 +8454,7 @@
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr">
         <is>
-          <t>L455: symbol-only separator/garbage line :: 91.30</t>
+          <t>L443: symbol-only separator/garbage line :: 113.97</t>
         </is>
       </c>
       <c r="O173" s="1" t="inlineStr"/>
@@ -8729,7 +8485,7 @@
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr">
         <is>
-          <t>L456: isolated marker/symbol line :: Ï‰</t>
+          <t>L444: symbol-only separator/garbage line :: 125 16</t>
         </is>
       </c>
       <c r="O174" s="1" t="inlineStr"/>
@@ -8760,7 +8516,7 @@
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr">
         <is>
-          <t>L459: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L445: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O175" s="1" t="inlineStr"/>
@@ -8791,7 +8547,7 @@
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr">
         <is>
-          <t>L463: symbol-only separator/garbage line :: 8.00</t>
+          <t>L446: symbol-only separator/garbage line :: 10,</t>
         </is>
       </c>
       <c r="O176" s="1" t="inlineStr"/>
@@ -8822,7 +8578,7 @@
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr">
         <is>
-          <t>L466: symbol-only separator/garbage line :: 5.00</t>
+          <t>L447: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O177" s="1" t="inlineStr"/>
@@ -8853,7 +8609,7 @@
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr">
         <is>
-          <t>L474: isolated marker/symbol line :: *</t>
+          <t>L448: isolated marker/symbol line :: " 6</t>
         </is>
       </c>
       <c r="O178" s="1" t="inlineStr"/>
@@ -8884,7 +8640,7 @@
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr">
         <is>
-          <t>L475: isolated marker/symbol line :: 400</t>
+          <t>L449: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O179" s="1" t="inlineStr"/>
@@ -8915,7 +8671,7 @@
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr">
         <is>
-          <t>L479: symbol-only separator/garbage line :: 100.00</t>
+          <t>L450: symbol-only separator/garbage line :: 15,</t>
         </is>
       </c>
       <c r="O180" s="1" t="inlineStr"/>
@@ -8946,7 +8702,7 @@
       <c r="M181" s="1" t="inlineStr"/>
       <c r="N181" s="1" t="inlineStr">
         <is>
-          <t>L483: symbol-only separator/garbage line :: 94.00</t>
+          <t>L451: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O181" s="1" t="inlineStr"/>
@@ -8977,7 +8733,7 @@
       <c r="M182" s="1" t="inlineStr"/>
       <c r="N182" s="1" t="inlineStr">
         <is>
-          <t>L485: isolated marker/symbol line :: "</t>
+          <t>L452: symbol-only separator/garbage line :: 2.1</t>
         </is>
       </c>
       <c r="O182" s="1" t="inlineStr"/>
@@ -9008,7 +8764,7 @@
       <c r="M183" s="1" t="inlineStr"/>
       <c r="N183" s="1" t="inlineStr">
         <is>
-          <t>L490: symbol-only separator/garbage line :: . 06</t>
+          <t>L454: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O183" s="1" t="inlineStr"/>
@@ -9039,7 +8795,7 @@
       <c r="M184" s="1" t="inlineStr"/>
       <c r="N184" s="1" t="inlineStr">
         <is>
-          <t>L500: isolated marker/symbol line :: S</t>
+          <t>L455: symbol-only separator/garbage line :: 91.30</t>
         </is>
       </c>
       <c r="O184" s="1" t="inlineStr"/>
@@ -9070,7 +8826,7 @@
       <c r="M185" s="1" t="inlineStr"/>
       <c r="N185" s="1" t="inlineStr">
         <is>
-          <t>L501: isolated marker/symbol line :: 100</t>
+          <t>L456: isolated marker/symbol line :: ω</t>
         </is>
       </c>
       <c r="O185" s="1" t="inlineStr"/>
@@ -9101,7 +8857,7 @@
       <c r="M186" s="1" t="inlineStr"/>
       <c r="N186" s="1" t="inlineStr">
         <is>
-          <t>L504: isolated marker/symbol line :: 2</t>
+          <t>L459: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="O186" s="1" t="inlineStr"/>
@@ -9132,7 +8888,7 @@
       <c r="M187" s="1" t="inlineStr"/>
       <c r="N187" s="1" t="inlineStr">
         <is>
-          <t>L513: isolated marker/symbol line :: 2</t>
+          <t>L463: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="O187" s="1" t="inlineStr"/>
@@ -9163,7 +8919,7 @@
       <c r="M188" s="1" t="inlineStr"/>
       <c r="N188" s="1" t="inlineStr">
         <is>
-          <t>L518: isolated marker/symbol line :: 1</t>
+          <t>L466: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O188" s="1" t="inlineStr"/>
@@ -9194,7 +8950,7 @@
       <c r="M189" s="1" t="inlineStr"/>
       <c r="N189" s="1" t="inlineStr">
         <is>
-          <t>L519: isolated marker/symbol line :: a</t>
+          <t>L474: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O189" s="1" t="inlineStr"/>
@@ -9225,7 +8981,7 @@
       <c r="M190" s="1" t="inlineStr"/>
       <c r="N190" s="1" t="inlineStr">
         <is>
-          <t>L521: symbol-only separator/garbage line :: 2.00</t>
+          <t>L475: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O190" s="1" t="inlineStr"/>
@@ -9256,7 +9012,7 @@
       <c r="M191" s="1" t="inlineStr"/>
       <c r="N191" s="1" t="inlineStr">
         <is>
-          <t>L526: symbol-only separator/garbage line :: 1600</t>
+          <t>L479: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="O191" s="1" t="inlineStr"/>
@@ -9287,7 +9043,7 @@
       <c r="M192" s="1" t="inlineStr"/>
       <c r="N192" s="1" t="inlineStr">
         <is>
-          <t>L531: isolated marker/symbol line :: 85</t>
+          <t>L483: symbol-only separator/garbage line :: 94.00</t>
         </is>
       </c>
       <c r="O192" s="1" t="inlineStr"/>
@@ -9318,7 +9074,7 @@
       <c r="M193" s="1" t="inlineStr"/>
       <c r="N193" s="1" t="inlineStr">
         <is>
-          <t>L536: symbol-only separator/garbage line :: 1.00</t>
+          <t>L485: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O193" s="1" t="inlineStr"/>
@@ -9349,7 +9105,7 @@
       <c r="M194" s="1" t="inlineStr"/>
       <c r="N194" s="1" t="inlineStr">
         <is>
-          <t>L539: symbol-only separator/garbage line :: 2.00</t>
+          <t>L490: symbol-only separator/garbage line :: . 06</t>
         </is>
       </c>
       <c r="O194" s="1" t="inlineStr"/>
@@ -9380,7 +9136,7 @@
       <c r="M195" s="1" t="inlineStr"/>
       <c r="N195" s="1" t="inlineStr">
         <is>
-          <t>L542: symbol-only separator/garbage line :: 5.00</t>
+          <t>L500: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O195" s="1" t="inlineStr"/>
@@ -9411,7 +9167,7 @@
       <c r="M196" s="1" t="inlineStr"/>
       <c r="N196" s="1" t="inlineStr">
         <is>
-          <t>L543: isolated marker/symbol line :: 0</t>
+          <t>L501: isolated marker/symbol line :: 100</t>
         </is>
       </c>
       <c r="O196" s="1" t="inlineStr"/>
@@ -9442,7 +9198,7 @@
       <c r="M197" s="1" t="inlineStr"/>
       <c r="N197" s="1" t="inlineStr">
         <is>
-          <t>L544: isolated marker/symbol line :: 4</t>
+          <t>L503: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
         </is>
       </c>
       <c r="O197" s="1" t="inlineStr"/>
@@ -9473,7 +9229,7 @@
       <c r="M198" s="1" t="inlineStr"/>
       <c r="N198" s="1" t="inlineStr">
         <is>
-          <t>L545: symbol-only separator/garbage line :: 30131</t>
+          <t>L504: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O198" s="1" t="inlineStr"/>
@@ -9504,7 +9260,7 @@
       <c r="M199" s="1" t="inlineStr"/>
       <c r="N199" s="1" t="inlineStr">
         <is>
-          <t>L550: isolated marker/symbol line :: 1</t>
+          <t>L513: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O199" s="1" t="inlineStr"/>
@@ -9535,7 +9291,7 @@
       <c r="M200" s="1" t="inlineStr"/>
       <c r="N200" s="1" t="inlineStr">
         <is>
-          <t>L552: isolated marker/symbol line :: $</t>
+          <t>L518: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O200" s="1" t="inlineStr"/>
@@ -9566,7 +9322,7 @@
       <c r="M201" s="1" t="inlineStr"/>
       <c r="N201" s="1" t="inlineStr">
         <is>
-          <t>L553: isolated marker/symbol line :: d</t>
+          <t>L519: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O201" s="1" t="inlineStr"/>
@@ -9597,7 +9353,7 @@
       <c r="M202" s="1" t="inlineStr"/>
       <c r="N202" s="1" t="inlineStr">
         <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�°</t>
+          <t>L521: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O202" s="1" t="inlineStr"/>
@@ -9628,7 +9384,7 @@
       <c r="M203" s="1" t="inlineStr"/>
       <c r="N203" s="1" t="inlineStr">
         <is>
-          <t>L555: isolated marker/symbol line :: 4</t>
+          <t>L526: symbol-only separator/garbage line :: 1600</t>
         </is>
       </c>
       <c r="O203" s="1" t="inlineStr"/>
@@ -9659,7 +9415,7 @@
       <c r="M204" s="1" t="inlineStr"/>
       <c r="N204" s="1" t="inlineStr">
         <is>
-          <t>L557: isolated marker/symbol line :: 13</t>
+          <t>L531: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="O204" s="1" t="inlineStr"/>
@@ -9690,7 +9446,7 @@
       <c r="M205" s="1" t="inlineStr"/>
       <c r="N205" s="1" t="inlineStr">
         <is>
-          <t>L558: symbol-only separator/garbage line :: 9555</t>
+          <t>L536: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O205" s="1" t="inlineStr"/>
@@ -9721,7 +9477,7 @@
       <c r="M206" s="1" t="inlineStr"/>
       <c r="N206" s="1" t="inlineStr">
         <is>
-          <t>L560: isolated marker/symbol line :: S</t>
+          <t>L539: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O206" s="1" t="inlineStr"/>
@@ -9752,7 +9508,7 @@
       <c r="M207" s="1" t="inlineStr"/>
       <c r="N207" s="1" t="inlineStr">
         <is>
-          <t>L561: isolated marker/symbol line :: 4</t>
+          <t>L542: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O207" s="1" t="inlineStr"/>
@@ -9783,7 +9539,7 @@
       <c r="M208" s="1" t="inlineStr"/>
       <c r="N208" s="1" t="inlineStr">
         <is>
-          <t>L567: isolated marker/symbol line :: 1</t>
+          <t>L543: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O208" s="1" t="inlineStr"/>
@@ -9814,7 +9570,7 @@
       <c r="M209" s="1" t="inlineStr"/>
       <c r="N209" s="1" t="inlineStr">
         <is>
-          <t>L570: isolated marker/symbol line :: 3</t>
+          <t>L544: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O209" s="1" t="inlineStr"/>
@@ -9845,7 +9601,7 @@
       <c r="M210" s="1" t="inlineStr"/>
       <c r="N210" s="1" t="inlineStr">
         <is>
-          <t>L572: symbol-only separator/garbage line :: 3, 00</t>
+          <t>L545: symbol-only separator/garbage line :: 30131</t>
         </is>
       </c>
       <c r="O210" s="1" t="inlineStr"/>
@@ -9876,7 +9632,7 @@
       <c r="M211" s="1" t="inlineStr"/>
       <c r="N211" s="1" t="inlineStr">
         <is>
-          <t>L574: symbol-only separator/garbage line :: $3542.404</t>
+          <t>L549: stray/suspicious non-ASCII glyph(s): U+7279 CJK UNIFIED IDEOGRAPH-7279 | isolated marker/symbol line :: 特</t>
         </is>
       </c>
       <c r="O211" s="1" t="inlineStr"/>
@@ -9907,7 +9663,7 @@
       <c r="M212" s="1" t="inlineStr"/>
       <c r="N212" s="1" t="inlineStr">
         <is>
-          <t>L575: symbol-only separator/garbage line :: 02.00</t>
+          <t>L550: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O212" s="1" t="inlineStr"/>
@@ -9938,7 +9694,7 @@
       <c r="M213" s="1" t="inlineStr"/>
       <c r="N213" s="1" t="inlineStr">
         <is>
-          <t>L576: isolated marker/symbol line :: 22</t>
+          <t>L552: isolated marker/symbol line :: $</t>
         </is>
       </c>
       <c r="O213" s="1" t="inlineStr"/>
@@ -9969,7 +9725,7 @@
       <c r="M214" s="1" t="inlineStr"/>
       <c r="N214" s="1" t="inlineStr">
         <is>
-          <t>L577: isolated marker/symbol line :: 00</t>
+          <t>L553: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O214" s="1" t="inlineStr"/>
@@ -10000,7 +9756,7 @@
       <c r="M215" s="1" t="inlineStr"/>
       <c r="N215" s="1" t="inlineStr">
         <is>
-          <t>L578: isolated marker/symbol line :: 15</t>
+          <t>L554: stray/suspicious non-ASCII glyph(s): U+53F0 CJK UNIFIED IDEOGRAPH-53F0 | isolated marker/symbol line :: 台</t>
         </is>
       </c>
       <c r="O215" s="1" t="inlineStr"/>
@@ -10031,7 +9787,7 @@
       <c r="M216" s="1" t="inlineStr"/>
       <c r="N216" s="1" t="inlineStr">
         <is>
-          <t>L579: symbol-only separator/garbage line :: 9.50</t>
+          <t>L555: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O216" s="1" t="inlineStr"/>
@@ -10062,7 +9818,7 @@
       <c r="M217" s="1" t="inlineStr"/>
       <c r="N217" s="1" t="inlineStr">
         <is>
-          <t>L580: isolated marker/symbol line :: e</t>
+          <t>L557: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="O217" s="1" t="inlineStr"/>
@@ -10093,7 +9849,7 @@
       <c r="M218" s="1" t="inlineStr"/>
       <c r="N218" s="1" t="inlineStr">
         <is>
-          <t>L586: isolated marker/symbol line :: A</t>
+          <t>L558: symbol-only separator/garbage line :: 9555</t>
         </is>
       </c>
       <c r="O218" s="1" t="inlineStr"/>
@@ -10124,7 +9880,7 @@
       <c r="M219" s="1" t="inlineStr"/>
       <c r="N219" s="1" t="inlineStr">
         <is>
-          <t>L600: isolated marker/symbol line :: -</t>
+          <t>L560: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O219" s="1" t="inlineStr"/>
@@ -10155,7 +9911,7 @@
       <c r="M220" s="1" t="inlineStr"/>
       <c r="N220" s="1" t="inlineStr">
         <is>
-          <t>L601: isolated marker/symbol line :: .</t>
+          <t>L561: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O220" s="1" t="inlineStr"/>
@@ -10186,7 +9942,7 @@
       <c r="M221" s="1" t="inlineStr"/>
       <c r="N221" s="1" t="inlineStr">
         <is>
-          <t>L603: isolated marker/symbol line :: E</t>
+          <t>L567: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O221" s="1" t="inlineStr"/>
@@ -10217,7 +9973,7 @@
       <c r="M222" s="1" t="inlineStr"/>
       <c r="N222" s="1" t="inlineStr">
         <is>
-          <t>L611: isolated marker/symbol line :: 337</t>
+          <t>L568: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O222" s="1" t="inlineStr"/>
@@ -10248,7 +10004,7 @@
       <c r="M223" s="1" t="inlineStr"/>
       <c r="N223" s="1" t="inlineStr">
         <is>
-          <t>L612: isolated marker/symbol line :: 3</t>
+          <t>L570: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O223" s="1" t="inlineStr"/>
@@ -10279,7 +10035,7 @@
       <c r="M224" s="1" t="inlineStr"/>
       <c r="N224" s="1" t="inlineStr">
         <is>
-          <t>L613: isolated marker/symbol line :: 3</t>
+          <t>L572: symbol-only separator/garbage line :: 3, 00</t>
         </is>
       </c>
       <c r="O224" s="1" t="inlineStr"/>
@@ -10310,7 +10066,7 @@
       <c r="M225" s="1" t="inlineStr"/>
       <c r="N225" s="1" t="inlineStr">
         <is>
-          <t>L615: isolated marker/symbol line :: 36</t>
+          <t>L574: symbol-only separator/garbage line :: $3542.404</t>
         </is>
       </c>
       <c r="O225" s="1" t="inlineStr"/>
@@ -10341,7 +10097,7 @@
       <c r="M226" s="1" t="inlineStr"/>
       <c r="N226" s="1" t="inlineStr">
         <is>
-          <t>L619: symbol-only separator/garbage line :: 5.91</t>
+          <t>L575: symbol-only separator/garbage line :: 02.00</t>
         </is>
       </c>
       <c r="O226" s="1" t="inlineStr"/>
@@ -10372,7 +10128,7 @@
       <c r="M227" s="1" t="inlineStr"/>
       <c r="N227" s="1" t="inlineStr">
         <is>
-          <t>L621: symbol-only separator/garbage line :: 1.30</t>
+          <t>L576: isolated marker/symbol line :: 22</t>
         </is>
       </c>
       <c r="O227" s="1" t="inlineStr"/>
@@ -10403,7 +10159,7 @@
       <c r="M228" s="1" t="inlineStr"/>
       <c r="N228" s="1" t="inlineStr">
         <is>
-          <t>L623: isolated marker/symbol line :: r,</t>
+          <t>L577: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O228" s="1" t="inlineStr"/>
@@ -10434,7 +10190,7 @@
       <c r="M229" s="1" t="inlineStr"/>
       <c r="N229" s="1" t="inlineStr">
         <is>
-          <t>L626: isolated marker/symbol line :: 7</t>
+          <t>L578: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="O229" s="1" t="inlineStr"/>
@@ -10465,7 +10221,7 @@
       <c r="M230" s="1" t="inlineStr"/>
       <c r="N230" s="1" t="inlineStr">
         <is>
-          <t>L629: symbol-only separator/garbage line :: 24.75</t>
+          <t>L579: symbol-only separator/garbage line :: 9.50</t>
         </is>
       </c>
       <c r="O230" s="1" t="inlineStr"/>
@@ -10496,7 +10252,7 @@
       <c r="M231" s="1" t="inlineStr"/>
       <c r="N231" s="1" t="inlineStr">
         <is>
-          <t>L633: isolated marker/symbol line :: 450</t>
+          <t>L580: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O231" s="1" t="inlineStr"/>
@@ -10527,7 +10283,7 @@
       <c r="M232" s="1" t="inlineStr"/>
       <c r="N232" s="1" t="inlineStr">
         <is>
-          <t>L634: isolated marker/symbol line :: 0</t>
+          <t>L586: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O232" s="1" t="inlineStr"/>
@@ -10558,7 +10314,7 @@
       <c r="M233" s="1" t="inlineStr"/>
       <c r="N233" s="1" t="inlineStr">
         <is>
-          <t>L638: symbol-only separator/garbage line :: 3.00</t>
+          <t>L600: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O233" s="1" t="inlineStr"/>
@@ -10589,7 +10345,7 @@
       <c r="M234" s="1" t="inlineStr"/>
       <c r="N234" s="1" t="inlineStr">
         <is>
-          <t>L641: symbol-only separator/garbage line :: 3900</t>
+          <t>L601: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O234" s="1" t="inlineStr"/>
@@ -10620,7 +10376,7 @@
       <c r="M235" s="1" t="inlineStr"/>
       <c r="N235" s="1" t="inlineStr">
         <is>
-          <t>L642: isolated marker/symbol line :: 39</t>
+          <t>L603: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O235" s="1" t="inlineStr"/>
@@ -10651,7 +10407,7 @@
       <c r="M236" s="1" t="inlineStr"/>
       <c r="N236" s="1" t="inlineStr">
         <is>
-          <t>L643: isolated marker/symbol line :: 00</t>
+          <t>L611: isolated marker/symbol line :: 337</t>
         </is>
       </c>
       <c r="O236" s="1" t="inlineStr"/>
@@ -10682,7 +10438,7 @@
       <c r="M237" s="1" t="inlineStr"/>
       <c r="N237" s="1" t="inlineStr">
         <is>
-          <t>L646: symbol-only separator/garbage line :: 39.00</t>
+          <t>L612: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O237" s="1" t="inlineStr"/>
@@ -10713,7 +10469,7 @@
       <c r="M238" s="1" t="inlineStr"/>
       <c r="N238" s="1" t="inlineStr">
         <is>
-          <t>L648: isolated marker/symbol line :: 3</t>
+          <t>L613: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O238" s="1" t="inlineStr"/>
@@ -10744,7 +10500,7 @@
       <c r="M239" s="1" t="inlineStr"/>
       <c r="N239" s="1" t="inlineStr">
         <is>
-          <t>L649: isolated marker/symbol line :: 1</t>
+          <t>L615: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="O239" s="1" t="inlineStr"/>
@@ -10775,7 +10531,7 @@
       <c r="M240" s="1" t="inlineStr"/>
       <c r="N240" s="1" t="inlineStr">
         <is>
-          <t>L650: symbol-only separator/garbage line :: 1.60</t>
+          <t>L619: symbol-only separator/garbage line :: 5.91</t>
         </is>
       </c>
       <c r="O240" s="1" t="inlineStr"/>
@@ -10806,7 +10562,7 @@
       <c r="M241" s="1" t="inlineStr"/>
       <c r="N241" s="1" t="inlineStr">
         <is>
-          <t>L653: symbol-only separator/garbage line :: 7.87</t>
+          <t>L621: symbol-only separator/garbage line :: 1.30</t>
         </is>
       </c>
       <c r="O241" s="1" t="inlineStr"/>
@@ -10837,7 +10593,7 @@
       <c r="M242" s="1" t="inlineStr"/>
       <c r="N242" s="1" t="inlineStr">
         <is>
-          <t>L654: symbol-only separator/garbage line :: 7.07</t>
+          <t>L623: isolated marker/symbol line :: r,</t>
         </is>
       </c>
       <c r="O242" s="1" t="inlineStr"/>
@@ -10868,7 +10624,7 @@
       <c r="M243" s="1" t="inlineStr"/>
       <c r="N243" s="1" t="inlineStr">
         <is>
-          <t>L656: symbol-only separator/garbage line :: 4.50</t>
+          <t>L626: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O243" s="1" t="inlineStr"/>
@@ -10899,7 +10655,7 @@
       <c r="M244" s="1" t="inlineStr"/>
       <c r="N244" s="1" t="inlineStr">
         <is>
-          <t>L662: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: å…¬</t>
+          <t>L629: symbol-only separator/garbage line :: 24.75</t>
         </is>
       </c>
       <c r="O244" s="1" t="inlineStr"/>
@@ -10930,7 +10686,7 @@
       <c r="M245" s="1" t="inlineStr"/>
       <c r="N245" s="1" t="inlineStr">
         <is>
-          <t>L663: isolated marker/symbol line :: A</t>
+          <t>L633: isolated marker/symbol line :: 450</t>
         </is>
       </c>
       <c r="O245" s="1" t="inlineStr"/>
@@ -10961,7 +10717,7 @@
       <c r="M246" s="1" t="inlineStr"/>
       <c r="N246" s="1" t="inlineStr">
         <is>
-          <t>L665: symbol-only separator/garbage line :: 618.60</t>
+          <t>L634: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O246" s="1" t="inlineStr"/>
@@ -10992,7 +10748,7 @@
       <c r="M247" s="1" t="inlineStr"/>
       <c r="N247" s="1" t="inlineStr">
         <is>
-          <t>L668: isolated marker/symbol line :: Y</t>
+          <t>L638: symbol-only separator/garbage line :: 3.00</t>
         </is>
       </c>
       <c r="O247" s="1" t="inlineStr"/>
@@ -11023,7 +10779,7 @@
       <c r="M248" s="1" t="inlineStr"/>
       <c r="N248" s="1" t="inlineStr">
         <is>
-          <t>L669: isolated marker/symbol line :: 1</t>
+          <t>L641: symbol-only separator/garbage line :: 3900</t>
         </is>
       </c>
       <c r="O248" s="1" t="inlineStr"/>
@@ -11054,7 +10810,7 @@
       <c r="M249" s="1" t="inlineStr"/>
       <c r="N249" s="1" t="inlineStr">
         <is>
-          <t>L697: isolated marker/symbol line :: 4</t>
+          <t>L642: isolated marker/symbol line :: 39</t>
         </is>
       </c>
       <c r="O249" s="1" t="inlineStr"/>
@@ -11085,7 +10841,7 @@
       <c r="M250" s="1" t="inlineStr"/>
       <c r="N250" s="1" t="inlineStr">
         <is>
-          <t>L699: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L643: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O250" s="1" t="inlineStr"/>
@@ -11116,7 +10872,7 @@
       <c r="M251" s="1" t="inlineStr"/>
       <c r="N251" s="1" t="inlineStr">
         <is>
-          <t>L700: isolated marker/symbol line :: "</t>
+          <t>L646: symbol-only separator/garbage line :: 39.00</t>
         </is>
       </c>
       <c r="O251" s="1" t="inlineStr"/>
@@ -11147,7 +10903,7 @@
       <c r="M252" s="1" t="inlineStr"/>
       <c r="N252" s="1" t="inlineStr">
         <is>
-          <t>L701: isolated marker/symbol line :: 0</t>
+          <t>L648: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O252" s="1" t="inlineStr"/>
@@ -11178,7 +10934,7 @@
       <c r="M253" s="1" t="inlineStr"/>
       <c r="N253" s="1" t="inlineStr">
         <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å�£</t>
+          <t>L649: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O253" s="1" t="inlineStr"/>
@@ -11209,7 +10965,7 @@
       <c r="M254" s="1" t="inlineStr"/>
       <c r="N254" s="1" t="inlineStr">
         <is>
-          <t>L707: isolated marker/symbol line :: 2</t>
+          <t>L650: symbol-only separator/garbage line :: 1.60</t>
         </is>
       </c>
       <c r="O254" s="1" t="inlineStr"/>
@@ -11240,7 +10996,7 @@
       <c r="M255" s="1" t="inlineStr"/>
       <c r="N255" s="1" t="inlineStr">
         <is>
-          <t>L712: isolated marker/symbol line :: a</t>
+          <t>L653: symbol-only separator/garbage line :: 7.87</t>
         </is>
       </c>
       <c r="O255" s="1" t="inlineStr"/>
@@ -11271,7 +11027,7 @@
       <c r="M256" s="1" t="inlineStr"/>
       <c r="N256" s="1" t="inlineStr">
         <is>
-          <t>L713: isolated marker/symbol line :: .</t>
+          <t>L654: symbol-only separator/garbage line :: 7.07</t>
         </is>
       </c>
       <c r="O256" s="1" t="inlineStr"/>
@@ -11302,7 +11058,7 @@
       <c r="M257" s="1" t="inlineStr"/>
       <c r="N257" s="1" t="inlineStr">
         <is>
-          <t>L715: isolated marker/symbol line :: .</t>
+          <t>L656: symbol-only separator/garbage line :: 4.50</t>
         </is>
       </c>
       <c r="O257" s="1" t="inlineStr"/>
@@ -11333,7 +11089,7 @@
       <c r="M258" s="1" t="inlineStr"/>
       <c r="N258" s="1" t="inlineStr">
         <is>
-          <t>L725: isolated marker/symbol line :: 4</t>
+          <t>L660: symbol-only separator/garbage line :: · 1.00</t>
         </is>
       </c>
       <c r="O258" s="1" t="inlineStr"/>
@@ -11364,7 +11120,7 @@
       <c r="M259" s="1" t="inlineStr"/>
       <c r="N259" s="1" t="inlineStr">
         <is>
-          <t>L728: isolated marker/symbol line :: 66</t>
+          <t>L662: stray/suspicious non-ASCII glyph(s): U+516C CJK UNIFIED IDEOGRAPH-516C | isolated marker/symbol line :: 公</t>
         </is>
       </c>
       <c r="O259" s="1" t="inlineStr"/>
@@ -11395,7 +11151,7 @@
       <c r="M260" s="1" t="inlineStr"/>
       <c r="N260" s="1" t="inlineStr">
         <is>
-          <t>L729: isolated marker/symbol line :: 64</t>
+          <t>L663: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O260" s="1" t="inlineStr"/>
@@ -11426,7 +11182,7 @@
       <c r="M261" s="1" t="inlineStr"/>
       <c r="N261" s="1" t="inlineStr">
         <is>
-          <t>L733: isolated marker/symbol line :: "</t>
+          <t>L665: symbol-only separator/garbage line :: 618.60</t>
         </is>
       </c>
       <c r="O261" s="1" t="inlineStr"/>
@@ -11457,7 +11213,7 @@
       <c r="M262" s="1" t="inlineStr"/>
       <c r="N262" s="1" t="inlineStr">
         <is>
-          <t>L739: isolated marker/symbol line :: 04</t>
+          <t>L668: isolated marker/symbol line :: Y</t>
         </is>
       </c>
       <c r="O262" s="1" t="inlineStr"/>
@@ -11488,7 +11244,7 @@
       <c r="M263" s="1" t="inlineStr"/>
       <c r="N263" s="1" t="inlineStr">
         <is>
-          <t>L741: isolated marker/symbol line :: .</t>
+          <t>L669: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O263" s="1" t="inlineStr"/>
@@ -11519,7 +11275,7 @@
       <c r="M264" s="1" t="inlineStr"/>
       <c r="N264" s="1" t="inlineStr">
         <is>
-          <t>L751: isolated marker/symbol line :: 68</t>
+          <t>L697: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O264" s="1" t="inlineStr"/>
@@ -11550,7 +11306,7 @@
       <c r="M265" s="1" t="inlineStr"/>
       <c r="N265" s="1" t="inlineStr">
         <is>
-          <t>L754: isolated marker/symbol line :: A</t>
+          <t>L699: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O265" s="1" t="inlineStr"/>
@@ -11581,7 +11337,7 @@
       <c r="M266" s="1" t="inlineStr"/>
       <c r="N266" s="1" t="inlineStr">
         <is>
-          <t>L756: isolated marker/symbol line :: 0</t>
+          <t>L700: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O266" s="1" t="inlineStr"/>
@@ -11612,7 +11368,7 @@
       <c r="M267" s="1" t="inlineStr"/>
       <c r="N267" s="1" t="inlineStr">
         <is>
-          <t>L759: isolated marker/symbol line :: 84</t>
+          <t>L701: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O267" s="1" t="inlineStr"/>
@@ -11643,7 +11399,7 @@
       <c r="M268" s="1" t="inlineStr"/>
       <c r="N268" s="1" t="inlineStr">
         <is>
-          <t>L766: isolated marker/symbol line :: 6</t>
+          <t>L703: stray/suspicious non-ASCII glyph(s): U+53E3 CJK UNIFIED IDEOGRAPH-53E3 | isolated marker/symbol line :: 口</t>
         </is>
       </c>
       <c r="O268" s="1" t="inlineStr"/>
@@ -11674,7 +11430,7 @@
       <c r="M269" s="1" t="inlineStr"/>
       <c r="N269" s="1" t="inlineStr">
         <is>
-          <t>L771: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L707: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O269" s="1" t="inlineStr"/>
@@ -11705,7 +11461,7 @@
       <c r="M270" s="1" t="inlineStr"/>
       <c r="N270" s="1" t="inlineStr">
         <is>
-          <t>L775: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L712: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O270" s="1" t="inlineStr"/>
@@ -11736,7 +11492,7 @@
       <c r="M271" s="1" t="inlineStr"/>
       <c r="N271" s="1" t="inlineStr">
         <is>
-          <t>L779: isolated marker/symbol line :: 19</t>
+          <t>L713: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O271" s="1" t="inlineStr"/>
@@ -11767,7 +11523,7 @@
       <c r="M272" s="1" t="inlineStr"/>
       <c r="N272" s="1" t="inlineStr">
         <is>
-          <t>L780: isolated marker/symbol line :: 4</t>
+          <t>L715: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O272" s="1" t="inlineStr"/>
@@ -11798,7 +11554,7 @@
       <c r="M273" s="1" t="inlineStr"/>
       <c r="N273" s="1" t="inlineStr">
         <is>
-          <t>L781: isolated marker/symbol line :: 66</t>
+          <t>L719: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O273" s="1" t="inlineStr"/>
@@ -11829,7 +11585,7 @@
       <c r="M274" s="1" t="inlineStr"/>
       <c r="N274" s="1" t="inlineStr">
         <is>
-          <t>L782: isolated marker/symbol line :: 200</t>
+          <t>L725: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O274" s="1" t="inlineStr"/>
@@ -11860,7 +11616,7 @@
       <c r="M275" s="1" t="inlineStr"/>
       <c r="N275" s="1" t="inlineStr">
         <is>
-          <t>L794: isolated marker/symbol line :: 84</t>
+          <t>L728: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O275" s="1" t="inlineStr"/>
@@ -11891,7 +11647,7 @@
       <c r="M276" s="1" t="inlineStr"/>
       <c r="N276" s="1" t="inlineStr">
         <is>
-          <t>L795: isolated marker/symbol line :: 8</t>
+          <t>L729: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O276" s="1" t="inlineStr"/>
@@ -11922,7 +11678,7 @@
       <c r="M277" s="1" t="inlineStr"/>
       <c r="N277" s="1" t="inlineStr">
         <is>
-          <t>L796: isolated marker/symbol line :: 1</t>
+          <t>L733: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O277" s="1" t="inlineStr"/>
@@ -11953,7 +11709,7 @@
       <c r="M278" s="1" t="inlineStr"/>
       <c r="N278" s="1" t="inlineStr">
         <is>
-          <t>L797: isolated marker/symbol line :: 4</t>
+          <t>L739: isolated marker/symbol line :: 04</t>
         </is>
       </c>
       <c r="O278" s="1" t="inlineStr"/>
@@ -11984,7 +11740,7 @@
       <c r="M279" s="1" t="inlineStr"/>
       <c r="N279" s="1" t="inlineStr">
         <is>
-          <t>L809: isolated marker/symbol line :: 89</t>
+          <t>L741: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O279" s="1" t="inlineStr"/>
@@ -12015,7 +11771,7 @@
       <c r="M280" s="1" t="inlineStr"/>
       <c r="N280" s="1" t="inlineStr">
         <is>
-          <t>L829: symbol-only separator/garbage line :: 86-15</t>
+          <t>L742: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O280" s="1" t="inlineStr"/>
@@ -12046,7 +11802,7 @@
       <c r="M281" s="1" t="inlineStr"/>
       <c r="N281" s="1" t="inlineStr">
         <is>
-          <t>L831: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L745: stray/suspicious non-ASCII glyph(s): U+5EFA CJK UNIFIED IDEOGRAPH-5EFA | isolated marker/symbol line :: 建</t>
         </is>
       </c>
       <c r="O281" s="1" t="inlineStr"/>
@@ -12077,7 +11833,7 @@
       <c r="M282" s="1" t="inlineStr"/>
       <c r="N282" s="1" t="inlineStr">
         <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+00A6 BROKEN BAR | isolated marker/symbol line :: è­¦</t>
+          <t>L749: stray/suspicious non-ASCII glyph(s): U+4E8B CJK UNIFIED IDEOGRAPH-4E8B | isolated marker/symbol line :: 事</t>
         </is>
       </c>
       <c r="O282" s="1" t="inlineStr"/>
@@ -12108,7 +11864,7 @@
       <c r="M283" s="1" t="inlineStr"/>
       <c r="N283" s="1" t="inlineStr">
         <is>
-          <t>L866: isolated marker/symbol line :: '</t>
+          <t>L751: isolated marker/symbol line :: 68</t>
         </is>
       </c>
       <c r="O283" s="1" t="inlineStr"/>
@@ -12139,7 +11895,7 @@
       <c r="M284" s="1" t="inlineStr"/>
       <c r="N284" s="1" t="inlineStr">
         <is>
-          <t>L867: isolated marker/symbol line :: 4</t>
+          <t>L754: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O284" s="1" t="inlineStr"/>
@@ -12170,7 +11926,7 @@
       <c r="M285" s="1" t="inlineStr"/>
       <c r="N285" s="1" t="inlineStr">
         <is>
-          <t>L869: isolated marker/symbol line :: 2</t>
+          <t>L756: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O285" s="1" t="inlineStr"/>
@@ -12201,7 +11957,7 @@
       <c r="M286" s="1" t="inlineStr"/>
       <c r="N286" s="1" t="inlineStr">
         <is>
-          <t>L875: isolated marker/symbol line :: -</t>
+          <t>L759: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O286" s="1" t="inlineStr"/>
@@ -12232,7 +11988,7 @@
       <c r="M287" s="1" t="inlineStr"/>
       <c r="N287" s="1" t="inlineStr">
         <is>
-          <t>L876: isolated marker/symbol line :: 2</t>
+          <t>L766: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O287" s="1" t="inlineStr"/>
@@ -12263,7 +12019,7 @@
       <c r="M288" s="1" t="inlineStr"/>
       <c r="N288" s="1" t="inlineStr">
         <is>
-          <t>L879: isolated marker/symbol line :: ;</t>
+          <t>L768: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O288" s="1" t="inlineStr"/>
@@ -12294,7 +12050,7 @@
       <c r="M289" s="1" t="inlineStr"/>
       <c r="N289" s="1" t="inlineStr">
         <is>
-          <t>L880: isolated marker/symbol line :: : s</t>
+          <t>L771: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O289" s="1" t="inlineStr"/>
@@ -12325,7 +12081,7 @@
       <c r="M290" s="1" t="inlineStr"/>
       <c r="N290" s="1" t="inlineStr">
         <is>
-          <t>L895: isolated marker/symbol line :: 0 #</t>
+          <t>L775: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O290" s="1" t="inlineStr"/>
@@ -12356,7 +12112,7 @@
       <c r="M291" s="1" t="inlineStr"/>
       <c r="N291" s="1" t="inlineStr">
         <is>
-          <t>L896: isolated marker/symbol line :: 000</t>
+          <t>L779: isolated marker/symbol line :: 19</t>
         </is>
       </c>
       <c r="O291" s="1" t="inlineStr"/>
@@ -12387,7 +12143,7 @@
       <c r="M292" s="1" t="inlineStr"/>
       <c r="N292" s="1" t="inlineStr">
         <is>
-          <t>L898: isolated marker/symbol line :: 0</t>
+          <t>L780: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O292" s="1" t="inlineStr"/>
@@ -12418,7 +12174,7 @@
       <c r="M293" s="1" t="inlineStr"/>
       <c r="N293" s="1" t="inlineStr">
         <is>
-          <t>L916: isolated marker/symbol line :: 2</t>
+          <t>L781: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O293" s="1" t="inlineStr"/>
@@ -12449,7 +12205,7 @@
       <c r="M294" s="1" t="inlineStr"/>
       <c r="N294" s="1" t="inlineStr">
         <is>
-          <t>L920: isolated marker/symbol line :: 77</t>
+          <t>L782: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O294" s="1" t="inlineStr"/>
@@ -12480,7 +12236,7 @@
       <c r="M295" s="1" t="inlineStr"/>
       <c r="N295" s="1" t="inlineStr">
         <is>
-          <t>L925: isolated marker/symbol line :: **</t>
+          <t>L794: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O295" s="1" t="inlineStr"/>
@@ -12511,7 +12267,7 @@
       <c r="M296" s="1" t="inlineStr"/>
       <c r="N296" s="1" t="inlineStr">
         <is>
-          <t>L927: symbol-only separator/garbage line :: 80.00</t>
+          <t>L795: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O296" s="1" t="inlineStr"/>
@@ -12542,7 +12298,7 @@
       <c r="M297" s="1" t="inlineStr"/>
       <c r="N297" s="1" t="inlineStr">
         <is>
-          <t>L931: symbol-only separator/garbage line :: 2021.15</t>
+          <t>L796: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O297" s="1" t="inlineStr"/>
@@ -12573,7 +12329,7 @@
       <c r="M298" s="1" t="inlineStr"/>
       <c r="N298" s="1" t="inlineStr">
         <is>
-          <t>L937: isolated marker/symbol line :: ***</t>
+          <t>L797: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O298" s="1" t="inlineStr"/>
@@ -12604,7 +12360,7 @@
       <c r="M299" s="1" t="inlineStr"/>
       <c r="N299" s="1" t="inlineStr">
         <is>
-          <t>L946: symbol-only separator/garbage line :: ***********</t>
+          <t>L809: isolated marker/symbol line :: 89</t>
         </is>
       </c>
       <c r="O299" s="1" t="inlineStr"/>
@@ -12635,7 +12391,7 @@
       <c r="M300" s="1" t="inlineStr"/>
       <c r="N300" s="1" t="inlineStr">
         <is>
-          <t>L947: symbol-only separator/garbage line :: **********</t>
+          <t>L829: symbol-only separator/garbage line :: 86-15</t>
         </is>
       </c>
       <c r="O300" s="1" t="inlineStr"/>
@@ -12666,7 +12422,7 @@
       <c r="M301" s="1" t="inlineStr"/>
       <c r="N301" s="1" t="inlineStr">
         <is>
-          <t>L950: isolated marker/symbol line :: *</t>
+          <t>L831: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O301" s="1" t="inlineStr"/>
@@ -12697,7 +12453,7 @@
       <c r="M302" s="1" t="inlineStr"/>
       <c r="N302" s="1" t="inlineStr">
         <is>
-          <t>L955: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L832: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
         </is>
       </c>
       <c r="O302" s="1" t="inlineStr"/>
@@ -12728,7 +12484,7 @@
       <c r="M303" s="1" t="inlineStr"/>
       <c r="N303" s="1" t="inlineStr">
         <is>
-          <t>L956: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L833: stray/suspicious non-ASCII glyph(s): U+8B66 CJK UNIFIED IDEOGRAPH-8B66 | isolated marker/symbol line :: 警</t>
         </is>
       </c>
       <c r="O303" s="1" t="inlineStr"/>
@@ -12759,7 +12515,7 @@
       <c r="M304" s="1" t="inlineStr"/>
       <c r="N304" s="1" t="inlineStr">
         <is>
-          <t>L957: isolated marker/symbol line :: D</t>
+          <t>L834: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
         </is>
       </c>
       <c r="O304" s="1" t="inlineStr"/>
@@ -12790,7 +12546,7 @@
       <c r="M305" s="1" t="inlineStr"/>
       <c r="N305" s="1" t="inlineStr">
         <is>
-          <t>L962: isolated marker/symbol line :: a.</t>
+          <t>L866: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O305" s="1" t="inlineStr"/>
@@ -12821,7 +12577,7 @@
       <c r="M306" s="1" t="inlineStr"/>
       <c r="N306" s="1" t="inlineStr">
         <is>
-          <t>L963: isolated marker/symbol line :: d</t>
+          <t>L867: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O306" s="1" t="inlineStr"/>
@@ -12852,7 +12608,7 @@
       <c r="M307" s="1" t="inlineStr"/>
       <c r="N307" s="1" t="inlineStr">
         <is>
-          <t>L992: isolated marker/symbol line :: *</t>
+          <t>L868: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O307" s="1" t="inlineStr"/>
@@ -12883,7 +12639,7 @@
       <c r="M308" s="1" t="inlineStr"/>
       <c r="N308" s="1" t="inlineStr">
         <is>
-          <t>L993: isolated marker/symbol line :: *</t>
+          <t>L869: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O308" s="1" t="inlineStr"/>
@@ -12914,7 +12670,7 @@
       <c r="M309" s="1" t="inlineStr"/>
       <c r="N309" s="1" t="inlineStr">
         <is>
-          <t>L999: isolated marker/symbol line :: 200</t>
+          <t>L875: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O309" s="1" t="inlineStr"/>
@@ -12945,7 +12701,7 @@
       <c r="M310" s="1" t="inlineStr"/>
       <c r="N310" s="1" t="inlineStr">
         <is>
-          <t>L1000: symbol-only separator/garbage line :: 25,</t>
+          <t>L876: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O310" s="1" t="inlineStr"/>
@@ -12976,7 +12732,7 @@
       <c r="M311" s="1" t="inlineStr"/>
       <c r="N311" s="1" t="inlineStr">
         <is>
-          <t>L1001: isolated marker/symbol line :: 0</t>
+          <t>L879: isolated marker/symbol line :: ;</t>
         </is>
       </c>
       <c r="O311" s="1" t="inlineStr"/>
@@ -13007,7 +12763,7 @@
       <c r="M312" s="1" t="inlineStr"/>
       <c r="N312" s="1" t="inlineStr">
         <is>
-          <t>L1002: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L880: isolated marker/symbol line :: : s</t>
         </is>
       </c>
       <c r="O312" s="1" t="inlineStr"/>
@@ -13038,7 +12794,7 @@
       <c r="M313" s="1" t="inlineStr"/>
       <c r="N313" s="1" t="inlineStr">
         <is>
-          <t>L1003: isolated marker/symbol line :: " 6</t>
+          <t>L889: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O313" s="1" t="inlineStr"/>
@@ -13069,7 +12825,7 @@
       <c r="M314" s="1" t="inlineStr"/>
       <c r="N314" s="1" t="inlineStr">
         <is>
-          <t>L1004: isolated marker/symbol line :: 46</t>
+          <t>L895: isolated marker/symbol line :: 0 #</t>
         </is>
       </c>
       <c r="O314" s="1" t="inlineStr"/>
@@ -13100,7 +12856,7 @@
       <c r="M315" s="1" t="inlineStr"/>
       <c r="N315" s="1" t="inlineStr">
         <is>
-          <t>L1005: isolated marker/symbol line :: 200</t>
+          <t>L896: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O315" s="1" t="inlineStr"/>
@@ -13131,7 +12887,7 @@
       <c r="M316" s="1" t="inlineStr"/>
       <c r="N316" s="1" t="inlineStr">
         <is>
-          <t>L1006: symbol-only separator/garbage line :: 27.</t>
+          <t>L898: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O316" s="1" t="inlineStr"/>
@@ -13162,7 +12918,7 @@
       <c r="M317" s="1" t="inlineStr"/>
       <c r="N317" s="1" t="inlineStr">
         <is>
-          <t>L1007: isolated marker/symbol line :: 2</t>
+          <t>L916: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O317" s="1" t="inlineStr"/>
@@ -13193,7 +12949,7 @@
       <c r="M318" s="1" t="inlineStr"/>
       <c r="N318" s="1" t="inlineStr">
         <is>
-          <t>L1008: isolated marker/symbol line :: "</t>
+          <t>L919: stray/suspicious non-ASCII glyph(s): U+697C CJK UNIFIED IDEOGRAPH-697C | isolated marker/symbol line :: 楼</t>
         </is>
       </c>
       <c r="O318" s="1" t="inlineStr"/>
@@ -13224,7 +12980,7 @@
       <c r="M319" s="1" t="inlineStr"/>
       <c r="N319" s="1" t="inlineStr">
         <is>
-          <t>L1009: isolated marker/symbol line :: 20</t>
+          <t>L920: isolated marker/symbol line :: 77</t>
         </is>
       </c>
       <c r="O319" s="1" t="inlineStr"/>
@@ -13255,7 +13011,7 @@
       <c r="M320" s="1" t="inlineStr"/>
       <c r="N320" s="1" t="inlineStr">
         <is>
-          <t>L1010: symbol-only separator/garbage line :: 28.</t>
+          <t>L925: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O320" s="1" t="inlineStr"/>
@@ -13286,7 +13042,7 @@
       <c r="M321" s="1" t="inlineStr"/>
       <c r="N321" s="1" t="inlineStr">
         <is>
-          <t>L1011: isolated marker/symbol line :: 4</t>
+          <t>L927: symbol-only separator/garbage line :: 80.00</t>
         </is>
       </c>
       <c r="O321" s="1" t="inlineStr"/>
@@ -13317,7 +13073,7 @@
       <c r="M322" s="1" t="inlineStr"/>
       <c r="N322" s="1" t="inlineStr">
         <is>
-          <t>L1012: isolated marker/symbol line :: 200</t>
+          <t>L928: stray/suspicious non-ASCII glyph(s): U+6210 CJK UNIFIED IDEOGRAPH-6210 | isolated marker/symbol line :: 成</t>
         </is>
       </c>
       <c r="O322" s="1" t="inlineStr"/>
@@ -13348,7 +13104,7 @@
       <c r="M323" s="1" t="inlineStr"/>
       <c r="N323" s="1" t="inlineStr">
         <is>
-          <t>L1014: isolated marker/symbol line :: .</t>
+          <t>L931: symbol-only separator/garbage line :: 2021.15</t>
         </is>
       </c>
       <c r="O323" s="1" t="inlineStr"/>
@@ -13379,7 +13135,7 @@
       <c r="M324" s="1" t="inlineStr"/>
       <c r="N324" s="1" t="inlineStr">
         <is>
-          <t>L1015: isolated marker/symbol line :: 20</t>
+          <t>L937: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O324" s="1" t="inlineStr"/>
@@ -13410,7 +13166,7 @@
       <c r="M325" s="1" t="inlineStr"/>
       <c r="N325" s="1" t="inlineStr">
         <is>
-          <t>L1016: isolated marker/symbol line :: "</t>
+          <t>L946: symbol-only separator/garbage line :: ***********</t>
         </is>
       </c>
       <c r="O325" s="1" t="inlineStr"/>
@@ -13441,7 +13197,7 @@
       <c r="M326" s="1" t="inlineStr"/>
       <c r="N326" s="1" t="inlineStr">
         <is>
-          <t>L1017: isolated marker/symbol line :: "</t>
+          <t>L947: symbol-only separator/garbage line :: **********</t>
         </is>
       </c>
       <c r="O326" s="1" t="inlineStr"/>
@@ -13472,7 +13228,7 @@
       <c r="M327" s="1" t="inlineStr"/>
       <c r="N327" s="1" t="inlineStr">
         <is>
-          <t>L1018: isolated marker/symbol line :: 200</t>
+          <t>L950: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O327" s="1" t="inlineStr"/>
@@ -13503,7 +13259,7 @@
       <c r="M328" s="1" t="inlineStr"/>
       <c r="N328" s="1" t="inlineStr">
         <is>
-          <t>L1019: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L955: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O328" s="1" t="inlineStr"/>
@@ -13534,7 +13290,7 @@
       <c r="M329" s="1" t="inlineStr"/>
       <c r="N329" s="1" t="inlineStr">
         <is>
-          <t>L1020: isolated marker/symbol line :: 200</t>
+          <t>L956: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O329" s="1" t="inlineStr"/>
@@ -13565,7 +13321,7 @@
       <c r="M330" s="1" t="inlineStr"/>
       <c r="N330" s="1" t="inlineStr">
         <is>
-          <t>L1021: isolated marker/symbol line :: 200</t>
+          <t>L957: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O330" s="1" t="inlineStr"/>
@@ -13596,7 +13352,7 @@
       <c r="M331" s="1" t="inlineStr"/>
       <c r="N331" s="1" t="inlineStr">
         <is>
-          <t>L1022: symbol-only separator/garbage line :: 1860</t>
+          <t>L962: isolated marker/symbol line :: a.</t>
         </is>
       </c>
       <c r="O331" s="1" t="inlineStr"/>
@@ -13627,7 +13383,7 @@
       <c r="M332" s="1" t="inlineStr"/>
       <c r="N332" s="1" t="inlineStr">
         <is>
-          <t>L1023: isolated marker/symbol line :: .</t>
+          <t>L963: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O332" s="1" t="inlineStr"/>
@@ -13658,7 +13414,7 @@
       <c r="M333" s="1" t="inlineStr"/>
       <c r="N333" s="1" t="inlineStr">
         <is>
-          <t>L1029: symbol-only separator/garbage line :: 300.00</t>
+          <t>L992: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O333" s="1" t="inlineStr"/>
@@ -13689,7 +13445,7 @@
       <c r="M334" s="1" t="inlineStr"/>
       <c r="N334" s="1" t="inlineStr">
         <is>
-          <t>L1030: isolated marker/symbol line :: 4</t>
+          <t>L993: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O334" s="1" t="inlineStr"/>
@@ -13720,7 +13476,7 @@
       <c r="M335" s="1" t="inlineStr"/>
       <c r="N335" s="1" t="inlineStr">
         <is>
-          <t>L1031: symbol-only separator/garbage line :: 100.0</t>
+          <t>L999: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O335" s="1" t="inlineStr"/>
@@ -13751,7 +13507,7 @@
       <c r="M336" s="1" t="inlineStr"/>
       <c r="N336" s="1" t="inlineStr">
         <is>
-          <t>L1032: symbol-only separator/garbage line :: 480.00</t>
+          <t>L1000: symbol-only separator/garbage line :: 25,</t>
         </is>
       </c>
       <c r="O336" s="1" t="inlineStr"/>
@@ -13782,7 +13538,7 @@
       <c r="M337" s="1" t="inlineStr"/>
       <c r="N337" s="1" t="inlineStr">
         <is>
-          <t>L1034: isolated marker/symbol line :: 4</t>
+          <t>L1001: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O337" s="1" t="inlineStr"/>
@@ -13813,7 +13569,7 @@
       <c r="M338" s="1" t="inlineStr"/>
       <c r="N338" s="1" t="inlineStr">
         <is>
-          <t>L1035: symbol-only separator/garbage line :: 6.90</t>
+          <t>L1002: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O338" s="1" t="inlineStr"/>
@@ -13844,7 +13600,7 @@
       <c r="M339" s="1" t="inlineStr"/>
       <c r="N339" s="1" t="inlineStr">
         <is>
-          <t>L1036: isolated marker/symbol line :: 0</t>
+          <t>L1003: isolated marker/symbol line :: " 6</t>
         </is>
       </c>
       <c r="O339" s="1" t="inlineStr"/>
@@ -13875,7 +13631,7 @@
       <c r="M340" s="1" t="inlineStr"/>
       <c r="N340" s="1" t="inlineStr">
         <is>
-          <t>L1038: isolated marker/symbol line :: 4</t>
+          <t>L1004: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O340" s="1" t="inlineStr"/>
@@ -13906,7 +13662,7 @@
       <c r="M341" s="1" t="inlineStr"/>
       <c r="N341" s="1" t="inlineStr">
         <is>
-          <t>L1039: isolated marker/symbol line :: 20</t>
+          <t>L1005: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O341" s="1" t="inlineStr"/>
@@ -13937,7 +13693,7 @@
       <c r="M342" s="1" t="inlineStr"/>
       <c r="N342" s="1" t="inlineStr">
         <is>
-          <t>L1040: symbol-only separator/garbage line :: 14.05</t>
+          <t>L1006: symbol-only separator/garbage line :: 27.</t>
         </is>
       </c>
       <c r="O342" s="1" t="inlineStr"/>
@@ -13968,7 +13724,7 @@
       <c r="M343" s="1" t="inlineStr"/>
       <c r="N343" s="1" t="inlineStr">
         <is>
-          <t>L1042: isolated marker/symbol line :: h</t>
+          <t>L1007: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O343" s="1" t="inlineStr"/>
@@ -13999,7 +13755,7 @@
       <c r="M344" s="1" t="inlineStr"/>
       <c r="N344" s="1" t="inlineStr">
         <is>
-          <t>L1043: isolated marker/symbol line :: .</t>
+          <t>L1008: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O344" s="1" t="inlineStr"/>
@@ -14030,7 +13786,7 @@
       <c r="M345" s="1" t="inlineStr"/>
       <c r="N345" s="1" t="inlineStr">
         <is>
-          <t>L1045: symbol-only separator/garbage line :: 40.00</t>
+          <t>L1009: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O345" s="1" t="inlineStr"/>
@@ -14061,7 +13817,7 @@
       <c r="M346" s="1" t="inlineStr"/>
       <c r="N346" s="1" t="inlineStr">
         <is>
-          <t>L1046: symbol-only separator/garbage line :: 1600</t>
+          <t>L1010: symbol-only separator/garbage line :: 28.</t>
         </is>
       </c>
       <c r="O346" s="1" t="inlineStr"/>
@@ -14092,7 +13848,7 @@
       <c r="M347" s="1" t="inlineStr"/>
       <c r="N347" s="1" t="inlineStr">
         <is>
-          <t>L1047: symbol-only separator/garbage line :: 22.00</t>
+          <t>L1011: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O347" s="1" t="inlineStr"/>
@@ -14123,7 +13879,7 @@
       <c r="M348" s="1" t="inlineStr"/>
       <c r="N348" s="1" t="inlineStr">
         <is>
-          <t>L1048: symbol-only separator/garbage line :: 50.00</t>
+          <t>L1012: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O348" s="1" t="inlineStr"/>
@@ -14154,7 +13910,7 @@
       <c r="M349" s="1" t="inlineStr"/>
       <c r="N349" s="1" t="inlineStr">
         <is>
-          <t>L1051: isolated marker/symbol line :: 4</t>
+          <t>L1014: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O349" s="1" t="inlineStr"/>
@@ -14185,7 +13941,7 @@
       <c r="M350" s="1" t="inlineStr"/>
       <c r="N350" s="1" t="inlineStr">
         <is>
-          <t>L1053: symbol-only separator/garbage line :: 21.00</t>
+          <t>L1015: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O350" s="1" t="inlineStr"/>
@@ -14216,7 +13972,7 @@
       <c r="M351" s="1" t="inlineStr"/>
       <c r="N351" s="1" t="inlineStr">
         <is>
-          <t>L1054: isolated marker/symbol line :: O</t>
+          <t>L1016: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O351" s="1" t="inlineStr"/>
@@ -14247,7 +14003,7 @@
       <c r="M352" s="1" t="inlineStr"/>
       <c r="N352" s="1" t="inlineStr">
         <is>
-          <t>L1057: symbol-only separator/garbage line :: 69.16</t>
+          <t>L1017: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O352" s="1" t="inlineStr"/>
@@ -14278,7 +14034,7 @@
       <c r="M353" s="1" t="inlineStr"/>
       <c r="N353" s="1" t="inlineStr">
         <is>
-          <t>L1065: isolated marker/symbol line :: 4</t>
+          <t>L1018: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O353" s="1" t="inlineStr"/>
@@ -14309,7 +14065,7 @@
       <c r="M354" s="1" t="inlineStr"/>
       <c r="N354" s="1" t="inlineStr">
         <is>
-          <t>L1068: symbol-only separator/garbage line :: 8.25</t>
+          <t>L1019: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O354" s="1" t="inlineStr"/>
@@ -14340,7 +14096,7 @@
       <c r="M355" s="1" t="inlineStr"/>
       <c r="N355" s="1" t="inlineStr">
         <is>
-          <t>L1070: symbol-only separator/garbage line :: 5.31</t>
+          <t>L1020: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O355" s="1" t="inlineStr"/>
@@ -14371,7 +14127,7 @@
       <c r="M356" s="1" t="inlineStr"/>
       <c r="N356" s="1" t="inlineStr">
         <is>
-          <t>L1072: isolated marker/symbol line :: 2</t>
+          <t>L1021: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O356" s="1" t="inlineStr"/>
@@ -14402,7 +14158,7 @@
       <c r="M357" s="1" t="inlineStr"/>
       <c r="N357" s="1" t="inlineStr">
         <is>
-          <t>L1073: isolated marker/symbol line :: 313</t>
+          <t>L1022: symbol-only separator/garbage line :: 1860</t>
         </is>
       </c>
       <c r="O357" s="1" t="inlineStr"/>
@@ -14433,7 +14189,7 @@
       <c r="M358" s="1" t="inlineStr"/>
       <c r="N358" s="1" t="inlineStr">
         <is>
-          <t>L1077: symbol-only separator/garbage line :: 10.80</t>
+          <t>L1023: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O358" s="1" t="inlineStr"/>
@@ -14464,7 +14220,7 @@
       <c r="M359" s="1" t="inlineStr"/>
       <c r="N359" s="1" t="inlineStr">
         <is>
-          <t>L1079: isolated marker/symbol line :: 2</t>
+          <t>L1029: symbol-only separator/garbage line :: 300.00</t>
         </is>
       </c>
       <c r="O359" s="1" t="inlineStr"/>
@@ -14495,7 +14251,7 @@
       <c r="M360" s="1" t="inlineStr"/>
       <c r="N360" s="1" t="inlineStr">
         <is>
-          <t>L1082: symbol-only separator/garbage line :: 5.00</t>
+          <t>L1030: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O360" s="1" t="inlineStr"/>
@@ -14526,7 +14282,7 @@
       <c r="M361" s="1" t="inlineStr"/>
       <c r="N361" s="1" t="inlineStr">
         <is>
-          <t>L1084: isolated marker/symbol line :: 780</t>
+          <t>L1031: symbol-only separator/garbage line :: 100.0</t>
         </is>
       </c>
       <c r="O361" s="1" t="inlineStr"/>
@@ -14557,7 +14313,7 @@
       <c r="M362" s="1" t="inlineStr"/>
       <c r="N362" s="1" t="inlineStr">
         <is>
-          <t>L1085: isolated marker/symbol line :: 730</t>
+          <t>L1032: symbol-only separator/garbage line :: 480.00</t>
         </is>
       </c>
       <c r="O362" s="1" t="inlineStr"/>
@@ -14588,7 +14344,7 @@
       <c r="M363" s="1" t="inlineStr"/>
       <c r="N363" s="1" t="inlineStr">
         <is>
-          <t>L1087: isolated marker/symbol line :: D</t>
+          <t>L1034: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O363" s="1" t="inlineStr"/>
@@ -14619,7 +14375,7 @@
       <c r="M364" s="1" t="inlineStr"/>
       <c r="N364" s="1" t="inlineStr">
         <is>
-          <t>L1089: isolated marker/symbol line :: .</t>
+          <t>L1035: symbol-only separator/garbage line :: 6.90</t>
         </is>
       </c>
       <c r="O364" s="1" t="inlineStr"/>
@@ -14650,7 +14406,7 @@
       <c r="M365" s="1" t="inlineStr"/>
       <c r="N365" s="1" t="inlineStr">
         <is>
-          <t>L1090: symbol-only separator/garbage line :: 20.00</t>
+          <t>L1036: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O365" s="1" t="inlineStr"/>
@@ -14681,7 +14437,7 @@
       <c r="M366" s="1" t="inlineStr"/>
       <c r="N366" s="1" t="inlineStr">
         <is>
-          <t>L1092: symbol-only separator/garbage line :: 5.60</t>
+          <t>L1038: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O366" s="1" t="inlineStr"/>
@@ -14712,7 +14468,7 @@
       <c r="M367" s="1" t="inlineStr"/>
       <c r="N367" s="1" t="inlineStr">
         <is>
-          <t>L1094: isolated marker/symbol line :: 250</t>
+          <t>L1039: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O367" s="1" t="inlineStr"/>
@@ -14743,7 +14499,7 @@
       <c r="M368" s="1" t="inlineStr"/>
       <c r="N368" s="1" t="inlineStr">
         <is>
-          <t>L1096: symbol-only separator/garbage line :: 2.00</t>
+          <t>L1040: symbol-only separator/garbage line :: 14.05</t>
         </is>
       </c>
       <c r="O368" s="1" t="inlineStr"/>
@@ -14774,7 +14530,7 @@
       <c r="M369" s="1" t="inlineStr"/>
       <c r="N369" s="1" t="inlineStr">
         <is>
-          <t>L1098: isolated marker/symbol line :: 8</t>
+          <t>L1042: isolated marker/symbol line :: h</t>
         </is>
       </c>
       <c r="O369" s="1" t="inlineStr"/>
@@ -14805,7 +14561,7 @@
       <c r="M370" s="1" t="inlineStr"/>
       <c r="N370" s="1" t="inlineStr">
         <is>
-          <t>L1099: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR | isolated marker/symbol line :: å¦‚</t>
+          <t>L1043: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O370" s="1" t="inlineStr"/>
@@ -14836,7 +14592,7 @@
       <c r="M371" s="1" t="inlineStr"/>
       <c r="N371" s="1" t="inlineStr">
         <is>
-          <t>L1100: symbol-only separator/garbage line :: 1.12</t>
+          <t>L1045: symbol-only separator/garbage line :: 40.00</t>
         </is>
       </c>
       <c r="O371" s="1" t="inlineStr"/>
@@ -14867,7 +14623,7 @@
       <c r="M372" s="1" t="inlineStr"/>
       <c r="N372" s="1" t="inlineStr">
         <is>
-          <t>L1102: symbol-only separator/garbage line :: 11.2</t>
+          <t>L1046: symbol-only separator/garbage line :: 1600</t>
         </is>
       </c>
       <c r="O372" s="1" t="inlineStr"/>
@@ -14898,7 +14654,7 @@
       <c r="M373" s="1" t="inlineStr"/>
       <c r="N373" s="1" t="inlineStr">
         <is>
-          <t>L1104: isolated marker/symbol line :: 451</t>
+          <t>L1047: symbol-only separator/garbage line :: 22.00</t>
         </is>
       </c>
       <c r="O373" s="1" t="inlineStr"/>
@@ -14929,7 +14685,7 @@
       <c r="M374" s="1" t="inlineStr"/>
       <c r="N374" s="1" t="inlineStr">
         <is>
-          <t>L1106: isolated marker/symbol line :: 12</t>
+          <t>L1048: symbol-only separator/garbage line :: 50.00</t>
         </is>
       </c>
       <c r="O374" s="1" t="inlineStr"/>
@@ -14960,7 +14716,7 @@
       <c r="M375" s="1" t="inlineStr"/>
       <c r="N375" s="1" t="inlineStr">
         <is>
-          <t>L1109: symbol-only separator/garbage line :: 7.10</t>
+          <t>L1051: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O375" s="1" t="inlineStr"/>
@@ -14991,7 +14747,7 @@
       <c r="M376" s="1" t="inlineStr"/>
       <c r="N376" s="1" t="inlineStr">
         <is>
-          <t>L1111: isolated marker/symbol line :: 2</t>
+          <t>L1053: symbol-only separator/garbage line :: 21.00</t>
         </is>
       </c>
       <c r="O376" s="1" t="inlineStr"/>
@@ -15022,7 +14778,7 @@
       <c r="M377" s="1" t="inlineStr"/>
       <c r="N377" s="1" t="inlineStr">
         <is>
-          <t>L1112: isolated marker/symbol line :: .</t>
+          <t>L1054: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O377" s="1" t="inlineStr"/>
@@ -15053,7 +14809,7 @@
       <c r="M378" s="1" t="inlineStr"/>
       <c r="N378" s="1" t="inlineStr">
         <is>
-          <t>L1114: symbol-only separator/garbage line :: 2.00</t>
+          <t>L1057: symbol-only separator/garbage line :: 69.16</t>
         </is>
       </c>
       <c r="O378" s="1" t="inlineStr"/>
@@ -15084,7 +14840,7 @@
       <c r="M379" s="1" t="inlineStr"/>
       <c r="N379" s="1" t="inlineStr">
         <is>
-          <t>L1116: symbol-only separator/garbage line :: 6, 60</t>
+          <t>L1058: stray/suspicious non-ASCII glyph(s): U+5730 CJK UNIFIED IDEOGRAPH-5730 | isolated marker/symbol line :: 地</t>
         </is>
       </c>
       <c r="O379" s="1" t="inlineStr"/>
@@ -15115,7 +14871,7 @@
       <c r="M380" s="1" t="inlineStr"/>
       <c r="N380" s="1" t="inlineStr">
         <is>
-          <t>L1117: symbol-only separator/garbage line :: $116, 37</t>
+          <t>L1065: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O380" s="1" t="inlineStr"/>
@@ -15146,7 +14902,7 @@
       <c r="M381" s="1" t="inlineStr"/>
       <c r="N381" s="1" t="inlineStr">
         <is>
-          <t>L1122: symbol-only separator/garbage line :: 1, 00</t>
+          <t>L1068: symbol-only separator/garbage line :: 8.25</t>
         </is>
       </c>
       <c r="O381" s="1" t="inlineStr"/>
@@ -15177,7 +14933,7 @@
       <c r="M382" s="1" t="inlineStr"/>
       <c r="N382" s="1" t="inlineStr">
         <is>
-          <t>L1124: isolated marker/symbol line :: 2</t>
+          <t>L1070: symbol-only separator/garbage line :: 5.31</t>
         </is>
       </c>
       <c r="O382" s="1" t="inlineStr"/>
@@ -15208,7 +14964,7 @@
       <c r="M383" s="1" t="inlineStr"/>
       <c r="N383" s="1" t="inlineStr">
         <is>
-          <t>L1127: symbol-only separator/garbage line :: 5, 20</t>
+          <t>L1072: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O383" s="1" t="inlineStr"/>
@@ -15239,7 +14995,7 @@
       <c r="M384" s="1" t="inlineStr"/>
       <c r="N384" s="1" t="inlineStr">
         <is>
-          <t>L1131: isolated marker/symbol line :: :.</t>
+          <t>L1073: isolated marker/symbol line :: 313</t>
         </is>
       </c>
       <c r="O384" s="1" t="inlineStr"/>
@@ -15270,7 +15026,7 @@
       <c r="M385" s="1" t="inlineStr"/>
       <c r="N385" s="1" t="inlineStr">
         <is>
-          <t>L1132: symbol-only separator/garbage line :: 20, 00</t>
+          <t>L1077: symbol-only separator/garbage line :: 10.80</t>
         </is>
       </c>
       <c r="O385" s="1" t="inlineStr"/>
@@ -15301,7 +15057,7 @@
       <c r="M386" s="1" t="inlineStr"/>
       <c r="N386" s="1" t="inlineStr">
         <is>
-          <t>L1135: isolated marker/symbol line :: 0</t>
+          <t>L1079: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O386" s="1" t="inlineStr"/>
@@ -15332,7 +15088,7 @@
       <c r="M387" s="1" t="inlineStr"/>
       <c r="N387" s="1" t="inlineStr">
         <is>
-          <t>L1136: isolated marker/symbol line :: 1</t>
+          <t>L1082: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O387" s="1" t="inlineStr"/>
@@ -15363,7 +15119,7 @@
       <c r="M388" s="1" t="inlineStr"/>
       <c r="N388" s="1" t="inlineStr">
         <is>
-          <t>L1137: isolated marker/symbol line :: 7</t>
+          <t>L1084: isolated marker/symbol line :: 780</t>
         </is>
       </c>
       <c r="O388" s="1" t="inlineStr"/>
@@ -15394,7 +15150,7 @@
       <c r="M389" s="1" t="inlineStr"/>
       <c r="N389" s="1" t="inlineStr">
         <is>
-          <t>L1139: symbol-only separator/garbage line :: 12, 90</t>
+          <t>L1085: isolated marker/symbol line :: 730</t>
         </is>
       </c>
       <c r="O389" s="1" t="inlineStr"/>
@@ -15425,7 +15181,7 @@
       <c r="M390" s="1" t="inlineStr"/>
       <c r="N390" s="1" t="inlineStr">
         <is>
-          <t>L1141: isolated marker/symbol line :: 4</t>
+          <t>L1087: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O390" s="1" t="inlineStr"/>
@@ -15456,7 +15212,7 @@
       <c r="M391" s="1" t="inlineStr"/>
       <c r="N391" s="1" t="inlineStr">
         <is>
-          <t>L1146: isolated marker/symbol line :: .</t>
+          <t>L1089: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O391" s="1" t="inlineStr"/>
@@ -15487,7 +15243,7 @@
       <c r="M392" s="1" t="inlineStr"/>
       <c r="N392" s="1" t="inlineStr">
         <is>
-          <t>L1147: symbol-only separator/garbage line :: 220.00</t>
+          <t>L1090: symbol-only separator/garbage line :: 20.00</t>
         </is>
       </c>
       <c r="O392" s="1" t="inlineStr"/>
@@ -15518,7 +15274,7 @@
       <c r="M393" s="1" t="inlineStr"/>
       <c r="N393" s="1" t="inlineStr">
         <is>
-          <t>L1149: symbol-only separator/garbage line :: 6, 00</t>
+          <t>L1092: symbol-only separator/garbage line :: 5.60</t>
         </is>
       </c>
       <c r="O393" s="1" t="inlineStr"/>
@@ -15549,7 +15305,7 @@
       <c r="M394" s="1" t="inlineStr"/>
       <c r="N394" s="1" t="inlineStr">
         <is>
-          <t>L1151: isolated marker/symbol line :: 3</t>
+          <t>L1094: isolated marker/symbol line :: 250</t>
         </is>
       </c>
       <c r="O394" s="1" t="inlineStr"/>
@@ -15580,7 +15336,7 @@
       <c r="M395" s="1" t="inlineStr"/>
       <c r="N395" s="1" t="inlineStr">
         <is>
-          <t>L1153: symbol-only separator/garbage line :: 3.00</t>
+          <t>L1096: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O395" s="1" t="inlineStr"/>
@@ -15611,7 +15367,7 @@
       <c r="M396" s="1" t="inlineStr"/>
       <c r="N396" s="1" t="inlineStr">
         <is>
-          <t>L1155: symbol-only separator/garbage line :: 7.55</t>
+          <t>L1098: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O396" s="1" t="inlineStr"/>
@@ -15642,7 +15398,7 @@
       <c r="M397" s="1" t="inlineStr"/>
       <c r="N397" s="1" t="inlineStr">
         <is>
-          <t>L1157: symbol-only separator/garbage line :: 50.00</t>
+          <t>L1099: stray/suspicious non-ASCII glyph(s): U+5982 CJK UNIFIED IDEOGRAPH-5982 | isolated marker/symbol line :: 如</t>
         </is>
       </c>
       <c r="O397" s="1" t="inlineStr"/>
@@ -15673,7 +15429,7 @@
       <c r="M398" s="1" t="inlineStr"/>
       <c r="N398" s="1" t="inlineStr">
         <is>
-          <t>L1161: isolated marker/symbol line :: 0</t>
+          <t>L1100: symbol-only separator/garbage line :: 1.12</t>
         </is>
       </c>
       <c r="O398" s="1" t="inlineStr"/>
@@ -15704,7 +15460,7 @@
       <c r="M399" s="1" t="inlineStr"/>
       <c r="N399" s="1" t="inlineStr">
         <is>
-          <t>L1164: symbol-only separator/garbage line :: 2.56</t>
+          <t>L1102: symbol-only separator/garbage line :: 11.2</t>
         </is>
       </c>
       <c r="O399" s="1" t="inlineStr"/>
@@ -15735,7 +15491,7 @@
       <c r="M400" s="1" t="inlineStr"/>
       <c r="N400" s="1" t="inlineStr">
         <is>
-          <t>L1170: isolated marker/symbol line :: .</t>
+          <t>L1104: isolated marker/symbol line :: 451</t>
         </is>
       </c>
       <c r="O400" s="1" t="inlineStr"/>
@@ -15766,7 +15522,7 @@
       <c r="M401" s="1" t="inlineStr"/>
       <c r="N401" s="1" t="inlineStr">
         <is>
-          <t>L1173: isolated marker/symbol line :: 1</t>
+          <t>L1106: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O401" s="1" t="inlineStr"/>
@@ -15797,7 +15553,7 @@
       <c r="M402" s="1" t="inlineStr"/>
       <c r="N402" s="1" t="inlineStr">
         <is>
-          <t>L1182: isolated marker/symbol line :: X</t>
+          <t>L1109: symbol-only separator/garbage line :: 7.10</t>
         </is>
       </c>
       <c r="O402" s="1" t="inlineStr"/>
@@ -15828,7 +15584,7 @@
       <c r="M403" s="1" t="inlineStr"/>
       <c r="N403" s="1" t="inlineStr">
         <is>
-          <t>L1183: isolated marker/symbol line :: t</t>
+          <t>L1111: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O403" s="1" t="inlineStr"/>
@@ -15859,7 +15615,7 @@
       <c r="M404" s="1" t="inlineStr"/>
       <c r="N404" s="1" t="inlineStr">
         <is>
-          <t>L1192: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: è¦�</t>
+          <t>L1112: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O404" s="1" t="inlineStr"/>
@@ -15890,7 +15646,7 @@
       <c r="M405" s="1" t="inlineStr"/>
       <c r="N405" s="1" t="inlineStr">
         <is>
-          <t>L1205: symbol-only separator/garbage line :: $1526.41</t>
+          <t>L1114: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O405" s="1" t="inlineStr"/>
@@ -15921,7 +15677,7 @@
       <c r="M406" s="1" t="inlineStr"/>
       <c r="N406" s="1" t="inlineStr">
         <is>
-          <t>L1207: symbol-only separator/garbage line :: 523, 75</t>
+          <t>L1116: symbol-only separator/garbage line :: 6, 60</t>
         </is>
       </c>
       <c r="O406" s="1" t="inlineStr"/>
@@ -15952,7 +15708,7 @@
       <c r="M407" s="1" t="inlineStr"/>
       <c r="N407" s="1" t="inlineStr">
         <is>
-          <t>L1209: symbol-only separator/garbage line :: 1016, 00</t>
+          <t>L1117: symbol-only separator/garbage line :: $116, 37</t>
         </is>
       </c>
       <c r="O407" s="1" t="inlineStr"/>
@@ -15983,7 +15739,7 @@
       <c r="M408" s="1" t="inlineStr"/>
       <c r="N408" s="1" t="inlineStr">
         <is>
-          <t>L1213: symbol-only separator/garbage line :: 167, 65</t>
+          <t>L1121: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O408" s="1" t="inlineStr"/>
@@ -16014,7 +15770,7 @@
       <c r="M409" s="1" t="inlineStr"/>
       <c r="N409" s="1" t="inlineStr">
         <is>
-          <t>L1215: isolated marker/symbol line :: 2</t>
+          <t>L1122: symbol-only separator/garbage line :: 1, 00</t>
         </is>
       </c>
       <c r="O409" s="1" t="inlineStr"/>
@@ -16045,7 +15801,7 @@
       <c r="M410" s="1" t="inlineStr"/>
       <c r="N410" s="1" t="inlineStr">
         <is>
-          <t>L1217: isolated marker/symbol line :: é›…</t>
+          <t>L1124: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O410" s="1" t="inlineStr"/>
@@ -16076,7 +15832,7 @@
       <c r="M411" s="1" t="inlineStr"/>
       <c r="N411" s="1" t="inlineStr">
         <is>
-          <t>L1218: stray/suspicious non-ASCII glyph(s): U+02DC SMALL TILDE, U+00A5 YEN SIGN | isolated marker/symbol line :: æ˜¥</t>
+          <t>L1127: symbol-only separator/garbage line :: 5, 20</t>
         </is>
       </c>
       <c r="O411" s="1" t="inlineStr"/>
@@ -16107,7 +15863,7 @@
       <c r="M412" s="1" t="inlineStr"/>
       <c r="N412" s="1" t="inlineStr">
         <is>
-          <t>L1221: isolated marker/symbol line :: 1</t>
+          <t>L1131: isolated marker/symbol line :: :.</t>
         </is>
       </c>
       <c r="O412" s="1" t="inlineStr"/>
@@ -16138,7 +15894,7 @@
       <c r="M413" s="1" t="inlineStr"/>
       <c r="N413" s="1" t="inlineStr">
         <is>
-          <t>L1225: isolated marker/symbol line :: .</t>
+          <t>L1132: symbol-only separator/garbage line :: 20, 00</t>
         </is>
       </c>
       <c r="O413" s="1" t="inlineStr"/>
@@ -16169,7 +15925,7 @@
       <c r="M414" s="1" t="inlineStr"/>
       <c r="N414" s="1" t="inlineStr">
         <is>
-          <t>L1240: isolated marker/symbol line :: 240</t>
+          <t>L1135: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O414" s="1" t="inlineStr"/>
@@ -16200,7 +15956,7 @@
       <c r="M415" s="1" t="inlineStr"/>
       <c r="N415" s="1" t="inlineStr">
         <is>
-          <t>L1241: symbol-only separator/garbage line :: 182.25</t>
+          <t>L1136: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O415" s="1" t="inlineStr"/>
@@ -16231,7 +15987,7 @@
       <c r="M416" s="1" t="inlineStr"/>
       <c r="N416" s="1" t="inlineStr">
         <is>
-          <t>L1242: symbol-only separator/garbage line :: 54.00</t>
+          <t>L1137: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O416" s="1" t="inlineStr"/>
@@ -16262,7 +16018,7 @@
       <c r="M417" s="1" t="inlineStr"/>
       <c r="N417" s="1" t="inlineStr">
         <is>
-          <t>L1248: symbol-only separator/garbage line :: 618, 60</t>
+          <t>L1139: symbol-only separator/garbage line :: 12, 90</t>
         </is>
       </c>
       <c r="O417" s="1" t="inlineStr"/>
@@ -16293,7 +16049,7 @@
       <c r="M418" s="1" t="inlineStr"/>
       <c r="N418" s="1" t="inlineStr">
         <is>
-          <t>L1253: symbol-only separator/garbage line :: $2760.20</t>
+          <t>L1141: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O418" s="1" t="inlineStr"/>
@@ -16324,7 +16080,7 @@
       <c r="M419" s="1" t="inlineStr"/>
       <c r="N419" s="1" t="inlineStr">
         <is>
-          <t>L1268: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L1146: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O419" s="1" t="inlineStr"/>
@@ -16355,7 +16111,7 @@
       <c r="M420" s="1" t="inlineStr"/>
       <c r="N420" s="1" t="inlineStr">
         <is>
-          <t>L1270: symbol-only separator/garbage line :: 2.85</t>
+          <t>L1147: symbol-only separator/garbage line :: 220.00</t>
         </is>
       </c>
       <c r="O420" s="1" t="inlineStr"/>
@@ -16386,7 +16142,7 @@
       <c r="M421" s="1" t="inlineStr"/>
       <c r="N421" s="1" t="inlineStr">
         <is>
-          <t>L1273: symbol-only separator/garbage line :: 9, 601</t>
+          <t>L1149: symbol-only separator/garbage line :: 6, 00</t>
         </is>
       </c>
       <c r="O421" s="1" t="inlineStr"/>
@@ -16417,7 +16173,7 @@
       <c r="M422" s="1" t="inlineStr"/>
       <c r="N422" s="1" t="inlineStr">
         <is>
-          <t>L1275: symbol-only separator/garbage line :: 53.80</t>
+          <t>L1151: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O422" s="1" t="inlineStr"/>
@@ -16448,7 +16204,7 @@
       <c r="M423" s="1" t="inlineStr"/>
       <c r="N423" s="1" t="inlineStr">
         <is>
-          <t>L1323: isolated marker/symbol line :: 8</t>
+          <t>L1153: symbol-only separator/garbage line :: 3.00</t>
         </is>
       </c>
       <c r="O423" s="1" t="inlineStr"/>
@@ -16479,7 +16235,7 @@
       <c r="M424" s="1" t="inlineStr"/>
       <c r="N424" s="1" t="inlineStr">
         <is>
-          <t>L1342: isolated marker/symbol line :: W</t>
+          <t>L1155: symbol-only separator/garbage line :: 7.55</t>
         </is>
       </c>
       <c r="O424" s="1" t="inlineStr"/>
@@ -16510,7 +16266,7 @@
       <c r="M425" s="1" t="inlineStr"/>
       <c r="N425" s="1" t="inlineStr">
         <is>
-          <t>L1389: isolated marker/symbol line :: 0</t>
+          <t>L1157: symbol-only separator/garbage line :: 50.00</t>
         </is>
       </c>
       <c r="O425" s="1" t="inlineStr"/>
@@ -16541,7 +16297,7 @@
       <c r="M426" s="1" t="inlineStr"/>
       <c r="N426" s="1" t="inlineStr">
         <is>
-          <t>L1417: isolated marker/symbol line :: 8</t>
+          <t>L1161: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O426" s="1" t="inlineStr"/>
@@ -16572,7 +16328,7 @@
       <c r="M427" s="1" t="inlineStr"/>
       <c r="N427" s="1" t="inlineStr">
         <is>
-          <t>L1425: isolated marker/symbol line :: D</t>
+          <t>L1164: symbol-only separator/garbage line :: 2.56</t>
         </is>
       </c>
       <c r="O427" s="1" t="inlineStr"/>
@@ -16603,7 +16359,7 @@
       <c r="M428" s="1" t="inlineStr"/>
       <c r="N428" s="1" t="inlineStr">
         <is>
-          <t>L1426: isolated marker/symbol line :: 2</t>
+          <t>L1166: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。。</t>
         </is>
       </c>
       <c r="O428" s="1" t="inlineStr"/>
@@ -16634,7 +16390,7 @@
       <c r="M429" s="1" t="inlineStr"/>
       <c r="N429" s="1" t="inlineStr">
         <is>
-          <t>L1427: isolated marker/symbol line :: 4</t>
+          <t>L1170: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O429" s="1" t="inlineStr"/>
@@ -16665,7 +16421,7 @@
       <c r="M430" s="1" t="inlineStr"/>
       <c r="N430" s="1" t="inlineStr">
         <is>
-          <t>L1434: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | isolated marker/symbol line :: å…¨</t>
+          <t>L1173: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O430" s="1" t="inlineStr"/>
@@ -16696,7 +16452,7 @@
       <c r="M431" s="1" t="inlineStr"/>
       <c r="N431" s="1" t="inlineStr">
         <is>
-          <t>L1435: isolated marker/symbol line :: 2</t>
+          <t>L1182: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O431" s="1" t="inlineStr"/>
@@ -16727,7 +16483,7 @@
       <c r="M432" s="1" t="inlineStr"/>
       <c r="N432" s="1" t="inlineStr">
         <is>
-          <t>L1467: isolated marker/symbol line :: T</t>
+          <t>L1183: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O432" s="1" t="inlineStr"/>
@@ -16758,7 +16514,7 @@
       <c r="M433" s="1" t="inlineStr"/>
       <c r="N433" s="1" t="inlineStr">
         <is>
-          <t>L1486: symbol-only separator/garbage line :: 114.00</t>
+          <t>L1192: stray/suspicious non-ASCII glyph(s): U+8981 CJK UNIFIED IDEOGRAPH-8981 | isolated marker/symbol line :: 要</t>
         </is>
       </c>
       <c r="O433" s="1" t="inlineStr"/>
@@ -16789,7 +16545,7 @@
       <c r="M434" s="1" t="inlineStr"/>
       <c r="N434" s="1" t="inlineStr">
         <is>
-          <t>L1487: isolated marker/symbol line :: .</t>
+          <t>L1205: symbol-only separator/garbage line :: $1526.41</t>
         </is>
       </c>
       <c r="O434" s="1" t="inlineStr"/>
@@ -16820,7 +16576,7 @@
       <c r="M435" s="1" t="inlineStr"/>
       <c r="N435" s="1" t="inlineStr">
         <is>
-          <t>L1488: isolated marker/symbol line :: "</t>
+          <t>L1207: symbol-only separator/garbage line :: 523, 75</t>
         </is>
       </c>
       <c r="O435" s="1" t="inlineStr"/>
@@ -16851,7 +16607,7 @@
       <c r="M436" s="1" t="inlineStr"/>
       <c r="N436" s="1" t="inlineStr">
         <is>
-          <t>L1489: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L1209: symbol-only separator/garbage line :: 1016, 00</t>
         </is>
       </c>
       <c r="O436" s="1" t="inlineStr"/>
@@ -16882,7 +16638,7 @@
       <c r="M437" s="1" t="inlineStr"/>
       <c r="N437" s="1" t="inlineStr">
         <is>
-          <t>L1490: symbol-only separator/garbage line :: 1.39</t>
+          <t>L1213: symbol-only separator/garbage line :: 167, 65</t>
         </is>
       </c>
       <c r="O437" s="1" t="inlineStr"/>
@@ -16913,7 +16669,7 @@
       <c r="M438" s="1" t="inlineStr"/>
       <c r="N438" s="1" t="inlineStr">
         <is>
-          <t>L1492: isolated marker/symbol line :: 7</t>
+          <t>L1215: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O438" s="1" t="inlineStr"/>
@@ -16944,7 +16700,7 @@
       <c r="M439" s="1" t="inlineStr"/>
       <c r="N439" s="1" t="inlineStr">
         <is>
-          <t>L1494: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L1217: stray/suspicious non-ASCII glyph(s): U+96C5 CJK UNIFIED IDEOGRAPH-96C5 | isolated marker/symbol line :: 雅</t>
         </is>
       </c>
       <c r="O439" s="1" t="inlineStr"/>
@@ -16975,7 +16731,7 @@
       <c r="M440" s="1" t="inlineStr"/>
       <c r="N440" s="1" t="inlineStr">
         <is>
-          <t>L1496: isolated marker/symbol line :: e</t>
+          <t>L1218: stray/suspicious non-ASCII glyph(s): U+6625 CJK UNIFIED IDEOGRAPH-6625 | isolated marker/symbol line :: 春</t>
         </is>
       </c>
       <c r="O440" s="1" t="inlineStr"/>
@@ -17006,7 +16762,7 @@
       <c r="M441" s="1" t="inlineStr"/>
       <c r="N441" s="1" t="inlineStr">
         <is>
-          <t>L1497: isolated marker/symbol line :: e.</t>
+          <t>L1221: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O441" s="1" t="inlineStr"/>
@@ -17037,7 +16793,7 @@
       <c r="M442" s="1" t="inlineStr"/>
       <c r="N442" s="1" t="inlineStr">
         <is>
-          <t>L1498: isolated marker/symbol line :: 4</t>
+          <t>L1225: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O442" s="1" t="inlineStr"/>
@@ -17068,7 +16824,7 @@
       <c r="M443" s="1" t="inlineStr"/>
       <c r="N443" s="1" t="inlineStr">
         <is>
-          <t>L1499: symbol-only separator/garbage line :: 34.48</t>
+          <t>L1240: isolated marker/symbol line :: 240</t>
         </is>
       </c>
       <c r="O443" s="1" t="inlineStr"/>
@@ -17099,7 +16855,7 @@
       <c r="M444" s="1" t="inlineStr"/>
       <c r="N444" s="1" t="inlineStr">
         <is>
-          <t>L1500: isolated marker/symbol line :: 6</t>
+          <t>L1241: symbol-only separator/garbage line :: 182.25</t>
         </is>
       </c>
       <c r="O444" s="1" t="inlineStr"/>
@@ -17130,7 +16886,7 @@
       <c r="M445" s="1" t="inlineStr"/>
       <c r="N445" s="1" t="inlineStr">
         <is>
-          <t>L1501: symbol-only separator/garbage line :: 15, 13</t>
+          <t>L1242: symbol-only separator/garbage line :: 54.00</t>
         </is>
       </c>
       <c r="O445" s="1" t="inlineStr"/>
@@ -17161,7 +16917,7 @@
       <c r="M446" s="1" t="inlineStr"/>
       <c r="N446" s="1" t="inlineStr">
         <is>
-          <t>L1502: isolated marker/symbol line :: #</t>
+          <t>L1248: symbol-only separator/garbage line :: 618, 60</t>
         </is>
       </c>
       <c r="O446" s="1" t="inlineStr"/>
@@ -17192,7 +16948,7 @@
       <c r="M447" s="1" t="inlineStr"/>
       <c r="N447" s="1" t="inlineStr">
         <is>
-          <t>L1504: symbol-only separator/garbage line :: 23.25</t>
+          <t>L1253: symbol-only separator/garbage line :: $2760.20</t>
         </is>
       </c>
       <c r="O447" s="1" t="inlineStr"/>
@@ -17223,7 +16979,7 @@
       <c r="M448" s="1" t="inlineStr"/>
       <c r="N448" s="1" t="inlineStr">
         <is>
-          <t>L1506: isolated marker/symbol line :: 4</t>
+          <t>L1268: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O448" s="1" t="inlineStr"/>
@@ -17254,7 +17010,7 @@
       <c r="M449" s="1" t="inlineStr"/>
       <c r="N449" s="1" t="inlineStr">
         <is>
-          <t>L1507: isolated marker/symbol line :: 2</t>
+          <t>L1270: symbol-only separator/garbage line :: 2.85</t>
         </is>
       </c>
       <c r="O449" s="1" t="inlineStr"/>
@@ -17285,7 +17041,7 @@
       <c r="M450" s="1" t="inlineStr"/>
       <c r="N450" s="1" t="inlineStr">
         <is>
-          <t>L1508: symbol-only separator/garbage line :: 12.70</t>
+          <t>L1273: symbol-only separator/garbage line :: 9, 601</t>
         </is>
       </c>
       <c r="O450" s="1" t="inlineStr"/>
@@ -17316,7 +17072,7 @@
       <c r="M451" s="1" t="inlineStr"/>
       <c r="N451" s="1" t="inlineStr">
         <is>
-          <t>L1513: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L1275: symbol-only separator/garbage line :: 53.80</t>
         </is>
       </c>
       <c r="O451" s="1" t="inlineStr"/>
@@ -17347,7 +17103,7 @@
       <c r="M452" s="1" t="inlineStr"/>
       <c r="N452" s="1" t="inlineStr">
         <is>
-          <t>L1517: isolated marker/symbol line :: 140</t>
+          <t>L1323: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O452" s="1" t="inlineStr"/>
@@ -17378,7 +17134,7 @@
       <c r="M453" s="1" t="inlineStr"/>
       <c r="N453" s="1" t="inlineStr">
         <is>
-          <t>L1520: symbol-only separator/garbage line :: 4.20</t>
+          <t>L1342: isolated marker/symbol line :: W</t>
         </is>
       </c>
       <c r="O453" s="1" t="inlineStr"/>
@@ -17409,7 +17165,7 @@
       <c r="M454" s="1" t="inlineStr"/>
       <c r="N454" s="1" t="inlineStr">
         <is>
-          <t>L1521: isolated marker/symbol line :: ~</t>
+          <t>L1361: stray/suspicious non-ASCII glyph(s): U+5E7F CJK UNIFIED IDEOGRAPH-5E7F | isolated marker/symbol line :: 广</t>
         </is>
       </c>
       <c r="O454" s="1" t="inlineStr"/>
@@ -17440,7 +17196,7 @@
       <c r="M455" s="1" t="inlineStr"/>
       <c r="N455" s="1" t="inlineStr">
         <is>
-          <t>L1525: symbol-only separator/garbage line :: 15.1</t>
+          <t>L1389: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O455" s="1" t="inlineStr"/>
@@ -17471,7 +17227,7 @@
       <c r="M456" s="1" t="inlineStr"/>
       <c r="N456" s="1" t="inlineStr">
         <is>
-          <t>L1528: symbol-only separator/garbage line :: 9, 16</t>
+          <t>L1417: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O456" s="1" t="inlineStr"/>
@@ -17502,7 +17258,7 @@
       <c r="M457" s="1" t="inlineStr"/>
       <c r="N457" s="1" t="inlineStr">
         <is>
-          <t>L1529: isolated marker/symbol line :: ,</t>
+          <t>L1425: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O457" s="1" t="inlineStr"/>
@@ -17533,7 +17289,7 @@
       <c r="M458" s="1" t="inlineStr"/>
       <c r="N458" s="1" t="inlineStr">
         <is>
-          <t>L1530: isolated marker/symbol line :: 30</t>
+          <t>L1426: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O458" s="1" t="inlineStr"/>
@@ -17564,7 +17320,7 @@
       <c r="M459" s="1" t="inlineStr"/>
       <c r="N459" s="1" t="inlineStr">
         <is>
-          <t>L1531: isolated marker/symbol line :: %</t>
+          <t>L1427: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O459" s="1" t="inlineStr"/>
@@ -17595,7 +17351,7 @@
       <c r="M460" s="1" t="inlineStr"/>
       <c r="N460" s="1" t="inlineStr">
         <is>
-          <t>L1532: isolated marker/symbol line :: .</t>
+          <t>L1434: stray/suspicious non-ASCII glyph(s): U+5168 CJK UNIFIED IDEOGRAPH-5168 | isolated marker/symbol line :: 全</t>
         </is>
       </c>
       <c r="O460" s="1" t="inlineStr"/>
@@ -17626,7 +17382,7 @@
       <c r="M461" s="1" t="inlineStr"/>
       <c r="N461" s="1" t="inlineStr">
         <is>
-          <t>L1533: symbol-only separator/garbage line :: 6167</t>
+          <t>L1435: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O461" s="1" t="inlineStr"/>
@@ -17657,7 +17413,7 @@
       <c r="M462" s="1" t="inlineStr"/>
       <c r="N462" s="1" t="inlineStr">
         <is>
-          <t>L1534: isolated marker/symbol line :: 4</t>
+          <t>L1467: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O462" s="1" t="inlineStr"/>
@@ -17688,7 +17444,7 @@
       <c r="M463" s="1" t="inlineStr"/>
       <c r="N463" s="1" t="inlineStr">
         <is>
-          <t>L1535: isolated marker/symbol line :: X</t>
+          <t>L1486: symbol-only separator/garbage line :: 114.00</t>
         </is>
       </c>
       <c r="O463" s="1" t="inlineStr"/>
@@ -17719,7 +17475,7 @@
       <c r="M464" s="1" t="inlineStr"/>
       <c r="N464" s="1" t="inlineStr">
         <is>
-          <t>L1536: isolated marker/symbol line :: æ°”</t>
+          <t>L1487: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O464" s="1" t="inlineStr"/>
@@ -17750,7 +17506,7 @@
       <c r="M465" s="1" t="inlineStr"/>
       <c r="N465" s="1" t="inlineStr">
         <is>
-          <t>L1537: isolated marker/symbol line :: 3</t>
+          <t>L1488: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O465" s="1" t="inlineStr"/>
@@ -17765,6 +17521,967 @@
       <c r="X465" s="1" t="inlineStr"/>
       <c r="Y465" s="1" t="inlineStr"/>
     </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr"/>
+      <c r="B466" s="1" t="inlineStr"/>
+      <c r="C466" s="1" t="inlineStr"/>
+      <c r="D466" s="1" t="inlineStr"/>
+      <c r="E466" s="1" t="inlineStr"/>
+      <c r="F466" s="1" t="inlineStr"/>
+      <c r="G466" s="1" t="inlineStr"/>
+      <c r="H466" s="1" t="inlineStr"/>
+      <c r="I466" s="1" t="inlineStr"/>
+      <c r="J466" s="1" t="inlineStr"/>
+      <c r="K466" s="1" t="inlineStr"/>
+      <c r="L466" s="1" t="inlineStr"/>
+      <c r="M466" s="1" t="inlineStr"/>
+      <c r="N466" s="1" t="inlineStr">
+        <is>
+          <t>L1489: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O466" s="1" t="inlineStr"/>
+      <c r="P466" s="1" t="inlineStr"/>
+      <c r="Q466" s="1" t="inlineStr"/>
+      <c r="R466" s="1" t="inlineStr"/>
+      <c r="S466" s="1" t="inlineStr"/>
+      <c r="T466" s="1" t="inlineStr"/>
+      <c r="U466" s="1" t="inlineStr"/>
+      <c r="V466" s="1" t="inlineStr"/>
+      <c r="W466" s="1" t="inlineStr"/>
+      <c r="X466" s="1" t="inlineStr"/>
+      <c r="Y466" s="1" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr"/>
+      <c r="B467" s="1" t="inlineStr"/>
+      <c r="C467" s="1" t="inlineStr"/>
+      <c r="D467" s="1" t="inlineStr"/>
+      <c r="E467" s="1" t="inlineStr"/>
+      <c r="F467" s="1" t="inlineStr"/>
+      <c r="G467" s="1" t="inlineStr"/>
+      <c r="H467" s="1" t="inlineStr"/>
+      <c r="I467" s="1" t="inlineStr"/>
+      <c r="J467" s="1" t="inlineStr"/>
+      <c r="K467" s="1" t="inlineStr"/>
+      <c r="L467" s="1" t="inlineStr"/>
+      <c r="M467" s="1" t="inlineStr"/>
+      <c r="N467" s="1" t="inlineStr">
+        <is>
+          <t>L1490: symbol-only separator/garbage line :: 1.39</t>
+        </is>
+      </c>
+      <c r="O467" s="1" t="inlineStr"/>
+      <c r="P467" s="1" t="inlineStr"/>
+      <c r="Q467" s="1" t="inlineStr"/>
+      <c r="R467" s="1" t="inlineStr"/>
+      <c r="S467" s="1" t="inlineStr"/>
+      <c r="T467" s="1" t="inlineStr"/>
+      <c r="U467" s="1" t="inlineStr"/>
+      <c r="V467" s="1" t="inlineStr"/>
+      <c r="W467" s="1" t="inlineStr"/>
+      <c r="X467" s="1" t="inlineStr"/>
+      <c r="Y467" s="1" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr"/>
+      <c r="B468" s="1" t="inlineStr"/>
+      <c r="C468" s="1" t="inlineStr"/>
+      <c r="D468" s="1" t="inlineStr"/>
+      <c r="E468" s="1" t="inlineStr"/>
+      <c r="F468" s="1" t="inlineStr"/>
+      <c r="G468" s="1" t="inlineStr"/>
+      <c r="H468" s="1" t="inlineStr"/>
+      <c r="I468" s="1" t="inlineStr"/>
+      <c r="J468" s="1" t="inlineStr"/>
+      <c r="K468" s="1" t="inlineStr"/>
+      <c r="L468" s="1" t="inlineStr"/>
+      <c r="M468" s="1" t="inlineStr"/>
+      <c r="N468" s="1" t="inlineStr">
+        <is>
+          <t>L1492: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O468" s="1" t="inlineStr"/>
+      <c r="P468" s="1" t="inlineStr"/>
+      <c r="Q468" s="1" t="inlineStr"/>
+      <c r="R468" s="1" t="inlineStr"/>
+      <c r="S468" s="1" t="inlineStr"/>
+      <c r="T468" s="1" t="inlineStr"/>
+      <c r="U468" s="1" t="inlineStr"/>
+      <c r="V468" s="1" t="inlineStr"/>
+      <c r="W468" s="1" t="inlineStr"/>
+      <c r="X468" s="1" t="inlineStr"/>
+      <c r="Y468" s="1" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr"/>
+      <c r="B469" s="1" t="inlineStr"/>
+      <c r="C469" s="1" t="inlineStr"/>
+      <c r="D469" s="1" t="inlineStr"/>
+      <c r="E469" s="1" t="inlineStr"/>
+      <c r="F469" s="1" t="inlineStr"/>
+      <c r="G469" s="1" t="inlineStr"/>
+      <c r="H469" s="1" t="inlineStr"/>
+      <c r="I469" s="1" t="inlineStr"/>
+      <c r="J469" s="1" t="inlineStr"/>
+      <c r="K469" s="1" t="inlineStr"/>
+      <c r="L469" s="1" t="inlineStr"/>
+      <c r="M469" s="1" t="inlineStr"/>
+      <c r="N469" s="1" t="inlineStr">
+        <is>
+          <t>L1494: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="O469" s="1" t="inlineStr"/>
+      <c r="P469" s="1" t="inlineStr"/>
+      <c r="Q469" s="1" t="inlineStr"/>
+      <c r="R469" s="1" t="inlineStr"/>
+      <c r="S469" s="1" t="inlineStr"/>
+      <c r="T469" s="1" t="inlineStr"/>
+      <c r="U469" s="1" t="inlineStr"/>
+      <c r="V469" s="1" t="inlineStr"/>
+      <c r="W469" s="1" t="inlineStr"/>
+      <c r="X469" s="1" t="inlineStr"/>
+      <c r="Y469" s="1" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr"/>
+      <c r="B470" s="1" t="inlineStr"/>
+      <c r="C470" s="1" t="inlineStr"/>
+      <c r="D470" s="1" t="inlineStr"/>
+      <c r="E470" s="1" t="inlineStr"/>
+      <c r="F470" s="1" t="inlineStr"/>
+      <c r="G470" s="1" t="inlineStr"/>
+      <c r="H470" s="1" t="inlineStr"/>
+      <c r="I470" s="1" t="inlineStr"/>
+      <c r="J470" s="1" t="inlineStr"/>
+      <c r="K470" s="1" t="inlineStr"/>
+      <c r="L470" s="1" t="inlineStr"/>
+      <c r="M470" s="1" t="inlineStr"/>
+      <c r="N470" s="1" t="inlineStr">
+        <is>
+          <t>L1496: isolated marker/symbol line :: e</t>
+        </is>
+      </c>
+      <c r="O470" s="1" t="inlineStr"/>
+      <c r="P470" s="1" t="inlineStr"/>
+      <c r="Q470" s="1" t="inlineStr"/>
+      <c r="R470" s="1" t="inlineStr"/>
+      <c r="S470" s="1" t="inlineStr"/>
+      <c r="T470" s="1" t="inlineStr"/>
+      <c r="U470" s="1" t="inlineStr"/>
+      <c r="V470" s="1" t="inlineStr"/>
+      <c r="W470" s="1" t="inlineStr"/>
+      <c r="X470" s="1" t="inlineStr"/>
+      <c r="Y470" s="1" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr"/>
+      <c r="B471" s="1" t="inlineStr"/>
+      <c r="C471" s="1" t="inlineStr"/>
+      <c r="D471" s="1" t="inlineStr"/>
+      <c r="E471" s="1" t="inlineStr"/>
+      <c r="F471" s="1" t="inlineStr"/>
+      <c r="G471" s="1" t="inlineStr"/>
+      <c r="H471" s="1" t="inlineStr"/>
+      <c r="I471" s="1" t="inlineStr"/>
+      <c r="J471" s="1" t="inlineStr"/>
+      <c r="K471" s="1" t="inlineStr"/>
+      <c r="L471" s="1" t="inlineStr"/>
+      <c r="M471" s="1" t="inlineStr"/>
+      <c r="N471" s="1" t="inlineStr">
+        <is>
+          <t>L1497: isolated marker/symbol line :: e.</t>
+        </is>
+      </c>
+      <c r="O471" s="1" t="inlineStr"/>
+      <c r="P471" s="1" t="inlineStr"/>
+      <c r="Q471" s="1" t="inlineStr"/>
+      <c r="R471" s="1" t="inlineStr"/>
+      <c r="S471" s="1" t="inlineStr"/>
+      <c r="T471" s="1" t="inlineStr"/>
+      <c r="U471" s="1" t="inlineStr"/>
+      <c r="V471" s="1" t="inlineStr"/>
+      <c r="W471" s="1" t="inlineStr"/>
+      <c r="X471" s="1" t="inlineStr"/>
+      <c r="Y471" s="1" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr"/>
+      <c r="B472" s="1" t="inlineStr"/>
+      <c r="C472" s="1" t="inlineStr"/>
+      <c r="D472" s="1" t="inlineStr"/>
+      <c r="E472" s="1" t="inlineStr"/>
+      <c r="F472" s="1" t="inlineStr"/>
+      <c r="G472" s="1" t="inlineStr"/>
+      <c r="H472" s="1" t="inlineStr"/>
+      <c r="I472" s="1" t="inlineStr"/>
+      <c r="J472" s="1" t="inlineStr"/>
+      <c r="K472" s="1" t="inlineStr"/>
+      <c r="L472" s="1" t="inlineStr"/>
+      <c r="M472" s="1" t="inlineStr"/>
+      <c r="N472" s="1" t="inlineStr">
+        <is>
+          <t>L1498: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O472" s="1" t="inlineStr"/>
+      <c r="P472" s="1" t="inlineStr"/>
+      <c r="Q472" s="1" t="inlineStr"/>
+      <c r="R472" s="1" t="inlineStr"/>
+      <c r="S472" s="1" t="inlineStr"/>
+      <c r="T472" s="1" t="inlineStr"/>
+      <c r="U472" s="1" t="inlineStr"/>
+      <c r="V472" s="1" t="inlineStr"/>
+      <c r="W472" s="1" t="inlineStr"/>
+      <c r="X472" s="1" t="inlineStr"/>
+      <c r="Y472" s="1" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr"/>
+      <c r="B473" s="1" t="inlineStr"/>
+      <c r="C473" s="1" t="inlineStr"/>
+      <c r="D473" s="1" t="inlineStr"/>
+      <c r="E473" s="1" t="inlineStr"/>
+      <c r="F473" s="1" t="inlineStr"/>
+      <c r="G473" s="1" t="inlineStr"/>
+      <c r="H473" s="1" t="inlineStr"/>
+      <c r="I473" s="1" t="inlineStr"/>
+      <c r="J473" s="1" t="inlineStr"/>
+      <c r="K473" s="1" t="inlineStr"/>
+      <c r="L473" s="1" t="inlineStr"/>
+      <c r="M473" s="1" t="inlineStr"/>
+      <c r="N473" s="1" t="inlineStr">
+        <is>
+          <t>L1499: symbol-only separator/garbage line :: 34.48</t>
+        </is>
+      </c>
+      <c r="O473" s="1" t="inlineStr"/>
+      <c r="P473" s="1" t="inlineStr"/>
+      <c r="Q473" s="1" t="inlineStr"/>
+      <c r="R473" s="1" t="inlineStr"/>
+      <c r="S473" s="1" t="inlineStr"/>
+      <c r="T473" s="1" t="inlineStr"/>
+      <c r="U473" s="1" t="inlineStr"/>
+      <c r="V473" s="1" t="inlineStr"/>
+      <c r="W473" s="1" t="inlineStr"/>
+      <c r="X473" s="1" t="inlineStr"/>
+      <c r="Y473" s="1" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr"/>
+      <c r="B474" s="1" t="inlineStr"/>
+      <c r="C474" s="1" t="inlineStr"/>
+      <c r="D474" s="1" t="inlineStr"/>
+      <c r="E474" s="1" t="inlineStr"/>
+      <c r="F474" s="1" t="inlineStr"/>
+      <c r="G474" s="1" t="inlineStr"/>
+      <c r="H474" s="1" t="inlineStr"/>
+      <c r="I474" s="1" t="inlineStr"/>
+      <c r="J474" s="1" t="inlineStr"/>
+      <c r="K474" s="1" t="inlineStr"/>
+      <c r="L474" s="1" t="inlineStr"/>
+      <c r="M474" s="1" t="inlineStr"/>
+      <c r="N474" s="1" t="inlineStr">
+        <is>
+          <t>L1500: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
+      <c r="O474" s="1" t="inlineStr"/>
+      <c r="P474" s="1" t="inlineStr"/>
+      <c r="Q474" s="1" t="inlineStr"/>
+      <c r="R474" s="1" t="inlineStr"/>
+      <c r="S474" s="1" t="inlineStr"/>
+      <c r="T474" s="1" t="inlineStr"/>
+      <c r="U474" s="1" t="inlineStr"/>
+      <c r="V474" s="1" t="inlineStr"/>
+      <c r="W474" s="1" t="inlineStr"/>
+      <c r="X474" s="1" t="inlineStr"/>
+      <c r="Y474" s="1" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr"/>
+      <c r="B475" s="1" t="inlineStr"/>
+      <c r="C475" s="1" t="inlineStr"/>
+      <c r="D475" s="1" t="inlineStr"/>
+      <c r="E475" s="1" t="inlineStr"/>
+      <c r="F475" s="1" t="inlineStr"/>
+      <c r="G475" s="1" t="inlineStr"/>
+      <c r="H475" s="1" t="inlineStr"/>
+      <c r="I475" s="1" t="inlineStr"/>
+      <c r="J475" s="1" t="inlineStr"/>
+      <c r="K475" s="1" t="inlineStr"/>
+      <c r="L475" s="1" t="inlineStr"/>
+      <c r="M475" s="1" t="inlineStr"/>
+      <c r="N475" s="1" t="inlineStr">
+        <is>
+          <t>L1501: symbol-only separator/garbage line :: 15, 13</t>
+        </is>
+      </c>
+      <c r="O475" s="1" t="inlineStr"/>
+      <c r="P475" s="1" t="inlineStr"/>
+      <c r="Q475" s="1" t="inlineStr"/>
+      <c r="R475" s="1" t="inlineStr"/>
+      <c r="S475" s="1" t="inlineStr"/>
+      <c r="T475" s="1" t="inlineStr"/>
+      <c r="U475" s="1" t="inlineStr"/>
+      <c r="V475" s="1" t="inlineStr"/>
+      <c r="W475" s="1" t="inlineStr"/>
+      <c r="X475" s="1" t="inlineStr"/>
+      <c r="Y475" s="1" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr"/>
+      <c r="B476" s="1" t="inlineStr"/>
+      <c r="C476" s="1" t="inlineStr"/>
+      <c r="D476" s="1" t="inlineStr"/>
+      <c r="E476" s="1" t="inlineStr"/>
+      <c r="F476" s="1" t="inlineStr"/>
+      <c r="G476" s="1" t="inlineStr"/>
+      <c r="H476" s="1" t="inlineStr"/>
+      <c r="I476" s="1" t="inlineStr"/>
+      <c r="J476" s="1" t="inlineStr"/>
+      <c r="K476" s="1" t="inlineStr"/>
+      <c r="L476" s="1" t="inlineStr"/>
+      <c r="M476" s="1" t="inlineStr"/>
+      <c r="N476" s="1" t="inlineStr">
+        <is>
+          <t>L1502: isolated marker/symbol line :: #</t>
+        </is>
+      </c>
+      <c r="O476" s="1" t="inlineStr"/>
+      <c r="P476" s="1" t="inlineStr"/>
+      <c r="Q476" s="1" t="inlineStr"/>
+      <c r="R476" s="1" t="inlineStr"/>
+      <c r="S476" s="1" t="inlineStr"/>
+      <c r="T476" s="1" t="inlineStr"/>
+      <c r="U476" s="1" t="inlineStr"/>
+      <c r="V476" s="1" t="inlineStr"/>
+      <c r="W476" s="1" t="inlineStr"/>
+      <c r="X476" s="1" t="inlineStr"/>
+      <c r="Y476" s="1" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr"/>
+      <c r="B477" s="1" t="inlineStr"/>
+      <c r="C477" s="1" t="inlineStr"/>
+      <c r="D477" s="1" t="inlineStr"/>
+      <c r="E477" s="1" t="inlineStr"/>
+      <c r="F477" s="1" t="inlineStr"/>
+      <c r="G477" s="1" t="inlineStr"/>
+      <c r="H477" s="1" t="inlineStr"/>
+      <c r="I477" s="1" t="inlineStr"/>
+      <c r="J477" s="1" t="inlineStr"/>
+      <c r="K477" s="1" t="inlineStr"/>
+      <c r="L477" s="1" t="inlineStr"/>
+      <c r="M477" s="1" t="inlineStr"/>
+      <c r="N477" s="1" t="inlineStr">
+        <is>
+          <t>L1504: symbol-only separator/garbage line :: 23.25</t>
+        </is>
+      </c>
+      <c r="O477" s="1" t="inlineStr"/>
+      <c r="P477" s="1" t="inlineStr"/>
+      <c r="Q477" s="1" t="inlineStr"/>
+      <c r="R477" s="1" t="inlineStr"/>
+      <c r="S477" s="1" t="inlineStr"/>
+      <c r="T477" s="1" t="inlineStr"/>
+      <c r="U477" s="1" t="inlineStr"/>
+      <c r="V477" s="1" t="inlineStr"/>
+      <c r="W477" s="1" t="inlineStr"/>
+      <c r="X477" s="1" t="inlineStr"/>
+      <c r="Y477" s="1" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr"/>
+      <c r="B478" s="1" t="inlineStr"/>
+      <c r="C478" s="1" t="inlineStr"/>
+      <c r="D478" s="1" t="inlineStr"/>
+      <c r="E478" s="1" t="inlineStr"/>
+      <c r="F478" s="1" t="inlineStr"/>
+      <c r="G478" s="1" t="inlineStr"/>
+      <c r="H478" s="1" t="inlineStr"/>
+      <c r="I478" s="1" t="inlineStr"/>
+      <c r="J478" s="1" t="inlineStr"/>
+      <c r="K478" s="1" t="inlineStr"/>
+      <c r="L478" s="1" t="inlineStr"/>
+      <c r="M478" s="1" t="inlineStr"/>
+      <c r="N478" s="1" t="inlineStr">
+        <is>
+          <t>L1506: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O478" s="1" t="inlineStr"/>
+      <c r="P478" s="1" t="inlineStr"/>
+      <c r="Q478" s="1" t="inlineStr"/>
+      <c r="R478" s="1" t="inlineStr"/>
+      <c r="S478" s="1" t="inlineStr"/>
+      <c r="T478" s="1" t="inlineStr"/>
+      <c r="U478" s="1" t="inlineStr"/>
+      <c r="V478" s="1" t="inlineStr"/>
+      <c r="W478" s="1" t="inlineStr"/>
+      <c r="X478" s="1" t="inlineStr"/>
+      <c r="Y478" s="1" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr"/>
+      <c r="B479" s="1" t="inlineStr"/>
+      <c r="C479" s="1" t="inlineStr"/>
+      <c r="D479" s="1" t="inlineStr"/>
+      <c r="E479" s="1" t="inlineStr"/>
+      <c r="F479" s="1" t="inlineStr"/>
+      <c r="G479" s="1" t="inlineStr"/>
+      <c r="H479" s="1" t="inlineStr"/>
+      <c r="I479" s="1" t="inlineStr"/>
+      <c r="J479" s="1" t="inlineStr"/>
+      <c r="K479" s="1" t="inlineStr"/>
+      <c r="L479" s="1" t="inlineStr"/>
+      <c r="M479" s="1" t="inlineStr"/>
+      <c r="N479" s="1" t="inlineStr">
+        <is>
+          <t>L1507: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O479" s="1" t="inlineStr"/>
+      <c r="P479" s="1" t="inlineStr"/>
+      <c r="Q479" s="1" t="inlineStr"/>
+      <c r="R479" s="1" t="inlineStr"/>
+      <c r="S479" s="1" t="inlineStr"/>
+      <c r="T479" s="1" t="inlineStr"/>
+      <c r="U479" s="1" t="inlineStr"/>
+      <c r="V479" s="1" t="inlineStr"/>
+      <c r="W479" s="1" t="inlineStr"/>
+      <c r="X479" s="1" t="inlineStr"/>
+      <c r="Y479" s="1" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr"/>
+      <c r="B480" s="1" t="inlineStr"/>
+      <c r="C480" s="1" t="inlineStr"/>
+      <c r="D480" s="1" t="inlineStr"/>
+      <c r="E480" s="1" t="inlineStr"/>
+      <c r="F480" s="1" t="inlineStr"/>
+      <c r="G480" s="1" t="inlineStr"/>
+      <c r="H480" s="1" t="inlineStr"/>
+      <c r="I480" s="1" t="inlineStr"/>
+      <c r="J480" s="1" t="inlineStr"/>
+      <c r="K480" s="1" t="inlineStr"/>
+      <c r="L480" s="1" t="inlineStr"/>
+      <c r="M480" s="1" t="inlineStr"/>
+      <c r="N480" s="1" t="inlineStr">
+        <is>
+          <t>L1508: symbol-only separator/garbage line :: 12.70</t>
+        </is>
+      </c>
+      <c r="O480" s="1" t="inlineStr"/>
+      <c r="P480" s="1" t="inlineStr"/>
+      <c r="Q480" s="1" t="inlineStr"/>
+      <c r="R480" s="1" t="inlineStr"/>
+      <c r="S480" s="1" t="inlineStr"/>
+      <c r="T480" s="1" t="inlineStr"/>
+      <c r="U480" s="1" t="inlineStr"/>
+      <c r="V480" s="1" t="inlineStr"/>
+      <c r="W480" s="1" t="inlineStr"/>
+      <c r="X480" s="1" t="inlineStr"/>
+      <c r="Y480" s="1" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr"/>
+      <c r="B481" s="1" t="inlineStr"/>
+      <c r="C481" s="1" t="inlineStr"/>
+      <c r="D481" s="1" t="inlineStr"/>
+      <c r="E481" s="1" t="inlineStr"/>
+      <c r="F481" s="1" t="inlineStr"/>
+      <c r="G481" s="1" t="inlineStr"/>
+      <c r="H481" s="1" t="inlineStr"/>
+      <c r="I481" s="1" t="inlineStr"/>
+      <c r="J481" s="1" t="inlineStr"/>
+      <c r="K481" s="1" t="inlineStr"/>
+      <c r="L481" s="1" t="inlineStr"/>
+      <c r="M481" s="1" t="inlineStr"/>
+      <c r="N481" s="1" t="inlineStr">
+        <is>
+          <t>L1513: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="O481" s="1" t="inlineStr"/>
+      <c r="P481" s="1" t="inlineStr"/>
+      <c r="Q481" s="1" t="inlineStr"/>
+      <c r="R481" s="1" t="inlineStr"/>
+      <c r="S481" s="1" t="inlineStr"/>
+      <c r="T481" s="1" t="inlineStr"/>
+      <c r="U481" s="1" t="inlineStr"/>
+      <c r="V481" s="1" t="inlineStr"/>
+      <c r="W481" s="1" t="inlineStr"/>
+      <c r="X481" s="1" t="inlineStr"/>
+      <c r="Y481" s="1" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr"/>
+      <c r="B482" s="1" t="inlineStr"/>
+      <c r="C482" s="1" t="inlineStr"/>
+      <c r="D482" s="1" t="inlineStr"/>
+      <c r="E482" s="1" t="inlineStr"/>
+      <c r="F482" s="1" t="inlineStr"/>
+      <c r="G482" s="1" t="inlineStr"/>
+      <c r="H482" s="1" t="inlineStr"/>
+      <c r="I482" s="1" t="inlineStr"/>
+      <c r="J482" s="1" t="inlineStr"/>
+      <c r="K482" s="1" t="inlineStr"/>
+      <c r="L482" s="1" t="inlineStr"/>
+      <c r="M482" s="1" t="inlineStr"/>
+      <c r="N482" s="1" t="inlineStr">
+        <is>
+          <t>L1514: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | isolated marker/symbol line :: 2 ，</t>
+        </is>
+      </c>
+      <c r="O482" s="1" t="inlineStr"/>
+      <c r="P482" s="1" t="inlineStr"/>
+      <c r="Q482" s="1" t="inlineStr"/>
+      <c r="R482" s="1" t="inlineStr"/>
+      <c r="S482" s="1" t="inlineStr"/>
+      <c r="T482" s="1" t="inlineStr"/>
+      <c r="U482" s="1" t="inlineStr"/>
+      <c r="V482" s="1" t="inlineStr"/>
+      <c r="W482" s="1" t="inlineStr"/>
+      <c r="X482" s="1" t="inlineStr"/>
+      <c r="Y482" s="1" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr"/>
+      <c r="B483" s="1" t="inlineStr"/>
+      <c r="C483" s="1" t="inlineStr"/>
+      <c r="D483" s="1" t="inlineStr"/>
+      <c r="E483" s="1" t="inlineStr"/>
+      <c r="F483" s="1" t="inlineStr"/>
+      <c r="G483" s="1" t="inlineStr"/>
+      <c r="H483" s="1" t="inlineStr"/>
+      <c r="I483" s="1" t="inlineStr"/>
+      <c r="J483" s="1" t="inlineStr"/>
+      <c r="K483" s="1" t="inlineStr"/>
+      <c r="L483" s="1" t="inlineStr"/>
+      <c r="M483" s="1" t="inlineStr"/>
+      <c r="N483" s="1" t="inlineStr">
+        <is>
+          <t>L1517: isolated marker/symbol line :: 140</t>
+        </is>
+      </c>
+      <c r="O483" s="1" t="inlineStr"/>
+      <c r="P483" s="1" t="inlineStr"/>
+      <c r="Q483" s="1" t="inlineStr"/>
+      <c r="R483" s="1" t="inlineStr"/>
+      <c r="S483" s="1" t="inlineStr"/>
+      <c r="T483" s="1" t="inlineStr"/>
+      <c r="U483" s="1" t="inlineStr"/>
+      <c r="V483" s="1" t="inlineStr"/>
+      <c r="W483" s="1" t="inlineStr"/>
+      <c r="X483" s="1" t="inlineStr"/>
+      <c r="Y483" s="1" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr"/>
+      <c r="B484" s="1" t="inlineStr"/>
+      <c r="C484" s="1" t="inlineStr"/>
+      <c r="D484" s="1" t="inlineStr"/>
+      <c r="E484" s="1" t="inlineStr"/>
+      <c r="F484" s="1" t="inlineStr"/>
+      <c r="G484" s="1" t="inlineStr"/>
+      <c r="H484" s="1" t="inlineStr"/>
+      <c r="I484" s="1" t="inlineStr"/>
+      <c r="J484" s="1" t="inlineStr"/>
+      <c r="K484" s="1" t="inlineStr"/>
+      <c r="L484" s="1" t="inlineStr"/>
+      <c r="M484" s="1" t="inlineStr"/>
+      <c r="N484" s="1" t="inlineStr">
+        <is>
+          <t>L1520: symbol-only separator/garbage line :: 4.20</t>
+        </is>
+      </c>
+      <c r="O484" s="1" t="inlineStr"/>
+      <c r="P484" s="1" t="inlineStr"/>
+      <c r="Q484" s="1" t="inlineStr"/>
+      <c r="R484" s="1" t="inlineStr"/>
+      <c r="S484" s="1" t="inlineStr"/>
+      <c r="T484" s="1" t="inlineStr"/>
+      <c r="U484" s="1" t="inlineStr"/>
+      <c r="V484" s="1" t="inlineStr"/>
+      <c r="W484" s="1" t="inlineStr"/>
+      <c r="X484" s="1" t="inlineStr"/>
+      <c r="Y484" s="1" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr"/>
+      <c r="B485" s="1" t="inlineStr"/>
+      <c r="C485" s="1" t="inlineStr"/>
+      <c r="D485" s="1" t="inlineStr"/>
+      <c r="E485" s="1" t="inlineStr"/>
+      <c r="F485" s="1" t="inlineStr"/>
+      <c r="G485" s="1" t="inlineStr"/>
+      <c r="H485" s="1" t="inlineStr"/>
+      <c r="I485" s="1" t="inlineStr"/>
+      <c r="J485" s="1" t="inlineStr"/>
+      <c r="K485" s="1" t="inlineStr"/>
+      <c r="L485" s="1" t="inlineStr"/>
+      <c r="M485" s="1" t="inlineStr"/>
+      <c r="N485" s="1" t="inlineStr">
+        <is>
+          <t>L1521: isolated marker/symbol line :: ~</t>
+        </is>
+      </c>
+      <c r="O485" s="1" t="inlineStr"/>
+      <c r="P485" s="1" t="inlineStr"/>
+      <c r="Q485" s="1" t="inlineStr"/>
+      <c r="R485" s="1" t="inlineStr"/>
+      <c r="S485" s="1" t="inlineStr"/>
+      <c r="T485" s="1" t="inlineStr"/>
+      <c r="U485" s="1" t="inlineStr"/>
+      <c r="V485" s="1" t="inlineStr"/>
+      <c r="W485" s="1" t="inlineStr"/>
+      <c r="X485" s="1" t="inlineStr"/>
+      <c r="Y485" s="1" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr"/>
+      <c r="B486" s="1" t="inlineStr"/>
+      <c r="C486" s="1" t="inlineStr"/>
+      <c r="D486" s="1" t="inlineStr"/>
+      <c r="E486" s="1" t="inlineStr"/>
+      <c r="F486" s="1" t="inlineStr"/>
+      <c r="G486" s="1" t="inlineStr"/>
+      <c r="H486" s="1" t="inlineStr"/>
+      <c r="I486" s="1" t="inlineStr"/>
+      <c r="J486" s="1" t="inlineStr"/>
+      <c r="K486" s="1" t="inlineStr"/>
+      <c r="L486" s="1" t="inlineStr"/>
+      <c r="M486" s="1" t="inlineStr"/>
+      <c r="N486" s="1" t="inlineStr">
+        <is>
+          <t>L1525: symbol-only separator/garbage line :: 15.1</t>
+        </is>
+      </c>
+      <c r="O486" s="1" t="inlineStr"/>
+      <c r="P486" s="1" t="inlineStr"/>
+      <c r="Q486" s="1" t="inlineStr"/>
+      <c r="R486" s="1" t="inlineStr"/>
+      <c r="S486" s="1" t="inlineStr"/>
+      <c r="T486" s="1" t="inlineStr"/>
+      <c r="U486" s="1" t="inlineStr"/>
+      <c r="V486" s="1" t="inlineStr"/>
+      <c r="W486" s="1" t="inlineStr"/>
+      <c r="X486" s="1" t="inlineStr"/>
+      <c r="Y486" s="1" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr"/>
+      <c r="B487" s="1" t="inlineStr"/>
+      <c r="C487" s="1" t="inlineStr"/>
+      <c r="D487" s="1" t="inlineStr"/>
+      <c r="E487" s="1" t="inlineStr"/>
+      <c r="F487" s="1" t="inlineStr"/>
+      <c r="G487" s="1" t="inlineStr"/>
+      <c r="H487" s="1" t="inlineStr"/>
+      <c r="I487" s="1" t="inlineStr"/>
+      <c r="J487" s="1" t="inlineStr"/>
+      <c r="K487" s="1" t="inlineStr"/>
+      <c r="L487" s="1" t="inlineStr"/>
+      <c r="M487" s="1" t="inlineStr"/>
+      <c r="N487" s="1" t="inlineStr">
+        <is>
+          <t>L1528: symbol-only separator/garbage line :: 9, 16</t>
+        </is>
+      </c>
+      <c r="O487" s="1" t="inlineStr"/>
+      <c r="P487" s="1" t="inlineStr"/>
+      <c r="Q487" s="1" t="inlineStr"/>
+      <c r="R487" s="1" t="inlineStr"/>
+      <c r="S487" s="1" t="inlineStr"/>
+      <c r="T487" s="1" t="inlineStr"/>
+      <c r="U487" s="1" t="inlineStr"/>
+      <c r="V487" s="1" t="inlineStr"/>
+      <c r="W487" s="1" t="inlineStr"/>
+      <c r="X487" s="1" t="inlineStr"/>
+      <c r="Y487" s="1" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr"/>
+      <c r="B488" s="1" t="inlineStr"/>
+      <c r="C488" s="1" t="inlineStr"/>
+      <c r="D488" s="1" t="inlineStr"/>
+      <c r="E488" s="1" t="inlineStr"/>
+      <c r="F488" s="1" t="inlineStr"/>
+      <c r="G488" s="1" t="inlineStr"/>
+      <c r="H488" s="1" t="inlineStr"/>
+      <c r="I488" s="1" t="inlineStr"/>
+      <c r="J488" s="1" t="inlineStr"/>
+      <c r="K488" s="1" t="inlineStr"/>
+      <c r="L488" s="1" t="inlineStr"/>
+      <c r="M488" s="1" t="inlineStr"/>
+      <c r="N488" s="1" t="inlineStr">
+        <is>
+          <t>L1529: isolated marker/symbol line :: ,</t>
+        </is>
+      </c>
+      <c r="O488" s="1" t="inlineStr"/>
+      <c r="P488" s="1" t="inlineStr"/>
+      <c r="Q488" s="1" t="inlineStr"/>
+      <c r="R488" s="1" t="inlineStr"/>
+      <c r="S488" s="1" t="inlineStr"/>
+      <c r="T488" s="1" t="inlineStr"/>
+      <c r="U488" s="1" t="inlineStr"/>
+      <c r="V488" s="1" t="inlineStr"/>
+      <c r="W488" s="1" t="inlineStr"/>
+      <c r="X488" s="1" t="inlineStr"/>
+      <c r="Y488" s="1" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr"/>
+      <c r="B489" s="1" t="inlineStr"/>
+      <c r="C489" s="1" t="inlineStr"/>
+      <c r="D489" s="1" t="inlineStr"/>
+      <c r="E489" s="1" t="inlineStr"/>
+      <c r="F489" s="1" t="inlineStr"/>
+      <c r="G489" s="1" t="inlineStr"/>
+      <c r="H489" s="1" t="inlineStr"/>
+      <c r="I489" s="1" t="inlineStr"/>
+      <c r="J489" s="1" t="inlineStr"/>
+      <c r="K489" s="1" t="inlineStr"/>
+      <c r="L489" s="1" t="inlineStr"/>
+      <c r="M489" s="1" t="inlineStr"/>
+      <c r="N489" s="1" t="inlineStr">
+        <is>
+          <t>L1530: isolated marker/symbol line :: 30</t>
+        </is>
+      </c>
+      <c r="O489" s="1" t="inlineStr"/>
+      <c r="P489" s="1" t="inlineStr"/>
+      <c r="Q489" s="1" t="inlineStr"/>
+      <c r="R489" s="1" t="inlineStr"/>
+      <c r="S489" s="1" t="inlineStr"/>
+      <c r="T489" s="1" t="inlineStr"/>
+      <c r="U489" s="1" t="inlineStr"/>
+      <c r="V489" s="1" t="inlineStr"/>
+      <c r="W489" s="1" t="inlineStr"/>
+      <c r="X489" s="1" t="inlineStr"/>
+      <c r="Y489" s="1" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr"/>
+      <c r="B490" s="1" t="inlineStr"/>
+      <c r="C490" s="1" t="inlineStr"/>
+      <c r="D490" s="1" t="inlineStr"/>
+      <c r="E490" s="1" t="inlineStr"/>
+      <c r="F490" s="1" t="inlineStr"/>
+      <c r="G490" s="1" t="inlineStr"/>
+      <c r="H490" s="1" t="inlineStr"/>
+      <c r="I490" s="1" t="inlineStr"/>
+      <c r="J490" s="1" t="inlineStr"/>
+      <c r="K490" s="1" t="inlineStr"/>
+      <c r="L490" s="1" t="inlineStr"/>
+      <c r="M490" s="1" t="inlineStr"/>
+      <c r="N490" s="1" t="inlineStr">
+        <is>
+          <t>L1531: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
+      <c r="O490" s="1" t="inlineStr"/>
+      <c r="P490" s="1" t="inlineStr"/>
+      <c r="Q490" s="1" t="inlineStr"/>
+      <c r="R490" s="1" t="inlineStr"/>
+      <c r="S490" s="1" t="inlineStr"/>
+      <c r="T490" s="1" t="inlineStr"/>
+      <c r="U490" s="1" t="inlineStr"/>
+      <c r="V490" s="1" t="inlineStr"/>
+      <c r="W490" s="1" t="inlineStr"/>
+      <c r="X490" s="1" t="inlineStr"/>
+      <c r="Y490" s="1" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr"/>
+      <c r="B491" s="1" t="inlineStr"/>
+      <c r="C491" s="1" t="inlineStr"/>
+      <c r="D491" s="1" t="inlineStr"/>
+      <c r="E491" s="1" t="inlineStr"/>
+      <c r="F491" s="1" t="inlineStr"/>
+      <c r="G491" s="1" t="inlineStr"/>
+      <c r="H491" s="1" t="inlineStr"/>
+      <c r="I491" s="1" t="inlineStr"/>
+      <c r="J491" s="1" t="inlineStr"/>
+      <c r="K491" s="1" t="inlineStr"/>
+      <c r="L491" s="1" t="inlineStr"/>
+      <c r="M491" s="1" t="inlineStr"/>
+      <c r="N491" s="1" t="inlineStr">
+        <is>
+          <t>L1532: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O491" s="1" t="inlineStr"/>
+      <c r="P491" s="1" t="inlineStr"/>
+      <c r="Q491" s="1" t="inlineStr"/>
+      <c r="R491" s="1" t="inlineStr"/>
+      <c r="S491" s="1" t="inlineStr"/>
+      <c r="T491" s="1" t="inlineStr"/>
+      <c r="U491" s="1" t="inlineStr"/>
+      <c r="V491" s="1" t="inlineStr"/>
+      <c r="W491" s="1" t="inlineStr"/>
+      <c r="X491" s="1" t="inlineStr"/>
+      <c r="Y491" s="1" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr"/>
+      <c r="B492" s="1" t="inlineStr"/>
+      <c r="C492" s="1" t="inlineStr"/>
+      <c r="D492" s="1" t="inlineStr"/>
+      <c r="E492" s="1" t="inlineStr"/>
+      <c r="F492" s="1" t="inlineStr"/>
+      <c r="G492" s="1" t="inlineStr"/>
+      <c r="H492" s="1" t="inlineStr"/>
+      <c r="I492" s="1" t="inlineStr"/>
+      <c r="J492" s="1" t="inlineStr"/>
+      <c r="K492" s="1" t="inlineStr"/>
+      <c r="L492" s="1" t="inlineStr"/>
+      <c r="M492" s="1" t="inlineStr"/>
+      <c r="N492" s="1" t="inlineStr">
+        <is>
+          <t>L1533: symbol-only separator/garbage line :: 6167</t>
+        </is>
+      </c>
+      <c r="O492" s="1" t="inlineStr"/>
+      <c r="P492" s="1" t="inlineStr"/>
+      <c r="Q492" s="1" t="inlineStr"/>
+      <c r="R492" s="1" t="inlineStr"/>
+      <c r="S492" s="1" t="inlineStr"/>
+      <c r="T492" s="1" t="inlineStr"/>
+      <c r="U492" s="1" t="inlineStr"/>
+      <c r="V492" s="1" t="inlineStr"/>
+      <c r="W492" s="1" t="inlineStr"/>
+      <c r="X492" s="1" t="inlineStr"/>
+      <c r="Y492" s="1" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr"/>
+      <c r="B493" s="1" t="inlineStr"/>
+      <c r="C493" s="1" t="inlineStr"/>
+      <c r="D493" s="1" t="inlineStr"/>
+      <c r="E493" s="1" t="inlineStr"/>
+      <c r="F493" s="1" t="inlineStr"/>
+      <c r="G493" s="1" t="inlineStr"/>
+      <c r="H493" s="1" t="inlineStr"/>
+      <c r="I493" s="1" t="inlineStr"/>
+      <c r="J493" s="1" t="inlineStr"/>
+      <c r="K493" s="1" t="inlineStr"/>
+      <c r="L493" s="1" t="inlineStr"/>
+      <c r="M493" s="1" t="inlineStr"/>
+      <c r="N493" s="1" t="inlineStr">
+        <is>
+          <t>L1534: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O493" s="1" t="inlineStr"/>
+      <c r="P493" s="1" t="inlineStr"/>
+      <c r="Q493" s="1" t="inlineStr"/>
+      <c r="R493" s="1" t="inlineStr"/>
+      <c r="S493" s="1" t="inlineStr"/>
+      <c r="T493" s="1" t="inlineStr"/>
+      <c r="U493" s="1" t="inlineStr"/>
+      <c r="V493" s="1" t="inlineStr"/>
+      <c r="W493" s="1" t="inlineStr"/>
+      <c r="X493" s="1" t="inlineStr"/>
+      <c r="Y493" s="1" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr"/>
+      <c r="B494" s="1" t="inlineStr"/>
+      <c r="C494" s="1" t="inlineStr"/>
+      <c r="D494" s="1" t="inlineStr"/>
+      <c r="E494" s="1" t="inlineStr"/>
+      <c r="F494" s="1" t="inlineStr"/>
+      <c r="G494" s="1" t="inlineStr"/>
+      <c r="H494" s="1" t="inlineStr"/>
+      <c r="I494" s="1" t="inlineStr"/>
+      <c r="J494" s="1" t="inlineStr"/>
+      <c r="K494" s="1" t="inlineStr"/>
+      <c r="L494" s="1" t="inlineStr"/>
+      <c r="M494" s="1" t="inlineStr"/>
+      <c r="N494" s="1" t="inlineStr">
+        <is>
+          <t>L1535: isolated marker/symbol line :: X</t>
+        </is>
+      </c>
+      <c r="O494" s="1" t="inlineStr"/>
+      <c r="P494" s="1" t="inlineStr"/>
+      <c r="Q494" s="1" t="inlineStr"/>
+      <c r="R494" s="1" t="inlineStr"/>
+      <c r="S494" s="1" t="inlineStr"/>
+      <c r="T494" s="1" t="inlineStr"/>
+      <c r="U494" s="1" t="inlineStr"/>
+      <c r="V494" s="1" t="inlineStr"/>
+      <c r="W494" s="1" t="inlineStr"/>
+      <c r="X494" s="1" t="inlineStr"/>
+      <c r="Y494" s="1" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr"/>
+      <c r="B495" s="1" t="inlineStr"/>
+      <c r="C495" s="1" t="inlineStr"/>
+      <c r="D495" s="1" t="inlineStr"/>
+      <c r="E495" s="1" t="inlineStr"/>
+      <c r="F495" s="1" t="inlineStr"/>
+      <c r="G495" s="1" t="inlineStr"/>
+      <c r="H495" s="1" t="inlineStr"/>
+      <c r="I495" s="1" t="inlineStr"/>
+      <c r="J495" s="1" t="inlineStr"/>
+      <c r="K495" s="1" t="inlineStr"/>
+      <c r="L495" s="1" t="inlineStr"/>
+      <c r="M495" s="1" t="inlineStr"/>
+      <c r="N495" s="1" t="inlineStr">
+        <is>
+          <t>L1536: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
+        </is>
+      </c>
+      <c r="O495" s="1" t="inlineStr"/>
+      <c r="P495" s="1" t="inlineStr"/>
+      <c r="Q495" s="1" t="inlineStr"/>
+      <c r="R495" s="1" t="inlineStr"/>
+      <c r="S495" s="1" t="inlineStr"/>
+      <c r="T495" s="1" t="inlineStr"/>
+      <c r="U495" s="1" t="inlineStr"/>
+      <c r="V495" s="1" t="inlineStr"/>
+      <c r="W495" s="1" t="inlineStr"/>
+      <c r="X495" s="1" t="inlineStr"/>
+      <c r="Y495" s="1" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr"/>
+      <c r="B496" s="1" t="inlineStr"/>
+      <c r="C496" s="1" t="inlineStr"/>
+      <c r="D496" s="1" t="inlineStr"/>
+      <c r="E496" s="1" t="inlineStr"/>
+      <c r="F496" s="1" t="inlineStr"/>
+      <c r="G496" s="1" t="inlineStr"/>
+      <c r="H496" s="1" t="inlineStr"/>
+      <c r="I496" s="1" t="inlineStr"/>
+      <c r="J496" s="1" t="inlineStr"/>
+      <c r="K496" s="1" t="inlineStr"/>
+      <c r="L496" s="1" t="inlineStr"/>
+      <c r="M496" s="1" t="inlineStr"/>
+      <c r="N496" s="1" t="inlineStr">
+        <is>
+          <t>L1537: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O496" s="1" t="inlineStr"/>
+      <c r="P496" s="1" t="inlineStr"/>
+      <c r="Q496" s="1" t="inlineStr"/>
+      <c r="R496" s="1" t="inlineStr"/>
+      <c r="S496" s="1" t="inlineStr"/>
+      <c r="T496" s="1" t="inlineStr"/>
+      <c r="U496" s="1" t="inlineStr"/>
+      <c r="V496" s="1" t="inlineStr"/>
+      <c r="W496" s="1" t="inlineStr"/>
+      <c r="X496" s="1" t="inlineStr"/>
+      <c r="Y496" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
